--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY153"/>
+  <dimension ref="A1:AY155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,7 +804,7 @@
         <v>126722664</v>
       </c>
       <c r="B3" t="n">
-        <v>105381</v>
+        <v>105456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126722149</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>126722342</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>126722592</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>126722905</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>126728180</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,32 +1392,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126722514</v>
+        <v>126722949</v>
       </c>
       <c r="B9" t="n">
-        <v>98382</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>857040</v>
+        <v>857001</v>
       </c>
       <c r="R9" t="n">
-        <v>7485799</v>
+        <v>7485674</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,32 +1489,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126722949</v>
+        <v>126722514</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98457</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>857001</v>
+        <v>857040</v>
       </c>
       <c r="R10" t="n">
-        <v>7485674</v>
+        <v>7485799</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,7 +1589,7 @@
         <v>126722689</v>
       </c>
       <c r="B11" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>126728177</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>126722224</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,32 +1877,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126728179</v>
+        <v>126728181</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>857020</v>
+        <v>857024</v>
       </c>
       <c r="R14" t="n">
-        <v>7485779</v>
+        <v>7485613</v>
       </c>
       <c r="S14" t="n">
         <v>14</v>
@@ -1977,7 +1977,7 @@
         <v>126722469</v>
       </c>
       <c r="B15" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,10 +2071,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126722237</v>
+        <v>126728179</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2099,29 +2099,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Aihkivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>856991</v>
+        <v>857020</v>
       </c>
       <c r="R16" t="n">
-        <v>7485798</v>
+        <v>7485779</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2165,60 +2156,69 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126728181</v>
+        <v>126722237</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>857024</v>
+        <v>856991</v>
       </c>
       <c r="R17" t="n">
-        <v>7485613</v>
+        <v>7485798</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2262,12 +2262,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2277,7 +2277,7 @@
         <v>126722544</v>
       </c>
       <c r="B18" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126722552</v>
+        <v>126722838</v>
       </c>
       <c r="B19" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,17 +2399,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>857113</v>
+        <v>857027</v>
       </c>
       <c r="R19" t="n">
-        <v>7485787</v>
+        <v>7485680</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2468,10 +2477,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126722838</v>
+        <v>126722552</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2496,26 +2505,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>857027</v>
+        <v>857113</v>
       </c>
       <c r="R20" t="n">
-        <v>7485680</v>
+        <v>7485787</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
         <v>126722312</v>
       </c>
       <c r="B21" t="n">
-        <v>91195</v>
+        <v>91269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>126722784</v>
       </c>
       <c r="B22" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126728176</v>
+        <v>126728174</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>857131</v>
+        <v>856948</v>
       </c>
       <c r="R23" t="n">
-        <v>7485656</v>
+        <v>7485759</v>
       </c>
       <c r="S23" t="n">
         <v>14</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126728174</v>
+        <v>126728176</v>
       </c>
       <c r="B24" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>856948</v>
+        <v>857131</v>
       </c>
       <c r="R24" t="n">
-        <v>7485759</v>
+        <v>7485656</v>
       </c>
       <c r="S24" t="n">
         <v>14</v>
@@ -2965,7 +2965,7 @@
         <v>126722975</v>
       </c>
       <c r="B25" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>126722205</v>
       </c>
       <c r="B26" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>126728182</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>126728178</v>
       </c>
       <c r="B28" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>126722914</v>
       </c>
       <c r="B29" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>126722768</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126895913</v>
+        <v>126893335</v>
       </c>
       <c r="B31" t="n">
-        <v>80112</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>857071</v>
+        <v>857254</v>
       </c>
       <c r="R31" t="n">
-        <v>7485419</v>
+        <v>7485706</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3638,12 +3638,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3654,32 +3654,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893335</v>
+        <v>126889016</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3689,13 +3689,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>857254</v>
+        <v>857042</v>
       </c>
       <c r="R32" t="n">
-        <v>7485706</v>
+        <v>7485656</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3739,12 +3739,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3755,10 +3755,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126889016</v>
+        <v>126893321</v>
       </c>
       <c r="B33" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>857042</v>
+        <v>857154</v>
       </c>
       <c r="R33" t="n">
-        <v>7485656</v>
+        <v>7485805</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3840,12 +3840,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3856,10 +3856,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126893321</v>
+        <v>126895913</v>
       </c>
       <c r="B34" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857154</v>
+        <v>857071</v>
       </c>
       <c r="R34" t="n">
-        <v>7485805</v>
+        <v>7485419</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3941,12 +3941,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -3960,7 +3960,7 @@
         <v>126894596</v>
       </c>
       <c r="B35" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4058,32 +4058,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126894589</v>
+        <v>126894580</v>
       </c>
       <c r="B36" t="n">
-        <v>98361</v>
+        <v>80143</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>857303</v>
+        <v>857065</v>
       </c>
       <c r="R36" t="n">
-        <v>7485733</v>
+        <v>7485568</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4162,7 +4162,7 @@
         <v>126893328</v>
       </c>
       <c r="B37" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,48 +4260,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126894580</v>
+        <v>126893330</v>
       </c>
       <c r="B38" t="n">
-        <v>80112</v>
+        <v>98436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>857065</v>
+        <v>857082</v>
       </c>
       <c r="R38" t="n">
-        <v>7485568</v>
+        <v>7485465</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4345,12 +4345,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4361,10 +4361,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126893330</v>
+        <v>126895971</v>
       </c>
       <c r="B39" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>857082</v>
+        <v>856836</v>
       </c>
       <c r="R39" t="n">
-        <v>7485465</v>
+        <v>7485559</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4446,26 +4446,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126895971</v>
+        <v>126894589</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,17 +4489,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>856836</v>
+        <v>857303</v>
       </c>
       <c r="R40" t="n">
-        <v>7485559</v>
+        <v>7485733</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4547,57 +4543,61 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126894594</v>
+        <v>126889022</v>
       </c>
       <c r="B41" t="n">
-        <v>98361</v>
+        <v>80143</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>857257</v>
+        <v>856972</v>
       </c>
       <c r="R41" t="n">
-        <v>7485627</v>
+        <v>7485632</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4644,12 +4644,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4660,10 +4660,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126893332</v>
+        <v>126894594</v>
       </c>
       <c r="B42" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,17 +4691,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>857047</v>
+        <v>857257</v>
       </c>
       <c r="R42" t="n">
-        <v>7485515</v>
+        <v>7485627</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4745,12 +4745,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4761,32 +4761,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126889022</v>
+        <v>126889042</v>
       </c>
       <c r="B43" t="n">
-        <v>80112</v>
+        <v>98436</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>856972</v>
+        <v>857162</v>
       </c>
       <c r="R43" t="n">
-        <v>7485632</v>
+        <v>7485708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4865,7 +4865,7 @@
         <v>126894588</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126883898</v>
+        <v>126895969</v>
       </c>
       <c r="B45" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4991,33 +4991,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>856979</v>
+        <v>856881</v>
       </c>
       <c r="R45" t="n">
-        <v>7485287</v>
+        <v>7485580</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5047,19 +5031,14 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:19</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Blommande</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5068,29 +5047,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126895969</v>
+        <v>126893332</v>
       </c>
       <c r="B46" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5118,17 +5096,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>856881</v>
+        <v>857047</v>
       </c>
       <c r="R46" t="n">
-        <v>7485580</v>
+        <v>7485515</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5158,11 +5136,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Blommande</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5177,57 +5150,61 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126889042</v>
+        <v>126894582</v>
       </c>
       <c r="B47" t="n">
-        <v>98361</v>
+        <v>80143</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>857162</v>
+        <v>856922</v>
       </c>
       <c r="R47" t="n">
-        <v>7485708</v>
+        <v>7485635</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5262,6 +5239,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>på Sälg</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5274,12 +5256,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5290,10 +5272,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126888930</v>
+        <v>126895968</v>
       </c>
       <c r="B48" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5321,17 +5303,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>856694</v>
+        <v>856872</v>
       </c>
       <c r="R48" t="n">
-        <v>7485592</v>
+        <v>7485620</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5361,6 +5343,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Flera blommande ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5375,26 +5362,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126888927</v>
+        <v>126889044</v>
       </c>
       <c r="B49" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5426,10 +5409,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>856896</v>
+        <v>857220</v>
       </c>
       <c r="R49" t="n">
-        <v>7485538</v>
+        <v>7485601</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5476,12 +5459,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5495,7 +5478,7 @@
         <v>126895916</v>
       </c>
       <c r="B50" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5593,10 +5576,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126889044</v>
+        <v>126888930</v>
       </c>
       <c r="B51" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5628,10 +5611,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>857220</v>
+        <v>856694</v>
       </c>
       <c r="R51" t="n">
-        <v>7485601</v>
+        <v>7485592</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5678,12 +5661,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5694,48 +5677,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126895963</v>
+        <v>126888927</v>
       </c>
       <c r="B52" t="n">
-        <v>98382</v>
+        <v>98436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>856930</v>
+        <v>856896</v>
       </c>
       <c r="R52" t="n">
-        <v>7485560</v>
+        <v>7485538</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5765,11 +5748,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5784,44 +5762,48 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126895968</v>
+        <v>126895963</v>
       </c>
       <c r="B53" t="n">
-        <v>98361</v>
+        <v>98457</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5831,10 +5813,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>856872</v>
+        <v>856930</v>
       </c>
       <c r="R53" t="n">
-        <v>7485620</v>
+        <v>7485560</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5871,7 +5853,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Flera blommande ex</t>
+          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5898,48 +5880,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126894582</v>
+        <v>126893336</v>
       </c>
       <c r="B54" t="n">
-        <v>80112</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>856922</v>
+        <v>857022</v>
       </c>
       <c r="R54" t="n">
-        <v>7485635</v>
+        <v>7485521</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5969,11 +5951,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>på Sälg</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5988,12 +5965,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6004,48 +5981,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126895972</v>
+        <v>126888926</v>
       </c>
       <c r="B55" t="n">
-        <v>98361</v>
+        <v>80150</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>856725</v>
+        <v>856904</v>
       </c>
       <c r="R55" t="n">
-        <v>7485571</v>
+        <v>7485446</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6089,44 +6066,48 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126888926</v>
+        <v>126893326</v>
       </c>
       <c r="B56" t="n">
-        <v>80119</v>
+        <v>57654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6136,13 +6117,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>856904</v>
+        <v>857089</v>
       </c>
       <c r="R56" t="n">
-        <v>7485446</v>
+        <v>7485450</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6172,6 +6153,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6186,12 +6172,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6202,48 +6188,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126893336</v>
+        <v>126895972</v>
       </c>
       <c r="B57" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>857022</v>
+        <v>856725</v>
       </c>
       <c r="R57" t="n">
-        <v>7485521</v>
+        <v>7485571</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6287,26 +6273,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126893326</v>
+        <v>126893319</v>
       </c>
       <c r="B58" t="n">
-        <v>57654</v>
+        <v>91494</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6314,21 +6296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>1588</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6338,10 +6320,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>857089</v>
+        <v>857122</v>
       </c>
       <c r="R58" t="n">
-        <v>7485450</v>
+        <v>7485443</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6374,11 +6356,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6409,10 +6386,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126893319</v>
+        <v>126889052</v>
       </c>
       <c r="B59" t="n">
-        <v>91420</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6420,21 +6397,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6444,13 +6421,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>857122</v>
+        <v>857206</v>
       </c>
       <c r="R59" t="n">
-        <v>7485443</v>
+        <v>7485553</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6494,12 +6471,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6513,7 +6490,7 @@
         <v>126889013</v>
       </c>
       <c r="B60" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6614,7 +6591,7 @@
         <v>126894581</v>
       </c>
       <c r="B61" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6715,7 +6692,7 @@
         <v>126888928</v>
       </c>
       <c r="B62" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6813,32 +6790,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126889052</v>
+        <v>126895915</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6848,13 +6825,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>857206</v>
+        <v>857242</v>
       </c>
       <c r="R63" t="n">
-        <v>7485553</v>
+        <v>7485724</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6898,12 +6875,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -6914,48 +6891,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126895961</v>
+        <v>126889041</v>
       </c>
       <c r="B64" t="n">
-        <v>75075</v>
+        <v>98436</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>856840</v>
+        <v>856978</v>
       </c>
       <c r="R64" t="n">
-        <v>7485479</v>
+        <v>7485792</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6999,22 +6976,26 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>126895921</v>
       </c>
       <c r="B65" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7112,48 +7093,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126894583</v>
+        <v>126895961</v>
       </c>
       <c r="B66" t="n">
-        <v>98382</v>
+        <v>75135</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>856988</v>
+        <v>856840</v>
       </c>
       <c r="R66" t="n">
-        <v>7485572</v>
+        <v>7485479</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7197,61 +7178,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126889041</v>
+        <v>126894583</v>
       </c>
       <c r="B67" t="n">
-        <v>98361</v>
+        <v>98457</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>856978</v>
+        <v>856988</v>
       </c>
       <c r="R67" t="n">
-        <v>7485792</v>
+        <v>7485572</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7298,12 +7275,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7317,7 +7294,7 @@
         <v>126889032</v>
       </c>
       <c r="B68" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7415,10 +7392,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126895915</v>
+        <v>126889045</v>
       </c>
       <c r="B69" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7450,13 +7427,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>857242</v>
+        <v>857084</v>
       </c>
       <c r="R69" t="n">
-        <v>7485724</v>
+        <v>7485530</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7500,12 +7477,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7516,32 +7493,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126895910</v>
+        <v>126889047</v>
       </c>
       <c r="B70" t="n">
-        <v>80112</v>
+        <v>98436</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7551,13 +7528,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>856984</v>
+        <v>857010</v>
       </c>
       <c r="R70" t="n">
-        <v>7485600</v>
+        <v>7485585</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7601,12 +7578,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7617,32 +7594,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126889045</v>
+        <v>126889029</v>
       </c>
       <c r="B71" t="n">
-        <v>98361</v>
+        <v>98457</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7652,10 +7629,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>857084</v>
+        <v>857083</v>
       </c>
       <c r="R71" t="n">
-        <v>7485530</v>
+        <v>7485527</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7718,10 +7695,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126889029</v>
+        <v>126895910</v>
       </c>
       <c r="B72" t="n">
-        <v>98382</v>
+        <v>80143</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7729,21 +7706,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7753,13 +7730,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>857083</v>
+        <v>856984</v>
       </c>
       <c r="R72" t="n">
-        <v>7485527</v>
+        <v>7485600</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7803,12 +7780,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7819,32 +7796,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126895920</v>
+        <v>126889021</v>
       </c>
       <c r="B73" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7854,13 +7831,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>857173</v>
+        <v>857000</v>
       </c>
       <c r="R73" t="n">
-        <v>7485506</v>
+        <v>7485629</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7904,12 +7881,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7920,10 +7897,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126889021</v>
+        <v>126889024</v>
       </c>
       <c r="B74" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7955,10 +7932,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>857000</v>
+        <v>856962</v>
       </c>
       <c r="R74" t="n">
-        <v>7485629</v>
+        <v>7485641</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8021,32 +7998,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126889047</v>
+        <v>126895920</v>
       </c>
       <c r="B75" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8056,13 +8033,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>857010</v>
+        <v>857173</v>
       </c>
       <c r="R75" t="n">
-        <v>7485585</v>
+        <v>7485506</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8106,12 +8083,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8122,32 +8099,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126889024</v>
+        <v>126895922</v>
       </c>
       <c r="B76" t="n">
-        <v>80112</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8157,13 +8134,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>856962</v>
+        <v>856981</v>
       </c>
       <c r="R76" t="n">
-        <v>7485641</v>
+        <v>7485578</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8207,12 +8184,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8223,48 +8200,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126895922</v>
+        <v>126894584</v>
       </c>
       <c r="B77" t="n">
-        <v>78980</v>
+        <v>97320</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>856981</v>
+        <v>857231</v>
       </c>
       <c r="R77" t="n">
-        <v>7485578</v>
+        <v>7485574</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8308,12 +8285,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8327,7 +8304,7 @@
         <v>126889039</v>
       </c>
       <c r="B78" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8425,32 +8402,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126894584</v>
+        <v>126894602</v>
       </c>
       <c r="B79" t="n">
-        <v>97245</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8460,10 +8437,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>857231</v>
+        <v>857075</v>
       </c>
       <c r="R79" t="n">
-        <v>7485574</v>
+        <v>7485539</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8526,48 +8503,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126894602</v>
+        <v>126895912</v>
       </c>
       <c r="B80" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>857075</v>
+        <v>857018</v>
       </c>
       <c r="R80" t="n">
-        <v>7485539</v>
+        <v>7485408</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8611,12 +8588,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8630,7 +8607,7 @@
         <v>126895918</v>
       </c>
       <c r="B81" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8728,32 +8705,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126895912</v>
+        <v>126888931</v>
       </c>
       <c r="B82" t="n">
-        <v>80112</v>
+        <v>91893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8763,13 +8740,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>857018</v>
+        <v>856896</v>
       </c>
       <c r="R82" t="n">
-        <v>7485408</v>
+        <v>7485431</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8813,12 +8790,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8829,32 +8806,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126894601</v>
+        <v>126894590</v>
       </c>
       <c r="B83" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8864,10 +8841,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>857215</v>
+        <v>857265</v>
       </c>
       <c r="R83" t="n">
-        <v>7485457</v>
+        <v>7485680</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8930,48 +8907,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126894590</v>
+        <v>126893339</v>
       </c>
       <c r="B84" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>857265</v>
+        <v>857104</v>
       </c>
       <c r="R84" t="n">
-        <v>7485680</v>
+        <v>7485447</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9015,12 +8992,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9031,45 +9008,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126888931</v>
+        <v>126894601</v>
       </c>
       <c r="B85" t="n">
-        <v>91819</v>
+        <v>79011</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>856896</v>
+        <v>857215</v>
       </c>
       <c r="R85" t="n">
-        <v>7485431</v>
+        <v>7485457</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9116,12 +9093,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9135,7 +9112,7 @@
         <v>126889019</v>
       </c>
       <c r="B86" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9233,32 +9210,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126893339</v>
+        <v>126888929</v>
       </c>
       <c r="B87" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9268,13 +9245,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>857104</v>
+        <v>856800</v>
       </c>
       <c r="R87" t="n">
-        <v>7485447</v>
+        <v>7485540</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9318,12 +9295,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9334,32 +9311,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126888929</v>
+        <v>126895917</v>
       </c>
       <c r="B88" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9369,13 +9346,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>856800</v>
+        <v>857220</v>
       </c>
       <c r="R88" t="n">
-        <v>7485540</v>
+        <v>7485407</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9419,12 +9396,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9435,48 +9412,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126895973</v>
+        <v>126889017</v>
       </c>
       <c r="B89" t="n">
-        <v>98361</v>
+        <v>80143</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>856707</v>
+        <v>857021</v>
       </c>
       <c r="R89" t="n">
-        <v>7485577</v>
+        <v>7485648</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9520,22 +9497,26 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126889017</v>
+        <v>126889034</v>
       </c>
       <c r="B90" t="n">
-        <v>80112</v>
+        <v>98457</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9543,21 +9524,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9567,10 +9548,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>857021</v>
+        <v>856998</v>
       </c>
       <c r="R90" t="n">
-        <v>7485648</v>
+        <v>7485630</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9633,48 +9614,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126895917</v>
+        <v>126895973</v>
       </c>
       <c r="B91" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>857220</v>
+        <v>856707</v>
       </c>
       <c r="R91" t="n">
-        <v>7485407</v>
+        <v>7485577</v>
       </c>
       <c r="S91" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9718,64 +9699,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126889034</v>
+        <v>126895962</v>
       </c>
       <c r="B92" t="n">
-        <v>98382</v>
+        <v>91319</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>856998</v>
+        <v>856927</v>
       </c>
       <c r="R92" t="n">
-        <v>7485630</v>
+        <v>7485482</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9819,26 +9796,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126889025</v>
+        <v>126893327</v>
       </c>
       <c r="B93" t="n">
-        <v>80112</v>
+        <v>91303</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9846,21 +9819,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>4660</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9870,13 +9843,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>856955</v>
+        <v>857141</v>
       </c>
       <c r="R93" t="n">
-        <v>7485682</v>
+        <v>7485413</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9920,12 +9893,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -9936,48 +9909,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126895962</v>
+        <v>126889025</v>
       </c>
       <c r="B94" t="n">
-        <v>91245</v>
+        <v>80143</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>856927</v>
+        <v>856955</v>
       </c>
       <c r="R94" t="n">
-        <v>7485482</v>
+        <v>7485682</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10021,44 +9994,48 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126893327</v>
+        <v>126889050</v>
       </c>
       <c r="B95" t="n">
-        <v>91229</v>
+        <v>79011</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10068,13 +10045,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>857141</v>
+        <v>857208</v>
       </c>
       <c r="R95" t="n">
-        <v>7485413</v>
+        <v>7485545</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10118,12 +10095,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10134,10 +10111,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126893325</v>
+        <v>126893323</v>
       </c>
       <c r="B96" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10169,10 +10146,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>856884</v>
+        <v>856995</v>
       </c>
       <c r="R96" t="n">
-        <v>7485698</v>
+        <v>7485538</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10235,10 +10212,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126895914</v>
+        <v>126893325</v>
       </c>
       <c r="B97" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10270,13 +10247,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>856958</v>
+        <v>856884</v>
       </c>
       <c r="R97" t="n">
-        <v>7485679</v>
+        <v>7485698</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10320,12 +10297,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10336,10 +10313,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126893323</v>
+        <v>126895914</v>
       </c>
       <c r="B98" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10371,13 +10348,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>856995</v>
+        <v>856958</v>
       </c>
       <c r="R98" t="n">
-        <v>7485538</v>
+        <v>7485679</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10421,12 +10398,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10440,7 +10417,7 @@
         <v>126893333</v>
       </c>
       <c r="B99" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10538,45 +10515,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126889050</v>
+        <v>126894595</v>
       </c>
       <c r="B100" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>857208</v>
+        <v>857231</v>
       </c>
       <c r="R100" t="n">
-        <v>7485545</v>
+        <v>7485574</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10623,12 +10600,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10642,7 +10619,7 @@
         <v>126889049</v>
       </c>
       <c r="B101" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10740,10 +10717,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126883661</v>
+        <v>126895967</v>
       </c>
       <c r="B102" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10771,14 +10748,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>856901</v>
+        <v>856932</v>
       </c>
       <c r="R102" t="n">
-        <v>7485387</v>
+        <v>7485559</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -10808,19 +10785,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>13:19</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10835,60 +10802,60 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126895967</v>
+        <v>126895911</v>
       </c>
       <c r="B103" t="n">
-        <v>98361</v>
+        <v>80143</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>856932</v>
+        <v>856885</v>
       </c>
       <c r="R103" t="n">
-        <v>7485559</v>
+        <v>7485704</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10918,6 +10885,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10932,69 +10904,64 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr"/>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126882171</v>
+        <v>126889036</v>
       </c>
       <c r="B104" t="n">
-        <v>98361</v>
+        <v>80018</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>856765</v>
+        <v>857182</v>
       </c>
       <c r="R104" t="n">
-        <v>7485445</v>
+        <v>7485442</v>
       </c>
       <c r="S104" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11021,19 +10988,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>11:57</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11048,22 +11005,26 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126895911</v>
+        <v>126889037</v>
       </c>
       <c r="B105" t="n">
-        <v>80112</v>
+        <v>80018</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11071,21 +11032,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11095,13 +11056,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>856885</v>
+        <v>857094</v>
       </c>
       <c r="R105" t="n">
-        <v>7485704</v>
+        <v>7485517</v>
       </c>
       <c r="S105" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11131,11 +11092,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11150,12 +11106,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11166,48 +11122,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126894595</v>
+        <v>126893322</v>
       </c>
       <c r="B106" t="n">
-        <v>98361</v>
+        <v>80143</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>857231</v>
+        <v>857015</v>
       </c>
       <c r="R106" t="n">
-        <v>7485574</v>
+        <v>7485514</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11251,12 +11207,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11267,10 +11223,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126889036</v>
+        <v>126895966</v>
       </c>
       <c r="B107" t="n">
-        <v>79987</v>
+        <v>80150</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11278,37 +11234,40 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>857182</v>
+        <v>856849</v>
       </c>
       <c r="R107" t="n">
-        <v>7485442</v>
+        <v>7485405</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11346,54 +11305,51 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126883505</v>
+        <v>126893338</v>
       </c>
       <c r="B108" t="n">
-        <v>91210</v>
+        <v>79011</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11403,13 +11359,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>856901</v>
+        <v>856954</v>
       </c>
       <c r="R108" t="n">
-        <v>7485387</v>
+        <v>7485603</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11436,21 +11392,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -11459,46 +11405,30 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126893322</v>
+        <v>126893324</v>
       </c>
       <c r="B109" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11530,10 +11460,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>857015</v>
+        <v>856949</v>
       </c>
       <c r="R109" t="n">
-        <v>7485514</v>
+        <v>7485588</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11596,48 +11526,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126889037</v>
+        <v>126895975</v>
       </c>
       <c r="B110" t="n">
-        <v>79987</v>
+        <v>79011</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>857094</v>
+        <v>856864</v>
       </c>
       <c r="R110" t="n">
-        <v>7485517</v>
+        <v>7485417</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11681,67 +11611,60 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126895966</v>
+        <v>126893334</v>
       </c>
       <c r="B111" t="n">
-        <v>80119</v>
+        <v>98436</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>856849</v>
+        <v>856938</v>
       </c>
       <c r="R111" t="n">
-        <v>7485405</v>
+        <v>7485632</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11779,51 +11702,54 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126893338</v>
+        <v>126893329</v>
       </c>
       <c r="B112" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11833,10 +11759,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>856954</v>
+        <v>857202</v>
       </c>
       <c r="R112" t="n">
-        <v>7485603</v>
+        <v>7485431</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11899,10 +11825,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126893324</v>
+        <v>126894585</v>
       </c>
       <c r="B113" t="n">
-        <v>80112</v>
+        <v>97320</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11910,37 +11836,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>856949</v>
+        <v>857167</v>
       </c>
       <c r="R113" t="n">
-        <v>7485588</v>
+        <v>7485432</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11984,12 +11910,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12000,32 +11926,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126893334</v>
+        <v>126893320</v>
       </c>
       <c r="B114" t="n">
-        <v>98361</v>
+        <v>80143</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12035,10 +11961,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>856938</v>
+        <v>857058</v>
       </c>
       <c r="R114" t="n">
-        <v>7485632</v>
+        <v>7485807</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12101,32 +12027,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126895975</v>
+        <v>126895970</v>
       </c>
       <c r="B115" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12136,10 +12062,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>856864</v>
+        <v>856849</v>
       </c>
       <c r="R115" t="n">
-        <v>7485417</v>
+        <v>7485559</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12198,48 +12124,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126893320</v>
+        <v>126894592</v>
       </c>
       <c r="B116" t="n">
-        <v>80112</v>
+        <v>98436</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>857058</v>
+        <v>857255</v>
       </c>
       <c r="R116" t="n">
-        <v>7485807</v>
+        <v>7485644</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12283,12 +12209,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12299,48 +12225,48 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126893329</v>
+        <v>126894600</v>
       </c>
       <c r="B117" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>857202</v>
+        <v>857163</v>
       </c>
       <c r="R117" t="n">
-        <v>7485431</v>
+        <v>7485497</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12384,12 +12310,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12400,32 +12326,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126894585</v>
+        <v>126894597</v>
       </c>
       <c r="B118" t="n">
-        <v>97245</v>
+        <v>79011</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12435,10 +12361,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>857167</v>
+        <v>857222</v>
       </c>
       <c r="R118" t="n">
-        <v>7485432</v>
+        <v>7485544</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12501,45 +12427,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126894597</v>
+        <v>126889027</v>
       </c>
       <c r="B119" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>857222</v>
+        <v>856947</v>
       </c>
       <c r="R119" t="n">
-        <v>7485544</v>
+        <v>7485678</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12586,12 +12512,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12602,32 +12528,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126895970</v>
+        <v>126895965</v>
       </c>
       <c r="B120" t="n">
-        <v>98361</v>
+        <v>80150</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12637,10 +12563,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>856849</v>
+        <v>856897</v>
       </c>
       <c r="R120" t="n">
-        <v>7485559</v>
+        <v>7485429</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12699,10 +12625,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126895965</v>
+        <v>126889014</v>
       </c>
       <c r="B121" t="n">
-        <v>80119</v>
+        <v>80143</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12710,37 +12636,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>856897</v>
+        <v>857043</v>
       </c>
       <c r="R121" t="n">
-        <v>7485429</v>
+        <v>7485634</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12784,57 +12710,61 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126894600</v>
+        <v>126889030</v>
       </c>
       <c r="B122" t="n">
-        <v>78980</v>
+        <v>98457</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>857163</v>
+        <v>857008</v>
       </c>
       <c r="R122" t="n">
-        <v>7485497</v>
+        <v>7485578</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12881,12 +12811,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -12897,10 +12827,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126894592</v>
+        <v>126899900</v>
       </c>
       <c r="B123" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12925,17 +12855,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>857255</v>
+        <v>856926</v>
       </c>
       <c r="R123" t="n">
-        <v>7485644</v>
+        <v>7485578</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12976,18 +12918,19 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -12998,45 +12941,57 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126889027</v>
+        <v>126899898</v>
       </c>
       <c r="B124" t="n">
-        <v>80112</v>
+        <v>98436</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>856947</v>
+        <v>856878</v>
       </c>
       <c r="R124" t="n">
-        <v>7485678</v>
+        <v>7485406</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13077,18 +13032,19 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13099,32 +13055,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126889030</v>
+        <v>126899894</v>
       </c>
       <c r="B125" t="n">
-        <v>98382</v>
+        <v>75135</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13134,10 +13090,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>857008</v>
+        <v>856906</v>
       </c>
       <c r="R125" t="n">
-        <v>7485578</v>
+        <v>7485559</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13184,12 +13140,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13200,10 +13156,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126882331</v>
+        <v>126899816</v>
       </c>
       <c r="B126" t="n">
-        <v>80111</v>
+        <v>80150</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13211,21 +13167,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13235,13 +13191,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>856765</v>
+        <v>856947</v>
       </c>
       <c r="R126" t="n">
-        <v>7485445</v>
+        <v>7485478</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13268,19 +13224,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13295,44 +13241,48 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126889014</v>
+        <v>126899814</v>
       </c>
       <c r="B127" t="n">
-        <v>80112</v>
+        <v>75135</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13342,10 +13292,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>857043</v>
+        <v>856935</v>
       </c>
       <c r="R127" t="n">
-        <v>7485634</v>
+        <v>7485477</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13392,12 +13342,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13408,57 +13358,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126899898</v>
+        <v>126899815</v>
       </c>
       <c r="B128" t="n">
-        <v>98361</v>
+        <v>98457</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>856878</v>
+        <v>856883</v>
       </c>
       <c r="R128" t="n">
-        <v>7485406</v>
+        <v>7485400</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13499,7 +13437,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13511,7 +13448,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13522,57 +13459,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126899900</v>
+        <v>126899897</v>
       </c>
       <c r="B129" t="n">
-        <v>98361</v>
+        <v>80150</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>856926</v>
+        <v>856930</v>
       </c>
       <c r="R129" t="n">
-        <v>7485578</v>
+        <v>7485569</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13613,7 +13538,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13636,45 +13560,57 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126899816</v>
+        <v>126899818</v>
       </c>
       <c r="B130" t="n">
-        <v>80119</v>
+        <v>98436</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>856947</v>
+        <v>856921</v>
       </c>
       <c r="R130" t="n">
-        <v>7485478</v>
+        <v>7485611</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13715,6 +13651,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13737,32 +13674,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126899894</v>
+        <v>126899896</v>
       </c>
       <c r="B131" t="n">
-        <v>75075</v>
+        <v>80143</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13772,10 +13709,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>856906</v>
+        <v>856908</v>
       </c>
       <c r="R131" t="n">
-        <v>7485559</v>
+        <v>7485414</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13838,45 +13775,57 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126895795</v>
+        <v>126899899</v>
       </c>
       <c r="B132" t="n">
-        <v>97239</v>
+        <v>98436</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Ritaiaki, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>856787</v>
+        <v>856845</v>
       </c>
       <c r="R132" t="n">
-        <v>7485429</v>
+        <v>7485518</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13917,63 +13866,80 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr"/>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126899814</v>
+        <v>126899817</v>
       </c>
       <c r="B133" t="n">
-        <v>75075</v>
+        <v>98436</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>856935</v>
+        <v>856875</v>
       </c>
       <c r="R133" t="n">
-        <v>7485477</v>
+        <v>7485584</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14014,6 +13980,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14036,45 +14003,57 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126899815</v>
+        <v>126899820</v>
       </c>
       <c r="B134" t="n">
-        <v>98382</v>
+        <v>98436</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>856883</v>
+        <v>856838</v>
       </c>
       <c r="R134" t="n">
-        <v>7485400</v>
+        <v>7485421</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14115,6 +14094,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14137,45 +14117,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126895801</v>
+        <v>126899902</v>
       </c>
       <c r="B135" t="n">
-        <v>78980</v>
+        <v>91893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Ritaiaki, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>856696</v>
+        <v>856867</v>
       </c>
       <c r="R135" t="n">
-        <v>7485502</v>
+        <v>7485409</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14222,57 +14202,73 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr"/>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126899897</v>
+        <v>126899819</v>
       </c>
       <c r="B136" t="n">
-        <v>80119</v>
+        <v>98436</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>856930</v>
+        <v>856846</v>
       </c>
       <c r="R136" t="n">
-        <v>7485569</v>
+        <v>7485645</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14313,6 +14309,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14324,7 +14321,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14335,57 +14332,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126899818</v>
+        <v>126899901</v>
       </c>
       <c r="B137" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>856921</v>
+        <v>856929</v>
       </c>
       <c r="R137" t="n">
-        <v>7485611</v>
+        <v>7485563</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14426,7 +14411,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14438,7 +14422,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14449,10 +14433,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126895799</v>
+        <v>126899895</v>
       </c>
       <c r="B138" t="n">
-        <v>78980</v>
+        <v>75135</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14460,34 +14444,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Ritaiaki, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>857189</v>
+        <v>856927</v>
       </c>
       <c r="R138" t="n">
-        <v>7485286</v>
+        <v>7485564</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14534,22 +14518,26 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr"/>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126899896</v>
+        <v>126882460</v>
       </c>
       <c r="B139" t="n">
-        <v>80112</v>
+        <v>56849</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14557,37 +14545,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>856908</v>
+        <v>856765</v>
       </c>
       <c r="R139" t="n">
-        <v>7485414</v>
+        <v>7485445</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14614,9 +14607,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14631,12 +14634,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Suvi Sivula</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -14647,10 +14650,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126899899</v>
+        <v>126883898</v>
       </c>
       <c r="B140" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14677,7 +14680,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -14685,7 +14688,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -14694,13 +14701,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>856845</v>
+        <v>856979</v>
       </c>
       <c r="R140" t="n">
-        <v>7485518</v>
+        <v>7485287</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14727,9 +14734,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14745,12 +14762,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Suvi Sivula</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -14761,10 +14778,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126895794</v>
+        <v>126895795</v>
       </c>
       <c r="B141" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14790,16 +14807,20 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Ritaiaki, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>856934</v>
+        <v>856787</v>
       </c>
       <c r="R141" t="n">
-        <v>7485392</v>
+        <v>7485429</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14840,6 +14861,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14851,53 +14873,48 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
-        </is>
-      </c>
-      <c r="AY141" t="inlineStr"/>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126899817</v>
+        <v>126895801</v>
       </c>
       <c r="B142" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -14905,10 +14922,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>856875</v>
+        <v>856696</v>
       </c>
       <c r="R142" t="n">
-        <v>7485584</v>
+        <v>7485502</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14956,12 +14973,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Suvi Sivula</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -14972,10 +14989,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126895796</v>
+        <v>127272114</v>
       </c>
       <c r="B143" t="n">
-        <v>97239</v>
+        <v>80143</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14983,37 +15000,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Ritaiaki, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>856693</v>
+        <v>856765</v>
       </c>
       <c r="R143" t="n">
-        <v>7485505</v>
+        <v>7485445</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15040,9 +15057,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15062,53 +15089,48 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr"/>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126899820</v>
+        <v>126895799</v>
       </c>
       <c r="B144" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
@@ -15116,10 +15138,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>856838</v>
+        <v>857189</v>
       </c>
       <c r="R144" t="n">
-        <v>7485421</v>
+        <v>7485286</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15167,12 +15189,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Suvi Sivula</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15183,45 +15205,50 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126899902</v>
+        <v>127150856</v>
       </c>
       <c r="B145" t="n">
-        <v>91819</v>
+        <v>56849</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>760</v>
+        <v>100138</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>856867</v>
+        <v>857037</v>
       </c>
       <c r="R145" t="n">
-        <v>7485409</v>
+        <v>7485288</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15251,9 +15278,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15268,12 +15305,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Suvi Sivula</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15284,60 +15321,67 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126899819</v>
+        <v>127155655</v>
       </c>
       <c r="B146" t="n">
-        <v>98361</v>
+        <v>41361</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>215713</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>856846</v>
+        <v>856901</v>
       </c>
       <c r="R146" t="n">
-        <v>7485645</v>
+        <v>7485387</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15364,79 +15408,88 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Suvi Sivula</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126899901</v>
+        <v>126895794</v>
       </c>
       <c r="B147" t="n">
-        <v>78980</v>
+        <v>97314</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>856929</v>
+        <v>856934</v>
       </c>
       <c r="R147" t="n">
-        <v>7485563</v>
+        <v>7485392</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15477,18 +15530,19 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Suvi Sivula</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15499,32 +15553,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126899895</v>
+        <v>126883438</v>
       </c>
       <c r="B148" t="n">
-        <v>75075</v>
+        <v>98436</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15534,13 +15588,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>856927</v>
+        <v>856901</v>
       </c>
       <c r="R148" t="n">
-        <v>7485564</v>
+        <v>7485387</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15567,9 +15621,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15584,64 +15648,69 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Suvi Sivula</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126895800</v>
+        <v>126882171</v>
       </c>
       <c r="B149" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Ritaiaki, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>856984</v>
+        <v>856765</v>
       </c>
       <c r="R149" t="n">
-        <v>7485301</v>
+        <v>7485445</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15668,9 +15737,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15690,17 +15769,21 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr"/>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126882460</v>
+        <v>126895796</v>
       </c>
       <c r="B150" t="n">
-        <v>56849</v>
+        <v>97314</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15708,42 +15791,41 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>856765</v>
+        <v>856693</v>
       </c>
       <c r="R150" t="n">
-        <v>7485445</v>
+        <v>7485505</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15770,27 +15852,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15805,14 +15878,18 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY150" t="inlineStr"/>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127150856</v>
+        <v>126883505</v>
       </c>
       <c r="B151" t="n">
-        <v>56849</v>
+        <v>91284</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15820,42 +15897,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R151" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15884,7 +15956,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -15894,7 +15966,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15905,6 +15977,26 @@
       </c>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -15921,67 +16013,52 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127155655</v>
+        <v>126895798</v>
       </c>
       <c r="B152" t="n">
-        <v>41361</v>
+        <v>97320</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>215713</v>
+        <v>221941</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R152" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16008,27 +16085,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16043,14 +16111,18 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY152" t="inlineStr"/>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126895798</v>
+        <v>127272276</v>
       </c>
       <c r="B153" t="n">
-        <v>97245</v>
+        <v>80080</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16058,21 +16130,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221941</v>
+        <v>229748</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16082,13 +16154,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>857037</v>
+        <v>856765</v>
       </c>
       <c r="R153" t="n">
-        <v>7485288</v>
+        <v>7485445</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16115,9 +16187,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16137,10 +16219,230 @@
       </c>
       <c r="AX153" t="inlineStr">
         <is>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>126895800</v>
+      </c>
+      <c r="B154" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>856984</v>
+      </c>
+      <c r="R154" t="n">
+        <v>7485301</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
           <t>Suvi Sivula</t>
         </is>
       </c>
-      <c r="AY153" t="inlineStr"/>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>126882331</v>
+      </c>
+      <c r="B155" t="n">
+        <v>80142</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>856765</v>
+      </c>
+      <c r="R155" t="n">
+        <v>7485445</v>
+      </c>
+      <c r="S155" t="n">
+        <v>25</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>126722664</v>
       </c>
       <c r="B3" t="n">
-        <v>105456</v>
+        <v>105462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126722149</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>126722342</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>126722592</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>126722905</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>126728180</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>126722949</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>126722514</v>
       </c>
       <c r="B10" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>126722689</v>
       </c>
       <c r="B11" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>126728177</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>126722224</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>126728181</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>126722469</v>
       </c>
       <c r="B15" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>126728179</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>126722237</v>
       </c>
       <c r="B17" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>126722544</v>
       </c>
       <c r="B18" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>126722838</v>
       </c>
       <c r="B19" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>126722552</v>
       </c>
       <c r="B20" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>126722312</v>
       </c>
       <c r="B21" t="n">
-        <v>91269</v>
+        <v>91275</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>126722784</v>
       </c>
       <c r="B22" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>126728174</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>126728176</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>126722975</v>
       </c>
       <c r="B25" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>126722205</v>
       </c>
       <c r="B26" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>126728182</v>
       </c>
       <c r="B27" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>126728178</v>
       </c>
       <c r="B28" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3359,32 +3359,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126722914</v>
+        <v>126722768</v>
       </c>
       <c r="B29" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>857004</v>
+        <v>857037</v>
       </c>
       <c r="R29" t="n">
-        <v>7485695</v>
+        <v>7485717</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3456,32 +3456,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126722768</v>
+        <v>126722914</v>
       </c>
       <c r="B30" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>857037</v>
+        <v>857004</v>
       </c>
       <c r="R30" t="n">
-        <v>7485717</v>
+        <v>7485695</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126893335</v>
+        <v>126889016</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>857254</v>
+        <v>857042</v>
       </c>
       <c r="R31" t="n">
-        <v>7485706</v>
+        <v>7485656</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3638,12 +3638,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889016</v>
+        <v>126893321</v>
       </c>
       <c r="B32" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3689,13 +3689,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>857042</v>
+        <v>857154</v>
       </c>
       <c r="R32" t="n">
-        <v>7485656</v>
+        <v>7485805</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3739,12 +3739,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3755,10 +3755,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126893321</v>
+        <v>126895913</v>
       </c>
       <c r="B33" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>857154</v>
+        <v>857071</v>
       </c>
       <c r="R33" t="n">
-        <v>7485805</v>
+        <v>7485419</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3840,12 +3840,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3856,32 +3856,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126895913</v>
+        <v>126893335</v>
       </c>
       <c r="B34" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857071</v>
+        <v>857254</v>
       </c>
       <c r="R34" t="n">
-        <v>7485419</v>
+        <v>7485706</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3941,12 +3941,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -3960,7 +3960,7 @@
         <v>126894596</v>
       </c>
       <c r="B35" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4058,10 +4058,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126894580</v>
+        <v>126893328</v>
       </c>
       <c r="B36" t="n">
-        <v>80143</v>
+        <v>80153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4069,37 +4069,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>857065</v>
+        <v>856959</v>
       </c>
       <c r="R36" t="n">
-        <v>7485568</v>
+        <v>7485620</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4143,12 +4143,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4159,10 +4159,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126893328</v>
+        <v>126894580</v>
       </c>
       <c r="B37" t="n">
-        <v>80150</v>
+        <v>80146</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4170,37 +4170,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>856959</v>
+        <v>857065</v>
       </c>
       <c r="R37" t="n">
-        <v>7485620</v>
+        <v>7485568</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4244,12 +4244,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4260,10 +4260,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126893330</v>
+        <v>126895971</v>
       </c>
       <c r="B38" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4291,17 +4291,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>857082</v>
+        <v>856836</v>
       </c>
       <c r="R38" t="n">
-        <v>7485465</v>
+        <v>7485559</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4345,26 +4345,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126895971</v>
+        <v>126893330</v>
       </c>
       <c r="B39" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4392,17 +4388,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>856836</v>
+        <v>857082</v>
       </c>
       <c r="R39" t="n">
-        <v>7485559</v>
+        <v>7485465</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4446,22 +4442,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>126894589</v>
       </c>
       <c r="B40" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>126889022</v>
       </c>
       <c r="B41" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4660,10 +4660,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126894594</v>
+        <v>126895969</v>
       </c>
       <c r="B42" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,17 +4691,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>857257</v>
+        <v>856881</v>
       </c>
       <c r="R42" t="n">
-        <v>7485627</v>
+        <v>7485580</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4731,6 +4731,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Blommande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4745,26 +4750,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>126889042</v>
       </c>
       <c r="B43" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4862,10 +4863,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126894588</v>
+        <v>126894594</v>
       </c>
       <c r="B44" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4897,10 +4898,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>857238</v>
+        <v>857257</v>
       </c>
       <c r="R44" t="n">
-        <v>7485785</v>
+        <v>7485627</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4963,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126895969</v>
+        <v>126894588</v>
       </c>
       <c r="B45" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4994,17 +4995,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>856881</v>
+        <v>857238</v>
       </c>
       <c r="R45" t="n">
-        <v>7485580</v>
+        <v>7485785</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5034,11 +5035,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Blommande</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,22 +5049,26 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>126893332</v>
       </c>
       <c r="B46" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>126894582</v>
       </c>
       <c r="B47" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5272,32 +5272,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126895968</v>
+        <v>126895963</v>
       </c>
       <c r="B48" t="n">
-        <v>98436</v>
+        <v>98463</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>856872</v>
+        <v>856930</v>
       </c>
       <c r="R48" t="n">
-        <v>7485620</v>
+        <v>7485560</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Flera blommande ex</t>
+          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5374,10 +5374,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126889044</v>
+        <v>126888930</v>
       </c>
       <c r="B49" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>857220</v>
+        <v>856694</v>
       </c>
       <c r="R49" t="n">
-        <v>7485601</v>
+        <v>7485592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5459,12 +5459,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5475,10 +5475,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126895916</v>
+        <v>126895968</v>
       </c>
       <c r="B50" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5506,17 +5506,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>857225</v>
+        <v>856872</v>
       </c>
       <c r="R50" t="n">
-        <v>7485668</v>
+        <v>7485620</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5546,6 +5546,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Flera blommande ex</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5560,26 +5565,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126888930</v>
+        <v>126888927</v>
       </c>
       <c r="B51" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5611,10 +5612,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>856694</v>
+        <v>856896</v>
       </c>
       <c r="R51" t="n">
-        <v>7485592</v>
+        <v>7485538</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5677,10 +5678,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126888927</v>
+        <v>126895916</v>
       </c>
       <c r="B52" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5712,13 +5713,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>856896</v>
+        <v>857225</v>
       </c>
       <c r="R52" t="n">
-        <v>7485538</v>
+        <v>7485668</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5762,12 +5763,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5778,48 +5779,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126895963</v>
+        <v>126889044</v>
       </c>
       <c r="B53" t="n">
-        <v>98457</v>
+        <v>98442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>856930</v>
+        <v>857220</v>
       </c>
       <c r="R53" t="n">
-        <v>7485560</v>
+        <v>7485601</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5849,11 +5850,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5868,44 +5864,48 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893336</v>
+        <v>126888926</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>80153</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>857022</v>
+        <v>856904</v>
       </c>
       <c r="R54" t="n">
-        <v>7485521</v>
+        <v>7485446</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5965,12 +5965,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -5981,32 +5981,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126888926</v>
+        <v>126893336</v>
       </c>
       <c r="B55" t="n">
-        <v>80150</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,13 +6016,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>856904</v>
+        <v>857022</v>
       </c>
       <c r="R55" t="n">
-        <v>7485446</v>
+        <v>7485521</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6066,12 +6066,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6191,7 +6191,7 @@
         <v>126895972</v>
       </c>
       <c r="B57" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6285,10 +6285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126893319</v>
+        <v>126889052</v>
       </c>
       <c r="B58" t="n">
-        <v>91494</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6296,21 +6296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6320,13 +6320,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>857122</v>
+        <v>857206</v>
       </c>
       <c r="R58" t="n">
-        <v>7485443</v>
+        <v>7485553</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6370,12 +6370,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6386,32 +6386,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126889052</v>
+        <v>126888928</v>
       </c>
       <c r="B59" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>857206</v>
+        <v>856845</v>
       </c>
       <c r="R59" t="n">
-        <v>7485553</v>
+        <v>7485513</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6471,12 +6471,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6490,7 +6490,7 @@
         <v>126889013</v>
       </c>
       <c r="B60" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>126894581</v>
       </c>
       <c r="B61" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6689,32 +6689,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126888928</v>
+        <v>126893319</v>
       </c>
       <c r="B62" t="n">
-        <v>98436</v>
+        <v>91500</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6724,13 +6724,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>856845</v>
+        <v>857122</v>
       </c>
       <c r="R62" t="n">
-        <v>7485513</v>
+        <v>7485443</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6774,12 +6774,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6790,48 +6790,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126895915</v>
+        <v>126895961</v>
       </c>
       <c r="B63" t="n">
-        <v>98436</v>
+        <v>75138</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>857242</v>
+        <v>856840</v>
       </c>
       <c r="R63" t="n">
-        <v>7485724</v>
+        <v>7485479</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6875,48 +6875,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126889041</v>
+        <v>126895921</v>
       </c>
       <c r="B64" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6926,13 +6922,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>856978</v>
+        <v>857123</v>
       </c>
       <c r="R64" t="n">
-        <v>7485792</v>
+        <v>7485402</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6976,12 +6972,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -6992,32 +6988,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126895921</v>
+        <v>126889041</v>
       </c>
       <c r="B65" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7027,13 +7023,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>857123</v>
+        <v>856978</v>
       </c>
       <c r="R65" t="n">
-        <v>7485402</v>
+        <v>7485792</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7077,12 +7073,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7093,48 +7089,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126895961</v>
+        <v>126895915</v>
       </c>
       <c r="B66" t="n">
-        <v>75135</v>
+        <v>98442</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>856840</v>
+        <v>857242</v>
       </c>
       <c r="R66" t="n">
-        <v>7485479</v>
+        <v>7485724</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7178,22 +7174,26 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>126894583</v>
       </c>
       <c r="B67" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>126889032</v>
       </c>
       <c r="B68" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7392,32 +7392,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126889045</v>
+        <v>126895920</v>
       </c>
       <c r="B69" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7427,13 +7427,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>857084</v>
+        <v>857173</v>
       </c>
       <c r="R69" t="n">
-        <v>7485530</v>
+        <v>7485506</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7477,12 +7477,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7493,32 +7493,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126889047</v>
+        <v>126895922</v>
       </c>
       <c r="B70" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>857010</v>
+        <v>856981</v>
       </c>
       <c r="R70" t="n">
-        <v>7485585</v>
+        <v>7485578</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7578,12 +7578,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7594,32 +7594,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126889029</v>
+        <v>126889045</v>
       </c>
       <c r="B71" t="n">
-        <v>98457</v>
+        <v>98442</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>857083</v>
+        <v>857084</v>
       </c>
       <c r="R71" t="n">
-        <v>7485527</v>
+        <v>7485530</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7695,32 +7695,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126895910</v>
+        <v>126889047</v>
       </c>
       <c r="B72" t="n">
-        <v>80143</v>
+        <v>98442</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7730,13 +7730,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>856984</v>
+        <v>857010</v>
       </c>
       <c r="R72" t="n">
-        <v>7485600</v>
+        <v>7485585</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7780,12 +7780,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7796,10 +7796,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126889021</v>
+        <v>126889029</v>
       </c>
       <c r="B73" t="n">
-        <v>80143</v>
+        <v>98463</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7807,21 +7807,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>857000</v>
+        <v>857083</v>
       </c>
       <c r="R73" t="n">
-        <v>7485629</v>
+        <v>7485527</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7897,10 +7897,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126889024</v>
+        <v>126895910</v>
       </c>
       <c r="B74" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7932,13 +7932,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>856962</v>
+        <v>856984</v>
       </c>
       <c r="R74" t="n">
-        <v>7485641</v>
+        <v>7485600</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7982,12 +7982,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -7998,32 +7998,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126895920</v>
+        <v>126889021</v>
       </c>
       <c r="B75" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8033,13 +8033,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>857173</v>
+        <v>857000</v>
       </c>
       <c r="R75" t="n">
-        <v>7485506</v>
+        <v>7485629</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8083,12 +8083,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8099,32 +8099,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126895922</v>
+        <v>126889024</v>
       </c>
       <c r="B76" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8134,13 +8134,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>856981</v>
+        <v>856962</v>
       </c>
       <c r="R76" t="n">
-        <v>7485578</v>
+        <v>7485641</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8184,12 +8184,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8203,7 +8203,7 @@
         <v>126894584</v>
       </c>
       <c r="B77" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>126889039</v>
       </c>
       <c r="B78" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>126894602</v>
       </c>
       <c r="B79" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8503,32 +8503,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126895912</v>
+        <v>126895918</v>
       </c>
       <c r="B80" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>857018</v>
+        <v>857150</v>
       </c>
       <c r="R80" t="n">
-        <v>7485408</v>
+        <v>7485418</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -8604,32 +8604,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126895918</v>
+        <v>126895912</v>
       </c>
       <c r="B81" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>857150</v>
+        <v>857018</v>
       </c>
       <c r="R81" t="n">
-        <v>7485418</v>
+        <v>7485408</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -8708,7 +8708,7 @@
         <v>126888931</v>
       </c>
       <c r="B82" t="n">
-        <v>91893</v>
+        <v>91899</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8806,45 +8806,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126894590</v>
+        <v>126889019</v>
       </c>
       <c r="B83" t="n">
-        <v>98436</v>
+        <v>80146</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>857265</v>
+        <v>857016</v>
       </c>
       <c r="R83" t="n">
-        <v>7485680</v>
+        <v>7485635</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8891,12 +8891,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8910,7 +8910,7 @@
         <v>126893339</v>
       </c>
       <c r="B84" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>126894601</v>
       </c>
       <c r="B85" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9109,32 +9109,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126889019</v>
+        <v>126888929</v>
       </c>
       <c r="B86" t="n">
-        <v>80143</v>
+        <v>98442</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>857016</v>
+        <v>856800</v>
       </c>
       <c r="R86" t="n">
-        <v>7485635</v>
+        <v>7485540</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9194,12 +9194,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9210,10 +9210,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126888929</v>
+        <v>126894590</v>
       </c>
       <c r="B87" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9241,14 +9241,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>856800</v>
+        <v>857265</v>
       </c>
       <c r="R87" t="n">
-        <v>7485540</v>
+        <v>7485680</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9295,12 +9295,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9311,32 +9311,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126895917</v>
+        <v>126889017</v>
       </c>
       <c r="B88" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>857220</v>
+        <v>857021</v>
       </c>
       <c r="R88" t="n">
-        <v>7485407</v>
+        <v>7485648</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9396,12 +9396,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9412,32 +9412,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126889017</v>
+        <v>126895917</v>
       </c>
       <c r="B89" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9447,13 +9447,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>857021</v>
+        <v>857220</v>
       </c>
       <c r="R89" t="n">
-        <v>7485648</v>
+        <v>7485407</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9497,12 +9497,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9516,7 +9516,7 @@
         <v>126889034</v>
       </c>
       <c r="B90" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>126895973</v>
       </c>
       <c r="B91" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>126895962</v>
       </c>
       <c r="B92" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9808,10 +9808,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126893327</v>
+        <v>126889025</v>
       </c>
       <c r="B93" t="n">
-        <v>91303</v>
+        <v>80146</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9819,21 +9819,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4660</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9843,13 +9843,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>857141</v>
+        <v>856955</v>
       </c>
       <c r="R93" t="n">
-        <v>7485413</v>
+        <v>7485682</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9893,12 +9893,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -9909,10 +9909,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126889025</v>
+        <v>126893327</v>
       </c>
       <c r="B94" t="n">
-        <v>80143</v>
+        <v>91309</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9920,21 +9920,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>4660</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9944,13 +9944,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>856955</v>
+        <v>857141</v>
       </c>
       <c r="R94" t="n">
-        <v>7485682</v>
+        <v>7485413</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9994,12 +9994,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10010,32 +10010,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126889050</v>
+        <v>126893333</v>
       </c>
       <c r="B95" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10045,13 +10045,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>857208</v>
+        <v>856968</v>
       </c>
       <c r="R95" t="n">
-        <v>7485545</v>
+        <v>7485570</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10095,12 +10095,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10114,7 +10114,7 @@
         <v>126893323</v>
       </c>
       <c r="B96" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>126893325</v>
       </c>
       <c r="B97" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>126895914</v>
       </c>
       <c r="B98" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10414,32 +10414,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126893333</v>
+        <v>126889050</v>
       </c>
       <c r="B99" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10449,13 +10449,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>856968</v>
+        <v>857208</v>
       </c>
       <c r="R99" t="n">
-        <v>7485570</v>
+        <v>7485545</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10499,12 +10499,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10515,10 +10515,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126894595</v>
+        <v>126889049</v>
       </c>
       <c r="B100" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10546,14 +10546,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>857231</v>
+        <v>857013</v>
       </c>
       <c r="R100" t="n">
-        <v>7485574</v>
+        <v>7485581</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10600,12 +10600,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10616,10 +10616,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126889049</v>
+        <v>126894595</v>
       </c>
       <c r="B101" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10647,14 +10647,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>857013</v>
+        <v>857231</v>
       </c>
       <c r="R101" t="n">
-        <v>7485581</v>
+        <v>7485574</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10701,12 +10701,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10720,7 +10720,7 @@
         <v>126895967</v>
       </c>
       <c r="B102" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>126895911</v>
       </c>
       <c r="B103" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>126889036</v>
       </c>
       <c r="B104" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>126889037</v>
       </c>
       <c r="B105" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11122,32 +11122,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126893322</v>
+        <v>126893338</v>
       </c>
       <c r="B106" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11157,10 +11157,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>857015</v>
+        <v>856954</v>
       </c>
       <c r="R106" t="n">
-        <v>7485514</v>
+        <v>7485603</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11226,7 +11226,7 @@
         <v>126895966</v>
       </c>
       <c r="B107" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11324,32 +11324,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126893338</v>
+        <v>126893322</v>
       </c>
       <c r="B108" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11359,10 +11359,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>856954</v>
+        <v>857015</v>
       </c>
       <c r="R108" t="n">
-        <v>7485603</v>
+        <v>7485514</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11428,7 +11428,7 @@
         <v>126893324</v>
       </c>
       <c r="B109" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11526,48 +11526,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126895975</v>
+        <v>126893334</v>
       </c>
       <c r="B110" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>856864</v>
+        <v>856938</v>
       </c>
       <c r="R110" t="n">
-        <v>7485417</v>
+        <v>7485632</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11611,60 +11611,64 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126893334</v>
+        <v>126895975</v>
       </c>
       <c r="B111" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>856938</v>
+        <v>856864</v>
       </c>
       <c r="R111" t="n">
-        <v>7485632</v>
+        <v>7485417</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11708,48 +11712,44 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126893329</v>
+        <v>126893320</v>
       </c>
       <c r="B112" t="n">
-        <v>98436</v>
+        <v>80146</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11759,10 +11759,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>857202</v>
+        <v>857058</v>
       </c>
       <c r="R112" t="n">
-        <v>7485431</v>
+        <v>7485807</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11825,48 +11825,48 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126894585</v>
+        <v>126893329</v>
       </c>
       <c r="B113" t="n">
-        <v>97320</v>
+        <v>98442</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>857167</v>
+        <v>857202</v>
       </c>
       <c r="R113" t="n">
-        <v>7485432</v>
+        <v>7485431</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11910,12 +11910,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -11926,10 +11926,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126893320</v>
+        <v>126894585</v>
       </c>
       <c r="B114" t="n">
-        <v>80143</v>
+        <v>97326</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11937,37 +11937,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>857058</v>
+        <v>857167</v>
       </c>
       <c r="R114" t="n">
-        <v>7485807</v>
+        <v>7485432</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12011,12 +12011,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12027,48 +12027,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126895970</v>
+        <v>126889027</v>
       </c>
       <c r="B115" t="n">
-        <v>98436</v>
+        <v>80146</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>856849</v>
+        <v>856947</v>
       </c>
       <c r="R115" t="n">
-        <v>7485559</v>
+        <v>7485678</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12112,60 +12112,64 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126894592</v>
+        <v>126895965</v>
       </c>
       <c r="B116" t="n">
-        <v>98436</v>
+        <v>80153</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>857255</v>
+        <v>856897</v>
       </c>
       <c r="R116" t="n">
-        <v>7485644</v>
+        <v>7485429</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12209,26 +12213,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126894600</v>
+        <v>126894597</v>
       </c>
       <c r="B117" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12260,10 +12260,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>857163</v>
+        <v>857222</v>
       </c>
       <c r="R117" t="n">
-        <v>7485497</v>
+        <v>7485544</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12326,10 +12326,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126894597</v>
+        <v>126894600</v>
       </c>
       <c r="B118" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>857222</v>
+        <v>857163</v>
       </c>
       <c r="R118" t="n">
-        <v>7485544</v>
+        <v>7485497</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12427,45 +12427,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126889027</v>
+        <v>126894592</v>
       </c>
       <c r="B119" t="n">
-        <v>80143</v>
+        <v>98442</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>856947</v>
+        <v>857255</v>
       </c>
       <c r="R119" t="n">
-        <v>7485678</v>
+        <v>7485644</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12512,12 +12512,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12528,32 +12528,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126895965</v>
+        <v>126895970</v>
       </c>
       <c r="B120" t="n">
-        <v>80150</v>
+        <v>98442</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12563,10 +12563,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>856897</v>
+        <v>856849</v>
       </c>
       <c r="R120" t="n">
-        <v>7485429</v>
+        <v>7485559</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12628,7 +12628,7 @@
         <v>126889014</v>
       </c>
       <c r="B121" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>126889030</v>
       </c>
       <c r="B122" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12827,10 +12827,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126899900</v>
+        <v>126899898</v>
       </c>
       <c r="B123" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12857,12 +12857,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -12874,10 +12874,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>856926</v>
+        <v>856878</v>
       </c>
       <c r="R123" t="n">
-        <v>7485578</v>
+        <v>7485406</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12941,10 +12941,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126899898</v>
+        <v>126899900</v>
       </c>
       <c r="B124" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12971,12 +12971,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>856878</v>
+        <v>856926</v>
       </c>
       <c r="R124" t="n">
-        <v>7485406</v>
+        <v>7485578</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13058,7 +13058,7 @@
         <v>126899894</v>
       </c>
       <c r="B125" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>126899816</v>
       </c>
       <c r="B126" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>126899814</v>
       </c>
       <c r="B127" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>126899815</v>
       </c>
       <c r="B128" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>126899897</v>
       </c>
       <c r="B129" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13560,57 +13560,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126899818</v>
+        <v>126899896</v>
       </c>
       <c r="B130" t="n">
-        <v>98436</v>
+        <v>80146</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>856921</v>
+        <v>856908</v>
       </c>
       <c r="R130" t="n">
-        <v>7485611</v>
+        <v>7485414</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13651,7 +13639,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13663,7 +13650,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13674,45 +13661,57 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126899896</v>
+        <v>126899818</v>
       </c>
       <c r="B131" t="n">
-        <v>80143</v>
+        <v>98442</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>856908</v>
+        <v>856921</v>
       </c>
       <c r="R131" t="n">
-        <v>7485414</v>
+        <v>7485611</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13753,6 +13752,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -13778,7 +13778,7 @@
         <v>126899899</v>
       </c>
       <c r="B132" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>126899817</v>
       </c>
       <c r="B133" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>126899820</v>
       </c>
       <c r="B134" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>126899902</v>
       </c>
       <c r="B135" t="n">
-        <v>91893</v>
+        <v>91899</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14218,57 +14218,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126899819</v>
+        <v>126899901</v>
       </c>
       <c r="B136" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>856846</v>
+        <v>856929</v>
       </c>
       <c r="R136" t="n">
-        <v>7485645</v>
+        <v>7485563</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14309,7 +14297,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14321,7 +14308,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14332,45 +14319,57 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126899901</v>
+        <v>126899819</v>
       </c>
       <c r="B137" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>856929</v>
+        <v>856846</v>
       </c>
       <c r="R137" t="n">
-        <v>7485563</v>
+        <v>7485645</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14411,6 +14410,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14436,7 +14436,7 @@
         <v>126899895</v>
       </c>
       <c r="B138" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>126883898</v>
       </c>
       <c r="B140" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>126895795</v>
       </c>
       <c r="B141" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>126895801</v>
       </c>
       <c r="B142" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>127272114</v>
       </c>
       <c r="B143" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>126895799</v>
       </c>
       <c r="B144" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15450,7 +15450,7 @@
         <v>126895794</v>
       </c>
       <c r="B147" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>126883438</v>
       </c>
       <c r="B148" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>126882171</v>
       </c>
       <c r="B149" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>126895796</v>
       </c>
       <c r="B150" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>126883505</v>
       </c>
       <c r="B151" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>126895798</v>
       </c>
       <c r="B152" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16119,48 +16119,51 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127272276</v>
+        <v>126895800</v>
       </c>
       <c r="B153" t="n">
-        <v>80080</v>
+        <v>79014</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>856765</v>
+        <v>856984</v>
       </c>
       <c r="R153" t="n">
-        <v>7485445</v>
+        <v>7485301</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16187,27 +16190,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16230,51 +16224,48 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126895800</v>
+        <v>127272276</v>
       </c>
       <c r="B154" t="n">
-        <v>79011</v>
+        <v>80083</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>856984</v>
+        <v>856765</v>
       </c>
       <c r="R154" t="n">
-        <v>7485301</v>
+        <v>7485445</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16301,18 +16292,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -16338,7 +16338,7 @@
         <v>126882331</v>
       </c>
       <c r="B155" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -1392,32 +1392,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126722949</v>
+        <v>126722514</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>857001</v>
+        <v>857040</v>
       </c>
       <c r="R9" t="n">
-        <v>7485674</v>
+        <v>7485799</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,32 +1489,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126722514</v>
+        <v>126722949</v>
       </c>
       <c r="B10" t="n">
-        <v>98463</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>857040</v>
+        <v>857001</v>
       </c>
       <c r="R10" t="n">
-        <v>7485799</v>
+        <v>7485674</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1877,32 +1877,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126728181</v>
+        <v>126728179</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>857024</v>
+        <v>857020</v>
       </c>
       <c r="R14" t="n">
-        <v>7485613</v>
+        <v>7485779</v>
       </c>
       <c r="S14" t="n">
         <v>14</v>
@@ -1974,45 +1974,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126722469</v>
+        <v>126722237</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>857037</v>
+        <v>856991</v>
       </c>
       <c r="R15" t="n">
-        <v>7485805</v>
+        <v>7485798</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,32 +2080,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126728179</v>
+        <v>126728181</v>
       </c>
       <c r="B16" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>857020</v>
+        <v>857024</v>
       </c>
       <c r="R16" t="n">
-        <v>7485779</v>
+        <v>7485613</v>
       </c>
       <c r="S16" t="n">
         <v>14</v>
@@ -2168,54 +2177,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126722237</v>
+        <v>126722469</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>856991</v>
+        <v>857037</v>
       </c>
       <c r="R17" t="n">
-        <v>7485798</v>
+        <v>7485805</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,54 +2371,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126722838</v>
+        <v>126722312</v>
       </c>
       <c r="B19" t="n">
-        <v>98442</v>
+        <v>91275</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>857027</v>
+        <v>857016</v>
       </c>
       <c r="R19" t="n">
-        <v>7485680</v>
+        <v>7485810</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2477,7 +2468,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126722552</v>
+        <v>126722838</v>
       </c>
       <c r="B20" t="n">
         <v>98442</v>
@@ -2505,17 +2496,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>857113</v>
+        <v>857027</v>
       </c>
       <c r="R20" t="n">
-        <v>7485787</v>
+        <v>7485680</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2574,32 +2574,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126722312</v>
+        <v>126722552</v>
       </c>
       <c r="B21" t="n">
-        <v>91275</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>857016</v>
+        <v>857113</v>
       </c>
       <c r="R21" t="n">
-        <v>7485810</v>
+        <v>7485787</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3165,32 +3165,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126728182</v>
+        <v>126728178</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>856962</v>
+        <v>857082</v>
       </c>
       <c r="R27" t="n">
-        <v>7485783</v>
+        <v>7485755</v>
       </c>
       <c r="S27" t="n">
         <v>14</v>
@@ -3262,32 +3262,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126728178</v>
+        <v>126728182</v>
       </c>
       <c r="B28" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>857082</v>
+        <v>856962</v>
       </c>
       <c r="R28" t="n">
-        <v>7485755</v>
+        <v>7485783</v>
       </c>
       <c r="S28" t="n">
         <v>14</v>
@@ -3856,48 +3856,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126893335</v>
+        <v>126894596</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857254</v>
+        <v>857232</v>
       </c>
       <c r="R34" t="n">
-        <v>7485706</v>
+        <v>7485521</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3941,12 +3941,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -3957,48 +3957,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126894596</v>
+        <v>126893335</v>
       </c>
       <c r="B35" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>857232</v>
+        <v>857254</v>
       </c>
       <c r="R35" t="n">
-        <v>7485521</v>
+        <v>7485706</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4058,32 +4058,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126893328</v>
+        <v>126893330</v>
       </c>
       <c r="B36" t="n">
-        <v>80153</v>
+        <v>98442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>856959</v>
+        <v>857082</v>
       </c>
       <c r="R36" t="n">
-        <v>7485620</v>
+        <v>7485465</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4159,32 +4159,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126894580</v>
+        <v>126894589</v>
       </c>
       <c r="B37" t="n">
-        <v>80146</v>
+        <v>98442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>857065</v>
+        <v>857303</v>
       </c>
       <c r="R37" t="n">
-        <v>7485568</v>
+        <v>7485733</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4260,48 +4260,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126895971</v>
+        <v>126893328</v>
       </c>
       <c r="B38" t="n">
-        <v>98442</v>
+        <v>80153</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>856836</v>
+        <v>856959</v>
       </c>
       <c r="R38" t="n">
-        <v>7485559</v>
+        <v>7485620</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4345,60 +4345,64 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126893330</v>
+        <v>126894580</v>
       </c>
       <c r="B39" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>857082</v>
+        <v>857065</v>
       </c>
       <c r="R39" t="n">
-        <v>7485465</v>
+        <v>7485568</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4442,12 +4446,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4458,7 +4462,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126894589</v>
+        <v>126895971</v>
       </c>
       <c r="B40" t="n">
         <v>98442</v>
@@ -4489,17 +4493,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>857303</v>
+        <v>856836</v>
       </c>
       <c r="R40" t="n">
-        <v>7485733</v>
+        <v>7485559</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4543,61 +4547,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126889022</v>
+        <v>126894594</v>
       </c>
       <c r="B41" t="n">
-        <v>80146</v>
+        <v>98442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>856972</v>
+        <v>857257</v>
       </c>
       <c r="R41" t="n">
-        <v>7485632</v>
+        <v>7485627</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4644,12 +4644,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4660,7 +4660,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126895969</v>
+        <v>126889042</v>
       </c>
       <c r="B42" t="n">
         <v>98442</v>
@@ -4691,17 +4691,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>856881</v>
+        <v>857162</v>
       </c>
       <c r="R42" t="n">
-        <v>7485580</v>
+        <v>7485708</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4731,11 +4731,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Blommande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4750,19 +4745,23 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126889042</v>
+        <v>126894588</v>
       </c>
       <c r="B43" t="n">
         <v>98442</v>
@@ -4793,14 +4792,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>857162</v>
+        <v>857238</v>
       </c>
       <c r="R43" t="n">
-        <v>7485708</v>
+        <v>7485785</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4847,12 +4846,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4863,7 +4862,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126894594</v>
+        <v>126893332</v>
       </c>
       <c r="B44" t="n">
         <v>98442</v>
@@ -4894,17 +4893,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>857257</v>
+        <v>857047</v>
       </c>
       <c r="R44" t="n">
-        <v>7485627</v>
+        <v>7485515</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4948,12 +4947,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -4964,7 +4963,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126894588</v>
+        <v>126895969</v>
       </c>
       <c r="B45" t="n">
         <v>98442</v>
@@ -4995,17 +4994,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>857238</v>
+        <v>856881</v>
       </c>
       <c r="R45" t="n">
-        <v>7485785</v>
+        <v>7485580</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5035,6 +5034,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Blommande</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5049,48 +5053,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126893332</v>
+        <v>126889022</v>
       </c>
       <c r="B46" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5100,13 +5100,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>857047</v>
+        <v>856972</v>
       </c>
       <c r="R46" t="n">
-        <v>7485515</v>
+        <v>7485632</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5150,12 +5150,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5272,32 +5272,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126895963</v>
+        <v>126895968</v>
       </c>
       <c r="B48" t="n">
-        <v>98463</v>
+        <v>98442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>856930</v>
+        <v>856872</v>
       </c>
       <c r="R48" t="n">
-        <v>7485560</v>
+        <v>7485620</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
+          <t>Flera blommande ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5374,7 +5374,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126888930</v>
+        <v>126888927</v>
       </c>
       <c r="B49" t="n">
         <v>98442</v>
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>856694</v>
+        <v>856896</v>
       </c>
       <c r="R49" t="n">
-        <v>7485592</v>
+        <v>7485538</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126895968</v>
+        <v>126895916</v>
       </c>
       <c r="B50" t="n">
         <v>98442</v>
@@ -5506,17 +5506,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>856872</v>
+        <v>857225</v>
       </c>
       <c r="R50" t="n">
-        <v>7485620</v>
+        <v>7485668</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5546,11 +5546,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Flera blommande ex</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5565,19 +5560,23 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126888927</v>
+        <v>126889044</v>
       </c>
       <c r="B51" t="n">
         <v>98442</v>
@@ -5612,10 +5611,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>856896</v>
+        <v>857220</v>
       </c>
       <c r="R51" t="n">
-        <v>7485538</v>
+        <v>7485601</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5662,12 +5661,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5678,7 +5677,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126895916</v>
+        <v>126888930</v>
       </c>
       <c r="B52" t="n">
         <v>98442</v>
@@ -5713,13 +5712,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>857225</v>
+        <v>856694</v>
       </c>
       <c r="R52" t="n">
-        <v>7485668</v>
+        <v>7485592</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5763,12 +5762,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5779,48 +5778,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889044</v>
+        <v>126895963</v>
       </c>
       <c r="B53" t="n">
-        <v>98442</v>
+        <v>98463</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>857220</v>
+        <v>856930</v>
       </c>
       <c r="R53" t="n">
-        <v>7485601</v>
+        <v>7485560</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5850,6 +5849,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5864,19 +5868,15 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6285,10 +6285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126889052</v>
+        <v>126893319</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>91500</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6296,21 +6296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6320,13 +6320,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>857206</v>
+        <v>857122</v>
       </c>
       <c r="R58" t="n">
-        <v>7485553</v>
+        <v>7485443</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6370,12 +6370,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6386,32 +6386,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126888928</v>
+        <v>126889052</v>
       </c>
       <c r="B59" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>856845</v>
+        <v>857206</v>
       </c>
       <c r="R59" t="n">
-        <v>7485513</v>
+        <v>7485553</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6471,12 +6471,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6689,32 +6689,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126893319</v>
+        <v>126888928</v>
       </c>
       <c r="B62" t="n">
-        <v>91500</v>
+        <v>98442</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6724,13 +6724,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>857122</v>
+        <v>856845</v>
       </c>
       <c r="R62" t="n">
-        <v>7485443</v>
+        <v>7485513</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6774,12 +6774,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6887,32 +6887,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126895921</v>
+        <v>126889041</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6922,13 +6922,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>857123</v>
+        <v>856978</v>
       </c>
       <c r="R64" t="n">
-        <v>7485402</v>
+        <v>7485792</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6972,12 +6972,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -6988,7 +6988,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126889041</v>
+        <v>126895915</v>
       </c>
       <c r="B65" t="n">
         <v>98442</v>
@@ -7023,13 +7023,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>856978</v>
+        <v>857242</v>
       </c>
       <c r="R65" t="n">
-        <v>7485792</v>
+        <v>7485724</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7073,12 +7073,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7089,32 +7089,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126895915</v>
+        <v>126895921</v>
       </c>
       <c r="B66" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7124,10 +7124,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>857242</v>
+        <v>857123</v>
       </c>
       <c r="R66" t="n">
-        <v>7485724</v>
+        <v>7485402</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -7392,32 +7392,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126895920</v>
+        <v>126889045</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7427,13 +7427,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>857173</v>
+        <v>857084</v>
       </c>
       <c r="R69" t="n">
-        <v>7485506</v>
+        <v>7485530</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7477,12 +7477,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7493,32 +7493,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126895922</v>
+        <v>126889047</v>
       </c>
       <c r="B70" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>856981</v>
+        <v>857010</v>
       </c>
       <c r="R70" t="n">
-        <v>7485578</v>
+        <v>7485585</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7578,12 +7578,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7594,32 +7594,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126889045</v>
+        <v>126895920</v>
       </c>
       <c r="B71" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7629,13 +7629,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>857084</v>
+        <v>857173</v>
       </c>
       <c r="R71" t="n">
-        <v>7485530</v>
+        <v>7485506</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7679,12 +7679,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7695,32 +7695,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126889047</v>
+        <v>126895922</v>
       </c>
       <c r="B72" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7730,13 +7730,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>857010</v>
+        <v>856981</v>
       </c>
       <c r="R72" t="n">
-        <v>7485585</v>
+        <v>7485578</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7780,12 +7780,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7796,10 +7796,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126889029</v>
+        <v>126895910</v>
       </c>
       <c r="B73" t="n">
-        <v>98463</v>
+        <v>80146</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7807,21 +7807,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7831,13 +7831,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>857083</v>
+        <v>856984</v>
       </c>
       <c r="R73" t="n">
-        <v>7485527</v>
+        <v>7485600</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7881,12 +7881,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7897,7 +7897,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126895910</v>
+        <v>126889021</v>
       </c>
       <c r="B74" t="n">
         <v>80146</v>
@@ -7932,13 +7932,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>856984</v>
+        <v>857000</v>
       </c>
       <c r="R74" t="n">
-        <v>7485600</v>
+        <v>7485629</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7982,12 +7982,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -7998,7 +7998,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126889021</v>
+        <v>126889024</v>
       </c>
       <c r="B75" t="n">
         <v>80146</v>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>857000</v>
+        <v>856962</v>
       </c>
       <c r="R75" t="n">
-        <v>7485629</v>
+        <v>7485641</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8099,10 +8099,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126889024</v>
+        <v>126889029</v>
       </c>
       <c r="B76" t="n">
-        <v>80146</v>
+        <v>98463</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8110,21 +8110,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>856962</v>
+        <v>857083</v>
       </c>
       <c r="R76" t="n">
-        <v>7485641</v>
+        <v>7485527</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8200,32 +8200,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126894584</v>
+        <v>126894602</v>
       </c>
       <c r="B77" t="n">
-        <v>97326</v>
+        <v>79014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>857231</v>
+        <v>857075</v>
       </c>
       <c r="R77" t="n">
-        <v>7485574</v>
+        <v>7485539</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8301,7 +8301,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126889039</v>
+        <v>126894584</v>
       </c>
       <c r="B78" t="n">
         <v>97326</v>
@@ -8332,14 +8332,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>857184</v>
+        <v>857231</v>
       </c>
       <c r="R78" t="n">
-        <v>7485414</v>
+        <v>7485574</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8386,12 +8386,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8402,45 +8402,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126894602</v>
+        <v>126889039</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>97326</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>857075</v>
+        <v>857184</v>
       </c>
       <c r="R79" t="n">
-        <v>7485539</v>
+        <v>7485414</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8487,12 +8487,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8705,32 +8705,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126888931</v>
+        <v>126889019</v>
       </c>
       <c r="B82" t="n">
-        <v>91899</v>
+        <v>80146</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>856896</v>
+        <v>857016</v>
       </c>
       <c r="R82" t="n">
-        <v>7485431</v>
+        <v>7485635</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8790,12 +8790,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8806,32 +8806,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126889019</v>
+        <v>126888931</v>
       </c>
       <c r="B83" t="n">
-        <v>80146</v>
+        <v>91899</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>857016</v>
+        <v>856896</v>
       </c>
       <c r="R83" t="n">
-        <v>7485635</v>
+        <v>7485431</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8891,12 +8891,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9311,32 +9311,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126889017</v>
+        <v>126895917</v>
       </c>
       <c r="B88" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>857021</v>
+        <v>857220</v>
       </c>
       <c r="R88" t="n">
-        <v>7485648</v>
+        <v>7485407</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9396,12 +9396,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9412,32 +9412,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126895917</v>
+        <v>126889017</v>
       </c>
       <c r="B89" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9447,13 +9447,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>857220</v>
+        <v>857021</v>
       </c>
       <c r="R89" t="n">
-        <v>7485407</v>
+        <v>7485648</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9497,12 +9497,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9513,48 +9513,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126889034</v>
+        <v>126895973</v>
       </c>
       <c r="B90" t="n">
-        <v>98463</v>
+        <v>98442</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>856998</v>
+        <v>856707</v>
       </c>
       <c r="R90" t="n">
-        <v>7485630</v>
+        <v>7485577</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9598,64 +9598,60 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126895973</v>
+        <v>126889034</v>
       </c>
       <c r="B91" t="n">
-        <v>98442</v>
+        <v>98463</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>856707</v>
+        <v>856998</v>
       </c>
       <c r="R91" t="n">
-        <v>7485577</v>
+        <v>7485630</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9699,15 +9695,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9808,10 +9808,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126889025</v>
+        <v>126893327</v>
       </c>
       <c r="B93" t="n">
-        <v>80146</v>
+        <v>91309</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9819,21 +9819,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>4660</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9843,13 +9843,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>856955</v>
+        <v>857141</v>
       </c>
       <c r="R93" t="n">
-        <v>7485682</v>
+        <v>7485413</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9893,12 +9893,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -9909,10 +9909,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126893327</v>
+        <v>126889025</v>
       </c>
       <c r="B94" t="n">
-        <v>91309</v>
+        <v>80146</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9920,21 +9920,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4660</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9944,13 +9944,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>857141</v>
+        <v>856955</v>
       </c>
       <c r="R94" t="n">
-        <v>7485413</v>
+        <v>7485682</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9994,12 +9994,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10010,32 +10010,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126893333</v>
+        <v>126895914</v>
       </c>
       <c r="B95" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10045,13 +10045,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>856968</v>
+        <v>856958</v>
       </c>
       <c r="R95" t="n">
-        <v>7485570</v>
+        <v>7485679</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10095,12 +10095,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10111,32 +10111,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126893323</v>
+        <v>126889050</v>
       </c>
       <c r="B96" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>856995</v>
+        <v>857208</v>
       </c>
       <c r="R96" t="n">
-        <v>7485538</v>
+        <v>7485545</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10196,12 +10196,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10212,7 +10212,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126893325</v>
+        <v>126893323</v>
       </c>
       <c r="B97" t="n">
         <v>80146</v>
@@ -10247,10 +10247,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>856884</v>
+        <v>856995</v>
       </c>
       <c r="R97" t="n">
-        <v>7485698</v>
+        <v>7485538</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10313,7 +10313,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126895914</v>
+        <v>126893325</v>
       </c>
       <c r="B98" t="n">
         <v>80146</v>
@@ -10348,13 +10348,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>856958</v>
+        <v>856884</v>
       </c>
       <c r="R98" t="n">
-        <v>7485679</v>
+        <v>7485698</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10398,12 +10398,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10414,32 +10414,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126889050</v>
+        <v>126893333</v>
       </c>
       <c r="B99" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10449,13 +10449,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>857208</v>
+        <v>856968</v>
       </c>
       <c r="R99" t="n">
-        <v>7485545</v>
+        <v>7485570</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10499,12 +10499,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10515,32 +10515,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126889049</v>
+        <v>126895911</v>
       </c>
       <c r="B100" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>857013</v>
+        <v>856885</v>
       </c>
       <c r="R100" t="n">
-        <v>7485581</v>
+        <v>7485704</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10586,6 +10586,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10600,12 +10605,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10717,7 +10722,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126895967</v>
+        <v>126889049</v>
       </c>
       <c r="B102" t="n">
         <v>98442</v>
@@ -10748,17 +10753,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>856932</v>
+        <v>857013</v>
       </c>
       <c r="R102" t="n">
-        <v>7485559</v>
+        <v>7485581</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10802,60 +10807,64 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126895911</v>
+        <v>126895967</v>
       </c>
       <c r="B103" t="n">
-        <v>80146</v>
+        <v>98442</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>856885</v>
+        <v>856932</v>
       </c>
       <c r="R103" t="n">
-        <v>7485704</v>
+        <v>7485559</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10885,11 +10894,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10904,48 +10908,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126889036</v>
+        <v>126893338</v>
       </c>
       <c r="B104" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10955,13 +10955,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>857182</v>
+        <v>856954</v>
       </c>
       <c r="R104" t="n">
-        <v>7485442</v>
+        <v>7485603</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11005,12 +11005,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11021,7 +11021,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126889037</v>
+        <v>126889036</v>
       </c>
       <c r="B105" t="n">
         <v>80021</v>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>857094</v>
+        <v>857182</v>
       </c>
       <c r="R105" t="n">
-        <v>7485517</v>
+        <v>7485442</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11122,48 +11122,51 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126893338</v>
+        <v>126895966</v>
       </c>
       <c r="B106" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>856954</v>
+        <v>856849</v>
       </c>
       <c r="R106" t="n">
-        <v>7485603</v>
+        <v>7485405</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11201,32 +11204,29 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126895966</v>
+        <v>126893322</v>
       </c>
       <c r="B107" t="n">
-        <v>80153</v>
+        <v>80146</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11234,40 +11234,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>856849</v>
+        <v>857015</v>
       </c>
       <c r="R107" t="n">
-        <v>7485405</v>
+        <v>7485514</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11305,29 +11302,32 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126893322</v>
+        <v>126889037</v>
       </c>
       <c r="B108" t="n">
-        <v>80146</v>
+        <v>80021</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11359,13 +11359,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>857015</v>
+        <v>857094</v>
       </c>
       <c r="R108" t="n">
-        <v>7485514</v>
+        <v>7485517</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11409,12 +11409,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11425,48 +11425,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126893324</v>
+        <v>126895975</v>
       </c>
       <c r="B109" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>856949</v>
+        <v>856864</v>
       </c>
       <c r="R109" t="n">
-        <v>7485588</v>
+        <v>7485417</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11510,48 +11510,44 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126893334</v>
+        <v>126893324</v>
       </c>
       <c r="B110" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11561,10 +11557,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>856938</v>
+        <v>856949</v>
       </c>
       <c r="R110" t="n">
-        <v>7485632</v>
+        <v>7485588</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11627,48 +11623,48 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126895975</v>
+        <v>126893334</v>
       </c>
       <c r="B111" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>856864</v>
+        <v>856938</v>
       </c>
       <c r="R111" t="n">
-        <v>7485417</v>
+        <v>7485632</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11712,44 +11708,48 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126893320</v>
+        <v>126893329</v>
       </c>
       <c r="B112" t="n">
-        <v>80146</v>
+        <v>98442</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11759,10 +11759,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>857058</v>
+        <v>857202</v>
       </c>
       <c r="R112" t="n">
-        <v>7485807</v>
+        <v>7485431</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11825,32 +11825,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126893329</v>
+        <v>126893320</v>
       </c>
       <c r="B113" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>857202</v>
+        <v>857058</v>
       </c>
       <c r="R113" t="n">
-        <v>7485431</v>
+        <v>7485807</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12027,45 +12027,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126889027</v>
+        <v>126894597</v>
       </c>
       <c r="B115" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>856947</v>
+        <v>857222</v>
       </c>
       <c r="R115" t="n">
-        <v>7485678</v>
+        <v>7485544</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12112,12 +12112,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12128,48 +12128,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126895965</v>
+        <v>126894600</v>
       </c>
       <c r="B116" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>856897</v>
+        <v>857163</v>
       </c>
       <c r="R116" t="n">
-        <v>7485429</v>
+        <v>7485497</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12213,57 +12213,61 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126894597</v>
+        <v>126889027</v>
       </c>
       <c r="B117" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>857222</v>
+        <v>856947</v>
       </c>
       <c r="R117" t="n">
-        <v>7485544</v>
+        <v>7485678</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12310,12 +12314,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12326,48 +12330,48 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126894600</v>
+        <v>126895965</v>
       </c>
       <c r="B118" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>857163</v>
+        <v>856897</v>
       </c>
       <c r="R118" t="n">
-        <v>7485497</v>
+        <v>7485429</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12411,19 +12415,15 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13560,45 +13560,57 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126899896</v>
+        <v>126899818</v>
       </c>
       <c r="B130" t="n">
-        <v>80146</v>
+        <v>98442</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>856908</v>
+        <v>856921</v>
       </c>
       <c r="R130" t="n">
-        <v>7485414</v>
+        <v>7485611</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13639,6 +13651,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13650,7 +13663,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13661,57 +13674,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126899818</v>
+        <v>126899896</v>
       </c>
       <c r="B131" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>856921</v>
+        <v>856908</v>
       </c>
       <c r="R131" t="n">
-        <v>7485611</v>
+        <v>7485414</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13752,7 +13753,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -15653,64 +15653,59 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126882171</v>
+        <v>126895796</v>
       </c>
       <c r="B149" t="n">
-        <v>98442</v>
+        <v>97320</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>856765</v>
+        <v>856693</v>
       </c>
       <c r="R149" t="n">
-        <v>7485445</v>
+        <v>7485505</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15737,27 +15732,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15780,52 +15766,57 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126895796</v>
+        <v>126882171</v>
       </c>
       <c r="B150" t="n">
-        <v>97320</v>
+        <v>98442</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>856693</v>
+        <v>856765</v>
       </c>
       <c r="R150" t="n">
-        <v>7485505</v>
+        <v>7485445</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15852,18 +15843,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15886,10 +15886,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126883505</v>
+        <v>126895798</v>
       </c>
       <c r="B151" t="n">
-        <v>91290</v>
+        <v>97326</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15897,37 +15897,41 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R151" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15954,49 +15958,20 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -16009,14 +15984,18 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY151" t="inlineStr"/>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126895798</v>
+        <v>126883505</v>
       </c>
       <c r="B152" t="n">
-        <v>97326</v>
+        <v>91290</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16024,41 +16003,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R152" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16085,20 +16060,49 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16111,11 +16115,7 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -3553,45 +3553,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889016</v>
+        <v>126894596</v>
       </c>
       <c r="B31" t="n">
-        <v>80146</v>
+        <v>98442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>857042</v>
+        <v>857232</v>
       </c>
       <c r="R31" t="n">
-        <v>7485656</v>
+        <v>7485521</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3638,12 +3638,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3654,32 +3654,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893321</v>
+        <v>126893335</v>
       </c>
       <c r="B32" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>857154</v>
+        <v>857254</v>
       </c>
       <c r="R32" t="n">
-        <v>7485805</v>
+        <v>7485706</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126895913</v>
+        <v>126889016</v>
       </c>
       <c r="B33" t="n">
         <v>80146</v>
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>857071</v>
+        <v>857042</v>
       </c>
       <c r="R33" t="n">
-        <v>7485419</v>
+        <v>7485656</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3840,12 +3840,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3856,48 +3856,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126894596</v>
+        <v>126893321</v>
       </c>
       <c r="B34" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857232</v>
+        <v>857154</v>
       </c>
       <c r="R34" t="n">
-        <v>7485521</v>
+        <v>7485805</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3941,12 +3941,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -3957,32 +3957,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126893335</v>
+        <v>126895913</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3992,13 +3992,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>857254</v>
+        <v>857071</v>
       </c>
       <c r="R35" t="n">
-        <v>7485706</v>
+        <v>7485419</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -5272,7 +5272,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126895968</v>
+        <v>126889044</v>
       </c>
       <c r="B48" t="n">
         <v>98442</v>
@@ -5303,17 +5303,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>856872</v>
+        <v>857220</v>
       </c>
       <c r="R48" t="n">
-        <v>7485620</v>
+        <v>7485601</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5343,11 +5343,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Flera blommande ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5362,19 +5357,23 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126888927</v>
+        <v>126888930</v>
       </c>
       <c r="B49" t="n">
         <v>98442</v>
@@ -5409,10 +5408,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>856896</v>
+        <v>856694</v>
       </c>
       <c r="R49" t="n">
-        <v>7485538</v>
+        <v>7485592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5475,48 +5474,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126895916</v>
+        <v>126895963</v>
       </c>
       <c r="B50" t="n">
-        <v>98442</v>
+        <v>98463</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>857225</v>
+        <v>856930</v>
       </c>
       <c r="R50" t="n">
-        <v>7485668</v>
+        <v>7485560</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5546,6 +5545,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5560,23 +5564,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126889044</v>
+        <v>126895968</v>
       </c>
       <c r="B51" t="n">
         <v>98442</v>
@@ -5607,17 +5607,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>857220</v>
+        <v>856872</v>
       </c>
       <c r="R51" t="n">
-        <v>7485601</v>
+        <v>7485620</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5647,6 +5647,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Flera blommande ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5661,23 +5666,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126888930</v>
+        <v>126888927</v>
       </c>
       <c r="B52" t="n">
         <v>98442</v>
@@ -5712,10 +5713,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>856694</v>
+        <v>856896</v>
       </c>
       <c r="R52" t="n">
-        <v>7485592</v>
+        <v>7485538</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5778,48 +5779,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126895963</v>
+        <v>126895916</v>
       </c>
       <c r="B53" t="n">
-        <v>98463</v>
+        <v>98442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>856930</v>
+        <v>857225</v>
       </c>
       <c r="R53" t="n">
-        <v>7485560</v>
+        <v>7485668</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5849,11 +5850,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5868,44 +5864,48 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126888926</v>
+        <v>126893336</v>
       </c>
       <c r="B54" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>856904</v>
+        <v>857022</v>
       </c>
       <c r="R54" t="n">
-        <v>7485446</v>
+        <v>7485521</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5965,12 +5965,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -5981,32 +5981,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893336</v>
+        <v>126888926</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,13 +6016,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>857022</v>
+        <v>856904</v>
       </c>
       <c r="R55" t="n">
-        <v>7485521</v>
+        <v>7485446</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6066,12 +6066,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -9311,32 +9311,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126895917</v>
+        <v>126889034</v>
       </c>
       <c r="B88" t="n">
-        <v>79014</v>
+        <v>98463</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>857220</v>
+        <v>856998</v>
       </c>
       <c r="R88" t="n">
-        <v>7485407</v>
+        <v>7485630</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9396,12 +9396,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9412,32 +9412,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126889017</v>
+        <v>126895917</v>
       </c>
       <c r="B89" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9447,13 +9447,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>857021</v>
+        <v>857220</v>
       </c>
       <c r="R89" t="n">
-        <v>7485648</v>
+        <v>7485407</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9497,12 +9497,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9513,48 +9513,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126895973</v>
+        <v>126889017</v>
       </c>
       <c r="B90" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>856707</v>
+        <v>857021</v>
       </c>
       <c r="R90" t="n">
-        <v>7485577</v>
+        <v>7485648</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9598,60 +9598,64 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126889034</v>
+        <v>126895973</v>
       </c>
       <c r="B91" t="n">
-        <v>98463</v>
+        <v>98442</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>856998</v>
+        <v>856707</v>
       </c>
       <c r="R91" t="n">
-        <v>7485630</v>
+        <v>7485577</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9695,64 +9699,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126895962</v>
+        <v>126889025</v>
       </c>
       <c r="B92" t="n">
-        <v>91325</v>
+        <v>80146</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>856927</v>
+        <v>856955</v>
       </c>
       <c r="R92" t="n">
-        <v>7485482</v>
+        <v>7485682</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9796,60 +9796,64 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126893327</v>
+        <v>126895962</v>
       </c>
       <c r="B93" t="n">
-        <v>91309</v>
+        <v>91325</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4660</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>857141</v>
+        <v>856927</v>
       </c>
       <c r="R93" t="n">
-        <v>7485413</v>
+        <v>7485482</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9893,26 +9897,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126889025</v>
+        <v>126893327</v>
       </c>
       <c r="B94" t="n">
-        <v>80146</v>
+        <v>91309</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9920,21 +9920,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>4660</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9944,13 +9944,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>856955</v>
+        <v>857141</v>
       </c>
       <c r="R94" t="n">
-        <v>7485682</v>
+        <v>7485413</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9994,12 +9994,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10010,32 +10010,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126895914</v>
+        <v>126889050</v>
       </c>
       <c r="B95" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10045,13 +10045,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>856958</v>
+        <v>857208</v>
       </c>
       <c r="R95" t="n">
-        <v>7485679</v>
+        <v>7485545</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10095,12 +10095,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10111,32 +10111,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126889050</v>
+        <v>126893323</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>857208</v>
+        <v>856995</v>
       </c>
       <c r="R96" t="n">
-        <v>7485545</v>
+        <v>7485538</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10196,12 +10196,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10212,7 +10212,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126893323</v>
+        <v>126893325</v>
       </c>
       <c r="B97" t="n">
         <v>80146</v>
@@ -10247,10 +10247,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>856995</v>
+        <v>856884</v>
       </c>
       <c r="R97" t="n">
-        <v>7485538</v>
+        <v>7485698</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10313,7 +10313,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126893325</v>
+        <v>126895914</v>
       </c>
       <c r="B98" t="n">
         <v>80146</v>
@@ -10348,13 +10348,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>856884</v>
+        <v>856958</v>
       </c>
       <c r="R98" t="n">
-        <v>7485698</v>
+        <v>7485679</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10398,12 +10398,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11425,48 +11425,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126895975</v>
+        <v>126893334</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>856864</v>
+        <v>856938</v>
       </c>
       <c r="R109" t="n">
-        <v>7485417</v>
+        <v>7485632</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11510,60 +11510,64 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126893324</v>
+        <v>126895975</v>
       </c>
       <c r="B110" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>856949</v>
+        <v>856864</v>
       </c>
       <c r="R110" t="n">
-        <v>7485588</v>
+        <v>7485417</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11607,48 +11611,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126893334</v>
+        <v>126893324</v>
       </c>
       <c r="B111" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11658,10 +11658,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>856938</v>
+        <v>856949</v>
       </c>
       <c r="R111" t="n">
-        <v>7485632</v>
+        <v>7485588</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11724,32 +11724,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126893329</v>
+        <v>126893320</v>
       </c>
       <c r="B112" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11759,10 +11759,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>857202</v>
+        <v>857058</v>
       </c>
       <c r="R112" t="n">
-        <v>7485431</v>
+        <v>7485807</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11825,32 +11825,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126893320</v>
+        <v>126893329</v>
       </c>
       <c r="B113" t="n">
-        <v>80146</v>
+        <v>98442</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>857058</v>
+        <v>857202</v>
       </c>
       <c r="R113" t="n">
-        <v>7485807</v>
+        <v>7485431</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12625,10 +12625,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126889014</v>
+        <v>126889030</v>
       </c>
       <c r="B121" t="n">
-        <v>80146</v>
+        <v>98463</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12636,21 +12636,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12660,10 +12660,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>857043</v>
+        <v>857008</v>
       </c>
       <c r="R121" t="n">
-        <v>7485634</v>
+        <v>7485578</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12726,10 +12726,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126889030</v>
+        <v>126889014</v>
       </c>
       <c r="B122" t="n">
-        <v>98463</v>
+        <v>80146</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12737,21 +12737,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12761,10 +12761,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>857008</v>
+        <v>857043</v>
       </c>
       <c r="R122" t="n">
-        <v>7485578</v>
+        <v>7485634</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15886,10 +15886,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126895798</v>
+        <v>126883505</v>
       </c>
       <c r="B151" t="n">
-        <v>97326</v>
+        <v>91290</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15897,41 +15897,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R151" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15958,20 +15954,49 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -15984,18 +16009,14 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126883505</v>
+        <v>126895798</v>
       </c>
       <c r="B152" t="n">
-        <v>91290</v>
+        <v>97326</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16003,37 +16024,41 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R152" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16060,49 +16085,20 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16115,7 +16111,11 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY152" t="inlineStr"/>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>126722664</v>
       </c>
       <c r="B3" t="n">
-        <v>105462</v>
+        <v>105463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126722149</v>
+        <v>126722342</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,26 +926,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>856933</v>
+        <v>857019</v>
       </c>
       <c r="R4" t="n">
-        <v>7485793</v>
+        <v>7485818</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126722342</v>
+        <v>126722149</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,17 +1023,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>857019</v>
+        <v>856933</v>
       </c>
       <c r="R5" t="n">
-        <v>7485818</v>
+        <v>7485793</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1104,7 @@
         <v>126722592</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>126722905</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>126728180</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,32 +1392,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126722514</v>
+        <v>126722949</v>
       </c>
       <c r="B9" t="n">
-        <v>98463</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>857040</v>
+        <v>857001</v>
       </c>
       <c r="R9" t="n">
-        <v>7485799</v>
+        <v>7485674</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,32 +1489,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126722949</v>
+        <v>126722514</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>98464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>857001</v>
+        <v>857040</v>
       </c>
       <c r="R10" t="n">
-        <v>7485674</v>
+        <v>7485799</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1686,7 @@
         <v>126728177</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>126722224</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>126728179</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>126722237</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>126722312</v>
       </c>
       <c r="B19" t="n">
-        <v>91275</v>
+        <v>91276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,10 +2468,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126722838</v>
+        <v>126722552</v>
       </c>
       <c r="B20" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2496,26 +2496,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>857027</v>
+        <v>857113</v>
       </c>
       <c r="R20" t="n">
-        <v>7485680</v>
+        <v>7485787</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2574,10 +2565,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126722552</v>
+        <v>126722838</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,17 +2593,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>857113</v>
+        <v>857027</v>
       </c>
       <c r="R21" t="n">
-        <v>7485787</v>
+        <v>7485680</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,7 +2674,7 @@
         <v>126722784</v>
       </c>
       <c r="B22" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>126728174</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>126728176</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>126722975</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>126722205</v>
       </c>
       <c r="B26" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3165,32 +3165,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126728178</v>
+        <v>126728182</v>
       </c>
       <c r="B27" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>857082</v>
+        <v>856962</v>
       </c>
       <c r="R27" t="n">
-        <v>7485755</v>
+        <v>7485783</v>
       </c>
       <c r="S27" t="n">
         <v>14</v>
@@ -3262,32 +3262,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126728182</v>
+        <v>126728178</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>856962</v>
+        <v>857082</v>
       </c>
       <c r="R28" t="n">
-        <v>7485783</v>
+        <v>7485755</v>
       </c>
       <c r="S28" t="n">
         <v>14</v>
@@ -3359,32 +3359,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126722768</v>
+        <v>126722914</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>857037</v>
+        <v>857004</v>
       </c>
       <c r="R29" t="n">
-        <v>7485717</v>
+        <v>7485695</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3456,32 +3456,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126722914</v>
+        <v>126722768</v>
       </c>
       <c r="B30" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>857004</v>
+        <v>857037</v>
       </c>
       <c r="R30" t="n">
-        <v>7485695</v>
+        <v>7485717</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3553,48 +3553,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126894596</v>
+        <v>126893335</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>857232</v>
+        <v>857254</v>
       </c>
       <c r="R31" t="n">
-        <v>7485521</v>
+        <v>7485706</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3638,12 +3638,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3654,32 +3654,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893335</v>
+        <v>126889016</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3689,13 +3689,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>857254</v>
+        <v>857042</v>
       </c>
       <c r="R32" t="n">
-        <v>7485706</v>
+        <v>7485656</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3739,12 +3739,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3755,7 +3755,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126889016</v>
+        <v>126893321</v>
       </c>
       <c r="B33" t="n">
         <v>80146</v>
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>857042</v>
+        <v>857154</v>
       </c>
       <c r="R33" t="n">
-        <v>7485656</v>
+        <v>7485805</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3840,12 +3840,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3856,7 +3856,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126893321</v>
+        <v>126895913</v>
       </c>
       <c r="B34" t="n">
         <v>80146</v>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857154</v>
+        <v>857071</v>
       </c>
       <c r="R34" t="n">
-        <v>7485805</v>
+        <v>7485419</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3941,12 +3941,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -3957,48 +3957,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126895913</v>
+        <v>126894596</v>
       </c>
       <c r="B35" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>857071</v>
+        <v>857232</v>
       </c>
       <c r="R35" t="n">
-        <v>7485419</v>
+        <v>7485521</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4058,32 +4058,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126893330</v>
+        <v>126893328</v>
       </c>
       <c r="B36" t="n">
-        <v>98442</v>
+        <v>80153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>857082</v>
+        <v>856959</v>
       </c>
       <c r="R36" t="n">
-        <v>7485465</v>
+        <v>7485620</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4159,32 +4159,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126894589</v>
+        <v>126894580</v>
       </c>
       <c r="B37" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>857303</v>
+        <v>857065</v>
       </c>
       <c r="R37" t="n">
-        <v>7485733</v>
+        <v>7485568</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4260,32 +4260,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126893328</v>
+        <v>126893330</v>
       </c>
       <c r="B38" t="n">
-        <v>80153</v>
+        <v>98443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>856959</v>
+        <v>857082</v>
       </c>
       <c r="R38" t="n">
-        <v>7485620</v>
+        <v>7485465</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4361,48 +4361,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126894580</v>
+        <v>126895971</v>
       </c>
       <c r="B39" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>857065</v>
+        <v>856836</v>
       </c>
       <c r="R39" t="n">
-        <v>7485568</v>
+        <v>7485559</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4446,26 +4446,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126895971</v>
+        <v>126894589</v>
       </c>
       <c r="B40" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,17 +4489,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>856836</v>
+        <v>857303</v>
       </c>
       <c r="R40" t="n">
-        <v>7485559</v>
+        <v>7485733</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4547,57 +4543,61 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126894594</v>
+        <v>126889022</v>
       </c>
       <c r="B41" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>857257</v>
+        <v>856972</v>
       </c>
       <c r="R41" t="n">
-        <v>7485627</v>
+        <v>7485632</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4644,12 +4644,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4660,10 +4660,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126889042</v>
+        <v>126894594</v>
       </c>
       <c r="B42" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,14 +4691,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>857162</v>
+        <v>857257</v>
       </c>
       <c r="R42" t="n">
-        <v>7485708</v>
+        <v>7485627</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4745,12 +4745,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4761,10 +4761,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126894588</v>
+        <v>126889042</v>
       </c>
       <c r="B43" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4792,14 +4792,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>857238</v>
+        <v>857162</v>
       </c>
       <c r="R43" t="n">
-        <v>7485785</v>
+        <v>7485708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4846,12 +4846,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4862,10 +4862,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126893332</v>
+        <v>126894588</v>
       </c>
       <c r="B44" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4893,17 +4893,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>857047</v>
+        <v>857238</v>
       </c>
       <c r="R44" t="n">
-        <v>7485515</v>
+        <v>7485785</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4947,12 +4947,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -4966,7 +4966,7 @@
         <v>126895969</v>
       </c>
       <c r="B45" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5065,32 +5065,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126889022</v>
+        <v>126893332</v>
       </c>
       <c r="B46" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5100,13 +5100,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>856972</v>
+        <v>857047</v>
       </c>
       <c r="R46" t="n">
-        <v>7485632</v>
+        <v>7485515</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5150,12 +5150,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5272,10 +5272,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126889044</v>
+        <v>126895968</v>
       </c>
       <c r="B48" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5303,17 +5303,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>857220</v>
+        <v>856872</v>
       </c>
       <c r="R48" t="n">
-        <v>7485601</v>
+        <v>7485620</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5343,6 +5343,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Flera blommande ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5357,26 +5362,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126888930</v>
+        <v>126889044</v>
       </c>
       <c r="B49" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,10 +5409,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>856694</v>
+        <v>857220</v>
       </c>
       <c r="R49" t="n">
-        <v>7485592</v>
+        <v>7485601</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5458,12 +5459,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5474,48 +5475,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126895963</v>
+        <v>126895916</v>
       </c>
       <c r="B50" t="n">
-        <v>98463</v>
+        <v>98443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>856930</v>
+        <v>857225</v>
       </c>
       <c r="R50" t="n">
-        <v>7485560</v>
+        <v>7485668</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5545,11 +5546,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5564,44 +5560,48 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126895968</v>
+        <v>126895963</v>
       </c>
       <c r="B51" t="n">
-        <v>98442</v>
+        <v>98464</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>856872</v>
+        <v>856930</v>
       </c>
       <c r="R51" t="n">
-        <v>7485620</v>
+        <v>7485560</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Flera blommande ex</t>
+          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5681,7 +5681,7 @@
         <v>126888927</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5779,10 +5779,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126895916</v>
+        <v>126888930</v>
       </c>
       <c r="B53" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5814,13 +5814,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>857225</v>
+        <v>856694</v>
       </c>
       <c r="R53" t="n">
-        <v>7485668</v>
+        <v>7485592</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5864,12 +5864,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -5880,32 +5880,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893336</v>
+        <v>126888926</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>857022</v>
+        <v>856904</v>
       </c>
       <c r="R54" t="n">
-        <v>7485521</v>
+        <v>7485446</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5965,12 +5965,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -5981,32 +5981,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126888926</v>
+        <v>126893336</v>
       </c>
       <c r="B55" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,13 +6016,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>856904</v>
+        <v>857022</v>
       </c>
       <c r="R55" t="n">
-        <v>7485446</v>
+        <v>7485521</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6066,12 +6066,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6082,48 +6082,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893326</v>
+        <v>126895972</v>
       </c>
       <c r="B56" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>857089</v>
+        <v>856725</v>
       </c>
       <c r="R56" t="n">
-        <v>7485450</v>
+        <v>7485571</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6153,11 +6153,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6172,64 +6167,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126895972</v>
+        <v>126893326</v>
       </c>
       <c r="B57" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>856725</v>
+        <v>857089</v>
       </c>
       <c r="R57" t="n">
-        <v>7485571</v>
+        <v>7485450</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6259,6 +6250,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6273,22 +6269,26 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126893319</v>
+        <v>126889052</v>
       </c>
       <c r="B58" t="n">
-        <v>91500</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6296,21 +6296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6320,13 +6320,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>857122</v>
+        <v>857206</v>
       </c>
       <c r="R58" t="n">
-        <v>7485443</v>
+        <v>7485553</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6370,12 +6370,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6386,32 +6386,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126889052</v>
+        <v>126889013</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>857206</v>
+        <v>857038</v>
       </c>
       <c r="R59" t="n">
-        <v>7485553</v>
+        <v>7485632</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6487,7 +6487,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126889013</v>
+        <v>126894581</v>
       </c>
       <c r="B60" t="n">
         <v>80146</v>
@@ -6518,14 +6518,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>857038</v>
+        <v>857009</v>
       </c>
       <c r="R60" t="n">
-        <v>7485632</v>
+        <v>7485612</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6572,12 +6572,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6588,48 +6588,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126894581</v>
+        <v>126893319</v>
       </c>
       <c r="B61" t="n">
-        <v>80146</v>
+        <v>91501</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>1588</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>857009</v>
+        <v>857122</v>
       </c>
       <c r="R61" t="n">
-        <v>7485612</v>
+        <v>7485443</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6673,12 +6673,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6692,7 +6692,7 @@
         <v>126888928</v>
       </c>
       <c r="B62" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6887,10 +6887,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126889041</v>
+        <v>126895915</v>
       </c>
       <c r="B64" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6922,13 +6922,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>856978</v>
+        <v>857242</v>
       </c>
       <c r="R64" t="n">
-        <v>7485792</v>
+        <v>7485724</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6972,12 +6972,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -6988,10 +6988,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126895915</v>
+        <v>126889041</v>
       </c>
       <c r="B65" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7023,13 +7023,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>857242</v>
+        <v>856978</v>
       </c>
       <c r="R65" t="n">
-        <v>7485724</v>
+        <v>7485792</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7073,12 +7073,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7089,48 +7089,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126895921</v>
+        <v>126894583</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>857123</v>
+        <v>856988</v>
       </c>
       <c r="R66" t="n">
-        <v>7485402</v>
+        <v>7485572</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7174,12 +7174,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7190,10 +7190,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126894583</v>
+        <v>126889032</v>
       </c>
       <c r="B67" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7221,14 +7221,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>856988</v>
+        <v>857038</v>
       </c>
       <c r="R67" t="n">
-        <v>7485572</v>
+        <v>7485636</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7275,12 +7275,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7291,32 +7291,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126889032</v>
+        <v>126895921</v>
       </c>
       <c r="B68" t="n">
-        <v>98463</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7326,13 +7326,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>857038</v>
+        <v>857123</v>
       </c>
       <c r="R68" t="n">
-        <v>7485636</v>
+        <v>7485402</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7376,12 +7376,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7392,32 +7392,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126889045</v>
+        <v>126889029</v>
       </c>
       <c r="B69" t="n">
-        <v>98442</v>
+        <v>98464</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>857084</v>
+        <v>857083</v>
       </c>
       <c r="R69" t="n">
-        <v>7485530</v>
+        <v>7485527</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7493,32 +7493,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126889047</v>
+        <v>126895920</v>
       </c>
       <c r="B70" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>857010</v>
+        <v>857173</v>
       </c>
       <c r="R70" t="n">
-        <v>7485585</v>
+        <v>7485506</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7578,12 +7578,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7594,7 +7594,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126895920</v>
+        <v>126895922</v>
       </c>
       <c r="B71" t="n">
         <v>79014</v>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>857173</v>
+        <v>856981</v>
       </c>
       <c r="R71" t="n">
-        <v>7485506</v>
+        <v>7485578</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -7695,32 +7695,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126895922</v>
+        <v>126895910</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7730,10 +7730,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>856981</v>
+        <v>856984</v>
       </c>
       <c r="R72" t="n">
-        <v>7485578</v>
+        <v>7485600</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -7796,7 +7796,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126895910</v>
+        <v>126889021</v>
       </c>
       <c r="B73" t="n">
         <v>80146</v>
@@ -7831,13 +7831,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>856984</v>
+        <v>857000</v>
       </c>
       <c r="R73" t="n">
-        <v>7485600</v>
+        <v>7485629</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7881,12 +7881,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7897,7 +7897,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126889021</v>
+        <v>126889024</v>
       </c>
       <c r="B74" t="n">
         <v>80146</v>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>857000</v>
+        <v>856962</v>
       </c>
       <c r="R74" t="n">
-        <v>7485629</v>
+        <v>7485641</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7998,32 +7998,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126889024</v>
+        <v>126889045</v>
       </c>
       <c r="B75" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>856962</v>
+        <v>857084</v>
       </c>
       <c r="R75" t="n">
-        <v>7485641</v>
+        <v>7485530</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8099,32 +8099,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126889029</v>
+        <v>126889047</v>
       </c>
       <c r="B76" t="n">
-        <v>98463</v>
+        <v>98443</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>857083</v>
+        <v>857010</v>
       </c>
       <c r="R76" t="n">
-        <v>7485527</v>
+        <v>7485585</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8304,7 +8304,7 @@
         <v>126894584</v>
       </c>
       <c r="B78" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>126889039</v>
       </c>
       <c r="B79" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8806,10 +8806,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126888931</v>
+        <v>126894590</v>
       </c>
       <c r="B83" t="n">
-        <v>91899</v>
+        <v>98443</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8817,34 +8817,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>856896</v>
+        <v>857265</v>
       </c>
       <c r="R83" t="n">
-        <v>7485431</v>
+        <v>7485680</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8891,12 +8891,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8907,32 +8907,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126893339</v>
+        <v>126888929</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8942,13 +8942,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>857104</v>
+        <v>856800</v>
       </c>
       <c r="R84" t="n">
-        <v>7485447</v>
+        <v>7485540</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8992,12 +8992,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9008,7 +9008,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126894601</v>
+        <v>126893339</v>
       </c>
       <c r="B85" t="n">
         <v>79014</v>
@@ -9039,17 +9039,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>857215</v>
+        <v>857104</v>
       </c>
       <c r="R85" t="n">
-        <v>7485457</v>
+        <v>7485447</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9093,12 +9093,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9109,45 +9109,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126888929</v>
+        <v>126894601</v>
       </c>
       <c r="B86" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>856800</v>
+        <v>857215</v>
       </c>
       <c r="R86" t="n">
-        <v>7485540</v>
+        <v>7485457</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9194,12 +9194,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9210,10 +9210,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126894590</v>
+        <v>126888931</v>
       </c>
       <c r="B87" t="n">
-        <v>98442</v>
+        <v>91900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9221,34 +9221,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>857265</v>
+        <v>856896</v>
       </c>
       <c r="R87" t="n">
-        <v>7485680</v>
+        <v>7485431</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9295,12 +9295,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9311,48 +9311,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126889034</v>
+        <v>126895973</v>
       </c>
       <c r="B88" t="n">
-        <v>98463</v>
+        <v>98443</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>856998</v>
+        <v>856707</v>
       </c>
       <c r="R88" t="n">
-        <v>7485630</v>
+        <v>7485577</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9396,19 +9396,15 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9614,48 +9610,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126895973</v>
+        <v>126889034</v>
       </c>
       <c r="B91" t="n">
-        <v>98442</v>
+        <v>98464</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>856707</v>
+        <v>856998</v>
       </c>
       <c r="R91" t="n">
-        <v>7485577</v>
+        <v>7485630</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9699,60 +9695,64 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126889025</v>
+        <v>126895962</v>
       </c>
       <c r="B92" t="n">
-        <v>80146</v>
+        <v>91326</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>856955</v>
+        <v>856927</v>
       </c>
       <c r="R92" t="n">
-        <v>7485682</v>
+        <v>7485482</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9796,64 +9796,60 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126895962</v>
+        <v>126893327</v>
       </c>
       <c r="B93" t="n">
-        <v>91325</v>
+        <v>91310</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>856927</v>
+        <v>857141</v>
       </c>
       <c r="R93" t="n">
-        <v>7485482</v>
+        <v>7485413</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9897,22 +9893,26 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126893327</v>
+        <v>126889025</v>
       </c>
       <c r="B94" t="n">
-        <v>91309</v>
+        <v>80146</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9920,21 +9920,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4660</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9944,13 +9944,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>857141</v>
+        <v>856955</v>
       </c>
       <c r="R94" t="n">
-        <v>7485413</v>
+        <v>7485682</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9994,12 +9994,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10417,7 +10417,7 @@
         <v>126893333</v>
       </c>
       <c r="B99" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>126894595</v>
       </c>
       <c r="B101" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>126889049</v>
       </c>
       <c r="B102" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>126895967</v>
       </c>
       <c r="B103" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10920,32 +10920,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126893338</v>
+        <v>126889036</v>
       </c>
       <c r="B104" t="n">
-        <v>79014</v>
+        <v>80021</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10955,13 +10955,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>856954</v>
+        <v>857182</v>
       </c>
       <c r="R104" t="n">
-        <v>7485603</v>
+        <v>7485442</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11005,12 +11005,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11021,10 +11021,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126889036</v>
+        <v>126895966</v>
       </c>
       <c r="B105" t="n">
-        <v>80021</v>
+        <v>80153</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11032,37 +11032,40 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>857182</v>
+        <v>856849</v>
       </c>
       <c r="R105" t="n">
-        <v>7485442</v>
+        <v>7485405</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11100,32 +11103,29 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126895966</v>
+        <v>126893322</v>
       </c>
       <c r="B106" t="n">
-        <v>80153</v>
+        <v>80146</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11133,40 +11133,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>856849</v>
+        <v>857015</v>
       </c>
       <c r="R106" t="n">
-        <v>7485405</v>
+        <v>7485514</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11204,29 +11201,32 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126893322</v>
+        <v>126889037</v>
       </c>
       <c r="B107" t="n">
-        <v>80146</v>
+        <v>80021</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11234,21 +11234,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11258,13 +11258,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>857015</v>
+        <v>857094</v>
       </c>
       <c r="R107" t="n">
-        <v>7485514</v>
+        <v>7485517</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11308,12 +11308,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11324,32 +11324,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126889037</v>
+        <v>126893338</v>
       </c>
       <c r="B108" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11359,13 +11359,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>857094</v>
+        <v>856954</v>
       </c>
       <c r="R108" t="n">
-        <v>7485517</v>
+        <v>7485603</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11409,12 +11409,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11425,32 +11425,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126893334</v>
+        <v>126893324</v>
       </c>
       <c r="B109" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11460,10 +11460,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>856938</v>
+        <v>856949</v>
       </c>
       <c r="R109" t="n">
-        <v>7485632</v>
+        <v>7485588</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11623,32 +11623,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126893324</v>
+        <v>126893334</v>
       </c>
       <c r="B111" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11658,10 +11658,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>856949</v>
+        <v>856938</v>
       </c>
       <c r="R111" t="n">
-        <v>7485588</v>
+        <v>7485632</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11724,10 +11724,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126893320</v>
+        <v>126894585</v>
       </c>
       <c r="B112" t="n">
-        <v>80146</v>
+        <v>97327</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11735,37 +11735,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>857058</v>
+        <v>857167</v>
       </c>
       <c r="R112" t="n">
-        <v>7485807</v>
+        <v>7485432</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11809,12 +11809,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -11825,32 +11825,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126893329</v>
+        <v>126893320</v>
       </c>
       <c r="B113" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>857202</v>
+        <v>857058</v>
       </c>
       <c r="R113" t="n">
-        <v>7485431</v>
+        <v>7485807</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11926,48 +11926,48 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126894585</v>
+        <v>126893329</v>
       </c>
       <c r="B114" t="n">
-        <v>97326</v>
+        <v>98443</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>857167</v>
+        <v>857202</v>
       </c>
       <c r="R114" t="n">
-        <v>7485432</v>
+        <v>7485431</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12011,12 +12011,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12427,10 +12427,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126894592</v>
+        <v>126895970</v>
       </c>
       <c r="B119" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12458,17 +12458,17 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>857255</v>
+        <v>856849</v>
       </c>
       <c r="R119" t="n">
-        <v>7485644</v>
+        <v>7485559</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12512,26 +12512,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126895970</v>
+        <v>126894592</v>
       </c>
       <c r="B120" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12559,17 +12555,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>856849</v>
+        <v>857255</v>
       </c>
       <c r="R120" t="n">
-        <v>7485559</v>
+        <v>7485644</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12613,22 +12609,26 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
         <v>126889030</v>
       </c>
       <c r="B121" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12827,10 +12827,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126899898</v>
+        <v>126899900</v>
       </c>
       <c r="B123" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12857,12 +12857,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -12874,10 +12874,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>856878</v>
+        <v>856926</v>
       </c>
       <c r="R123" t="n">
-        <v>7485406</v>
+        <v>7485578</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12941,10 +12941,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126899900</v>
+        <v>126899898</v>
       </c>
       <c r="B124" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12971,12 +12971,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>856926</v>
+        <v>856878</v>
       </c>
       <c r="R124" t="n">
-        <v>7485578</v>
+        <v>7485406</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13055,32 +13055,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126899894</v>
+        <v>126899816</v>
       </c>
       <c r="B125" t="n">
-        <v>75138</v>
+        <v>80153</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>856906</v>
+        <v>856947</v>
       </c>
       <c r="R125" t="n">
-        <v>7485559</v>
+        <v>7485478</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13145,7 +13145,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13156,32 +13156,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126899816</v>
+        <v>126899894</v>
       </c>
       <c r="B126" t="n">
-        <v>80153</v>
+        <v>75138</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13191,10 +13191,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>856947</v>
+        <v>856906</v>
       </c>
       <c r="R126" t="n">
-        <v>7485478</v>
+        <v>7485559</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13361,7 +13361,7 @@
         <v>126899815</v>
       </c>
       <c r="B128" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13560,57 +13560,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126899818</v>
+        <v>126899896</v>
       </c>
       <c r="B130" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>856921</v>
+        <v>856908</v>
       </c>
       <c r="R130" t="n">
-        <v>7485611</v>
+        <v>7485414</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13651,7 +13639,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13663,7 +13650,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13674,45 +13661,57 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126899896</v>
+        <v>126899818</v>
       </c>
       <c r="B131" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>856908</v>
+        <v>856921</v>
       </c>
       <c r="R131" t="n">
-        <v>7485414</v>
+        <v>7485611</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13753,6 +13752,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -13778,7 +13778,7 @@
         <v>126899899</v>
       </c>
       <c r="B132" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>126899817</v>
       </c>
       <c r="B133" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>126899820</v>
       </c>
       <c r="B134" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>126899902</v>
       </c>
       <c r="B135" t="n">
-        <v>91899</v>
+        <v>91900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>126899819</v>
       </c>
       <c r="B137" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>126883898</v>
       </c>
       <c r="B140" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>126895795</v>
       </c>
       <c r="B141" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>126895794</v>
       </c>
       <c r="B147" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>126883438</v>
       </c>
       <c r="B148" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -15663,7 +15663,7 @@
         <v>126895796</v>
       </c>
       <c r="B149" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>126882171</v>
       </c>
       <c r="B150" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>126883505</v>
       </c>
       <c r="B151" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>126895798</v>
       </c>
       <c r="B152" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -2371,32 +2371,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126722312</v>
+        <v>126722552</v>
       </c>
       <c r="B19" t="n">
-        <v>91276</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>857016</v>
+        <v>857113</v>
       </c>
       <c r="R19" t="n">
-        <v>7485810</v>
+        <v>7485787</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126722552</v>
+        <v>126722838</v>
       </c>
       <c r="B20" t="n">
         <v>98443</v>
@@ -2496,17 +2496,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>857113</v>
+        <v>857027</v>
       </c>
       <c r="R20" t="n">
-        <v>7485787</v>
+        <v>7485680</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2565,54 +2574,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126722838</v>
+        <v>126722312</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>91276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>857027</v>
+        <v>857016</v>
       </c>
       <c r="R21" t="n">
-        <v>7485680</v>
+        <v>7485810</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3165,32 +3165,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126728182</v>
+        <v>126728178</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>856962</v>
+        <v>857082</v>
       </c>
       <c r="R27" t="n">
-        <v>7485783</v>
+        <v>7485755</v>
       </c>
       <c r="S27" t="n">
         <v>14</v>
@@ -3262,32 +3262,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126728178</v>
+        <v>126728182</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>857082</v>
+        <v>856962</v>
       </c>
       <c r="R28" t="n">
-        <v>7485755</v>
+        <v>7485783</v>
       </c>
       <c r="S28" t="n">
         <v>14</v>
@@ -3359,32 +3359,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126722914</v>
+        <v>126722768</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>857004</v>
+        <v>857037</v>
       </c>
       <c r="R29" t="n">
-        <v>7485695</v>
+        <v>7485717</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3456,32 +3456,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126722768</v>
+        <v>126722914</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>857037</v>
+        <v>857004</v>
       </c>
       <c r="R30" t="n">
-        <v>7485717</v>
+        <v>7485695</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -6285,32 +6285,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126889052</v>
+        <v>126889013</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>857206</v>
+        <v>857038</v>
       </c>
       <c r="R58" t="n">
-        <v>7485553</v>
+        <v>7485632</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6386,7 +6386,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126889013</v>
+        <v>126894581</v>
       </c>
       <c r="B59" t="n">
         <v>80146</v>
@@ -6417,14 +6417,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>857038</v>
+        <v>857009</v>
       </c>
       <c r="R59" t="n">
-        <v>7485632</v>
+        <v>7485612</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6471,12 +6471,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6487,48 +6487,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126894581</v>
+        <v>126893319</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>91501</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>1588</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>857009</v>
+        <v>857122</v>
       </c>
       <c r="R60" t="n">
-        <v>7485612</v>
+        <v>7485443</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6572,12 +6572,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6588,10 +6588,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126893319</v>
+        <v>126889052</v>
       </c>
       <c r="B61" t="n">
-        <v>91501</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6599,21 +6599,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6623,13 +6623,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>857122</v>
+        <v>857206</v>
       </c>
       <c r="R61" t="n">
-        <v>7485443</v>
+        <v>7485553</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6673,12 +6673,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6790,10 +6790,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126895961</v>
+        <v>126895921</v>
       </c>
       <c r="B63" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6801,37 +6801,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>856840</v>
+        <v>857123</v>
       </c>
       <c r="R63" t="n">
-        <v>7485479</v>
+        <v>7485402</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6875,60 +6875,64 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126895915</v>
+        <v>126895961</v>
       </c>
       <c r="B64" t="n">
-        <v>98443</v>
+        <v>75138</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>857242</v>
+        <v>856840</v>
       </c>
       <c r="R64" t="n">
-        <v>7485724</v>
+        <v>7485479</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6972,61 +6976,57 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126889041</v>
+        <v>126894583</v>
       </c>
       <c r="B65" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>856978</v>
+        <v>856988</v>
       </c>
       <c r="R65" t="n">
-        <v>7485792</v>
+        <v>7485572</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7073,12 +7073,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7089,7 +7089,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126894583</v>
+        <v>126889032</v>
       </c>
       <c r="B66" t="n">
         <v>98464</v>
@@ -7120,14 +7120,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>856988</v>
+        <v>857038</v>
       </c>
       <c r="R66" t="n">
-        <v>7485572</v>
+        <v>7485636</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7174,12 +7174,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7190,32 +7190,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126889032</v>
+        <v>126895915</v>
       </c>
       <c r="B67" t="n">
-        <v>98464</v>
+        <v>98443</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7225,13 +7225,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>857038</v>
+        <v>857242</v>
       </c>
       <c r="R67" t="n">
-        <v>7485636</v>
+        <v>7485724</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7275,12 +7275,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7291,32 +7291,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126895921</v>
+        <v>126889041</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7326,13 +7326,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>857123</v>
+        <v>856978</v>
       </c>
       <c r="R68" t="n">
-        <v>7485402</v>
+        <v>7485792</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7376,12 +7376,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8705,32 +8705,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126889019</v>
+        <v>126893339</v>
       </c>
       <c r="B82" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8740,13 +8740,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>857016</v>
+        <v>857104</v>
       </c>
       <c r="R82" t="n">
-        <v>7485635</v>
+        <v>7485447</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8790,12 +8790,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8806,32 +8806,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126894590</v>
+        <v>126894601</v>
       </c>
       <c r="B83" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>857265</v>
+        <v>857215</v>
       </c>
       <c r="R83" t="n">
-        <v>7485680</v>
+        <v>7485457</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8907,10 +8907,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126888929</v>
+        <v>126888931</v>
       </c>
       <c r="B84" t="n">
-        <v>98443</v>
+        <v>91900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8918,21 +8918,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>856800</v>
+        <v>856896</v>
       </c>
       <c r="R84" t="n">
-        <v>7485540</v>
+        <v>7485431</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9008,32 +9008,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126893339</v>
+        <v>126889019</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9043,13 +9043,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>857104</v>
+        <v>857016</v>
       </c>
       <c r="R85" t="n">
-        <v>7485447</v>
+        <v>7485635</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9093,12 +9093,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9109,32 +9109,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126894601</v>
+        <v>126894590</v>
       </c>
       <c r="B86" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>857215</v>
+        <v>857265</v>
       </c>
       <c r="R86" t="n">
-        <v>7485457</v>
+        <v>7485680</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9210,10 +9210,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126888931</v>
+        <v>126888929</v>
       </c>
       <c r="B87" t="n">
-        <v>91900</v>
+        <v>98443</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9221,21 +9221,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9245,10 +9245,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>856896</v>
+        <v>856800</v>
       </c>
       <c r="R87" t="n">
-        <v>7485431</v>
+        <v>7485540</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9711,48 +9711,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126895962</v>
+        <v>126893327</v>
       </c>
       <c r="B92" t="n">
-        <v>91326</v>
+        <v>91310</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>856927</v>
+        <v>857141</v>
       </c>
       <c r="R92" t="n">
-        <v>7485482</v>
+        <v>7485413</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9796,22 +9796,26 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126893327</v>
+        <v>126889025</v>
       </c>
       <c r="B93" t="n">
-        <v>91310</v>
+        <v>80146</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9819,21 +9823,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4660</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9843,13 +9847,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>857141</v>
+        <v>856955</v>
       </c>
       <c r="R93" t="n">
-        <v>7485413</v>
+        <v>7485682</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9893,12 +9897,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -9909,48 +9913,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126889025</v>
+        <v>126895962</v>
       </c>
       <c r="B94" t="n">
-        <v>80146</v>
+        <v>91326</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>856955</v>
+        <v>856927</v>
       </c>
       <c r="R94" t="n">
-        <v>7485682</v>
+        <v>7485482</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9994,19 +9998,15 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10111,32 +10111,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126893323</v>
+        <v>126893333</v>
       </c>
       <c r="B96" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>856995</v>
+        <v>856968</v>
       </c>
       <c r="R96" t="n">
-        <v>7485538</v>
+        <v>7485570</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10212,7 +10212,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126893325</v>
+        <v>126893323</v>
       </c>
       <c r="B97" t="n">
         <v>80146</v>
@@ -10247,10 +10247,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>856884</v>
+        <v>856995</v>
       </c>
       <c r="R97" t="n">
-        <v>7485698</v>
+        <v>7485538</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10313,7 +10313,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126895914</v>
+        <v>126893325</v>
       </c>
       <c r="B98" t="n">
         <v>80146</v>
@@ -10348,13 +10348,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>856958</v>
+        <v>856884</v>
       </c>
       <c r="R98" t="n">
-        <v>7485679</v>
+        <v>7485698</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10398,12 +10398,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10414,32 +10414,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126893333</v>
+        <v>126895914</v>
       </c>
       <c r="B99" t="n">
-        <v>98443</v>
+        <v>80146</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10449,13 +10449,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>856968</v>
+        <v>856958</v>
       </c>
       <c r="R99" t="n">
-        <v>7485570</v>
+        <v>7485679</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10499,12 +10499,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11526,48 +11526,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126895975</v>
+        <v>126893334</v>
       </c>
       <c r="B110" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>856864</v>
+        <v>856938</v>
       </c>
       <c r="R110" t="n">
-        <v>7485417</v>
+        <v>7485632</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11611,60 +11611,64 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126893334</v>
+        <v>126895975</v>
       </c>
       <c r="B111" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>856938</v>
+        <v>856864</v>
       </c>
       <c r="R111" t="n">
-        <v>7485632</v>
+        <v>7485417</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11708,19 +11712,15 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12027,48 +12027,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126894597</v>
+        <v>126895965</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>857222</v>
+        <v>856897</v>
       </c>
       <c r="R115" t="n">
-        <v>7485544</v>
+        <v>7485429</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12112,23 +12112,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126894600</v>
+        <v>126894597</v>
       </c>
       <c r="B116" t="n">
         <v>79014</v>
@@ -12163,10 +12159,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>857163</v>
+        <v>857222</v>
       </c>
       <c r="R116" t="n">
-        <v>7485497</v>
+        <v>7485544</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12229,45 +12225,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126889027</v>
+        <v>126894600</v>
       </c>
       <c r="B117" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>856947</v>
+        <v>857163</v>
       </c>
       <c r="R117" t="n">
-        <v>7485678</v>
+        <v>7485497</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12314,12 +12310,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12330,10 +12326,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126895965</v>
+        <v>126889027</v>
       </c>
       <c r="B118" t="n">
-        <v>80153</v>
+        <v>80146</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12341,37 +12337,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>856897</v>
+        <v>856947</v>
       </c>
       <c r="R118" t="n">
-        <v>7485429</v>
+        <v>7485678</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12415,15 +12411,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12625,10 +12625,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126889030</v>
+        <v>126889014</v>
       </c>
       <c r="B121" t="n">
-        <v>98464</v>
+        <v>80146</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12636,21 +12636,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12660,10 +12660,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>857008</v>
+        <v>857043</v>
       </c>
       <c r="R121" t="n">
-        <v>7485578</v>
+        <v>7485634</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12726,10 +12726,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126889014</v>
+        <v>126889030</v>
       </c>
       <c r="B122" t="n">
-        <v>80146</v>
+        <v>98464</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12737,21 +12737,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12761,10 +12761,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>857043</v>
+        <v>857008</v>
       </c>
       <c r="R122" t="n">
-        <v>7485634</v>
+        <v>7485578</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126722342</v>
+        <v>126722149</v>
       </c>
       <c r="B4" t="n">
         <v>98443</v>
@@ -926,17 +926,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>857019</v>
+        <v>856933</v>
       </c>
       <c r="R4" t="n">
-        <v>7485818</v>
+        <v>7485793</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +1004,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126722149</v>
+        <v>126722342</v>
       </c>
       <c r="B5" t="n">
         <v>98443</v>
@@ -1023,26 +1032,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>856933</v>
+        <v>857019</v>
       </c>
       <c r="R5" t="n">
-        <v>7485793</v>
+        <v>7485818</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1877,32 +1877,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126728179</v>
+        <v>126728181</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>857020</v>
+        <v>857024</v>
       </c>
       <c r="R14" t="n">
-        <v>7485779</v>
+        <v>7485613</v>
       </c>
       <c r="S14" t="n">
         <v>14</v>
@@ -1974,54 +1974,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126722237</v>
+        <v>126722469</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>856991</v>
+        <v>857037</v>
       </c>
       <c r="R15" t="n">
-        <v>7485798</v>
+        <v>7485805</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,32 +2071,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126728181</v>
+        <v>126728179</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>857024</v>
+        <v>857020</v>
       </c>
       <c r="R16" t="n">
-        <v>7485613</v>
+        <v>7485779</v>
       </c>
       <c r="S16" t="n">
         <v>14</v>
@@ -2177,45 +2168,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126722469</v>
+        <v>126722237</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>857037</v>
+        <v>856991</v>
       </c>
       <c r="R17" t="n">
-        <v>7485805</v>
+        <v>7485798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,32 +2371,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126722552</v>
+        <v>126722312</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>91276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>857113</v>
+        <v>857016</v>
       </c>
       <c r="R19" t="n">
-        <v>7485787</v>
+        <v>7485810</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,32 +2574,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126722312</v>
+        <v>126722552</v>
       </c>
       <c r="B21" t="n">
-        <v>91276</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>857016</v>
+        <v>857113</v>
       </c>
       <c r="R21" t="n">
-        <v>7485810</v>
+        <v>7485787</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3165,32 +3165,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126728178</v>
+        <v>126728182</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>857082</v>
+        <v>856962</v>
       </c>
       <c r="R27" t="n">
-        <v>7485755</v>
+        <v>7485783</v>
       </c>
       <c r="S27" t="n">
         <v>14</v>
@@ -3262,32 +3262,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126728182</v>
+        <v>126728178</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>856962</v>
+        <v>857082</v>
       </c>
       <c r="R28" t="n">
-        <v>7485783</v>
+        <v>7485755</v>
       </c>
       <c r="S28" t="n">
         <v>14</v>
@@ -3359,32 +3359,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126722768</v>
+        <v>126722914</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>857037</v>
+        <v>857004</v>
       </c>
       <c r="R29" t="n">
-        <v>7485717</v>
+        <v>7485695</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3456,32 +3456,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126722914</v>
+        <v>126722768</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>857004</v>
+        <v>857037</v>
       </c>
       <c r="R30" t="n">
-        <v>7485695</v>
+        <v>7485717</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126893335</v>
+        <v>126889016</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>857254</v>
+        <v>857042</v>
       </c>
       <c r="R31" t="n">
-        <v>7485706</v>
+        <v>7485656</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3638,12 +3638,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3654,7 +3654,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889016</v>
+        <v>126893321</v>
       </c>
       <c r="B32" t="n">
         <v>80146</v>
@@ -3689,13 +3689,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>857042</v>
+        <v>857154</v>
       </c>
       <c r="R32" t="n">
-        <v>7485656</v>
+        <v>7485805</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3739,12 +3739,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3755,7 +3755,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126893321</v>
+        <v>126895913</v>
       </c>
       <c r="B33" t="n">
         <v>80146</v>
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>857154</v>
+        <v>857071</v>
       </c>
       <c r="R33" t="n">
-        <v>7485805</v>
+        <v>7485419</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3840,12 +3840,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3856,32 +3856,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126895913</v>
+        <v>126893335</v>
       </c>
       <c r="B34" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857071</v>
+        <v>857254</v>
       </c>
       <c r="R34" t="n">
-        <v>7485419</v>
+        <v>7485706</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3941,12 +3941,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -5475,7 +5475,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126895916</v>
+        <v>126888927</v>
       </c>
       <c r="B50" t="n">
         <v>98443</v>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>857225</v>
+        <v>856896</v>
       </c>
       <c r="R50" t="n">
-        <v>7485668</v>
+        <v>7485538</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5560,12 +5560,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5576,48 +5576,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126895963</v>
+        <v>126895916</v>
       </c>
       <c r="B51" t="n">
-        <v>98464</v>
+        <v>98443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>856930</v>
+        <v>857225</v>
       </c>
       <c r="R51" t="n">
-        <v>7485560</v>
+        <v>7485668</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5647,11 +5647,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5666,19 +5661,23 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126888927</v>
+        <v>126888930</v>
       </c>
       <c r="B52" t="n">
         <v>98443</v>
@@ -5713,10 +5712,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>856896</v>
+        <v>856694</v>
       </c>
       <c r="R52" t="n">
-        <v>7485538</v>
+        <v>7485592</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5779,48 +5778,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126888930</v>
+        <v>126895963</v>
       </c>
       <c r="B53" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>856694</v>
+        <v>856930</v>
       </c>
       <c r="R53" t="n">
-        <v>7485592</v>
+        <v>7485560</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5850,6 +5849,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5864,48 +5868,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126888926</v>
+        <v>126893336</v>
       </c>
       <c r="B54" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>856904</v>
+        <v>857022</v>
       </c>
       <c r="R54" t="n">
-        <v>7485446</v>
+        <v>7485521</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5965,12 +5965,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -5981,32 +5981,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893336</v>
+        <v>126888926</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,13 +6016,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>857022</v>
+        <v>856904</v>
       </c>
       <c r="R55" t="n">
-        <v>7485521</v>
+        <v>7485446</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6066,12 +6066,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6082,48 +6082,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126895972</v>
+        <v>126893326</v>
       </c>
       <c r="B56" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>856725</v>
+        <v>857089</v>
       </c>
       <c r="R56" t="n">
-        <v>7485571</v>
+        <v>7485450</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6153,6 +6153,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6167,60 +6172,64 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126893326</v>
+        <v>126895972</v>
       </c>
       <c r="B57" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>857089</v>
+        <v>856725</v>
       </c>
       <c r="R57" t="n">
-        <v>7485450</v>
+        <v>7485571</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6250,11 +6259,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6269,48 +6273,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126889013</v>
+        <v>126893319</v>
       </c>
       <c r="B58" t="n">
-        <v>80146</v>
+        <v>91501</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>1588</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6320,13 +6320,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>857038</v>
+        <v>857122</v>
       </c>
       <c r="R58" t="n">
-        <v>7485632</v>
+        <v>7485443</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6370,12 +6370,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6386,7 +6386,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126894581</v>
+        <v>126889013</v>
       </c>
       <c r="B59" t="n">
         <v>80146</v>
@@ -6417,14 +6417,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>857009</v>
+        <v>857038</v>
       </c>
       <c r="R59" t="n">
-        <v>7485612</v>
+        <v>7485632</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6471,12 +6471,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6487,48 +6487,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126893319</v>
+        <v>126894581</v>
       </c>
       <c r="B60" t="n">
-        <v>91501</v>
+        <v>80146</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1588</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>857122</v>
+        <v>857009</v>
       </c>
       <c r="R60" t="n">
-        <v>7485443</v>
+        <v>7485612</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6572,12 +6572,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6988,48 +6988,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126894583</v>
+        <v>126895915</v>
       </c>
       <c r="B65" t="n">
-        <v>98464</v>
+        <v>98443</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>856988</v>
+        <v>857242</v>
       </c>
       <c r="R65" t="n">
-        <v>7485572</v>
+        <v>7485724</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7073,12 +7073,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7089,32 +7089,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126889032</v>
+        <v>126889041</v>
       </c>
       <c r="B66" t="n">
-        <v>98464</v>
+        <v>98443</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7124,10 +7124,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>857038</v>
+        <v>856978</v>
       </c>
       <c r="R66" t="n">
-        <v>7485636</v>
+        <v>7485792</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7190,48 +7190,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126895915</v>
+        <v>126894583</v>
       </c>
       <c r="B67" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>857242</v>
+        <v>856988</v>
       </c>
       <c r="R67" t="n">
-        <v>7485724</v>
+        <v>7485572</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7275,12 +7275,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7291,32 +7291,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126889041</v>
+        <v>126889032</v>
       </c>
       <c r="B68" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>856978</v>
+        <v>857038</v>
       </c>
       <c r="R68" t="n">
-        <v>7485792</v>
+        <v>7485636</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7392,32 +7392,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126889029</v>
+        <v>126895920</v>
       </c>
       <c r="B69" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7427,13 +7427,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>857083</v>
+        <v>857173</v>
       </c>
       <c r="R69" t="n">
-        <v>7485527</v>
+        <v>7485506</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7477,12 +7477,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7493,7 +7493,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126895920</v>
+        <v>126895922</v>
       </c>
       <c r="B70" t="n">
         <v>79014</v>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>857173</v>
+        <v>856981</v>
       </c>
       <c r="R70" t="n">
-        <v>7485506</v>
+        <v>7485578</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -7594,32 +7594,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126895922</v>
+        <v>126895910</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>856981</v>
+        <v>856984</v>
       </c>
       <c r="R71" t="n">
-        <v>7485578</v>
+        <v>7485600</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -7695,7 +7695,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126895910</v>
+        <v>126889021</v>
       </c>
       <c r="B72" t="n">
         <v>80146</v>
@@ -7730,13 +7730,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>856984</v>
+        <v>857000</v>
       </c>
       <c r="R72" t="n">
-        <v>7485600</v>
+        <v>7485629</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7780,12 +7780,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7796,7 +7796,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126889021</v>
+        <v>126889024</v>
       </c>
       <c r="B73" t="n">
         <v>80146</v>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>857000</v>
+        <v>856962</v>
       </c>
       <c r="R73" t="n">
-        <v>7485629</v>
+        <v>7485641</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7897,32 +7897,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126889024</v>
+        <v>126889045</v>
       </c>
       <c r="B74" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>856962</v>
+        <v>857084</v>
       </c>
       <c r="R74" t="n">
-        <v>7485641</v>
+        <v>7485530</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7998,7 +7998,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126889045</v>
+        <v>126889047</v>
       </c>
       <c r="B75" t="n">
         <v>98443</v>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>857084</v>
+        <v>857010</v>
       </c>
       <c r="R75" t="n">
-        <v>7485530</v>
+        <v>7485585</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8099,32 +8099,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126889047</v>
+        <v>126889029</v>
       </c>
       <c r="B76" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>857010</v>
+        <v>857083</v>
       </c>
       <c r="R76" t="n">
-        <v>7485585</v>
+        <v>7485527</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8200,32 +8200,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126894602</v>
+        <v>126894584</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>97327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>857075</v>
+        <v>857231</v>
       </c>
       <c r="R77" t="n">
-        <v>7485539</v>
+        <v>7485574</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8301,7 +8301,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126894584</v>
+        <v>126889039</v>
       </c>
       <c r="B78" t="n">
         <v>97327</v>
@@ -8332,14 +8332,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>857231</v>
+        <v>857184</v>
       </c>
       <c r="R78" t="n">
-        <v>7485574</v>
+        <v>7485414</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8386,12 +8386,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8402,45 +8402,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126889039</v>
+        <v>126894602</v>
       </c>
       <c r="B79" t="n">
-        <v>97327</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>857184</v>
+        <v>857075</v>
       </c>
       <c r="R79" t="n">
-        <v>7485414</v>
+        <v>7485539</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8487,12 +8487,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8705,32 +8705,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126893339</v>
+        <v>126888931</v>
       </c>
       <c r="B82" t="n">
-        <v>79014</v>
+        <v>91900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8740,13 +8740,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>857104</v>
+        <v>856896</v>
       </c>
       <c r="R82" t="n">
-        <v>7485447</v>
+        <v>7485431</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8790,12 +8790,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8806,7 +8806,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126894601</v>
+        <v>126893339</v>
       </c>
       <c r="B83" t="n">
         <v>79014</v>
@@ -8837,17 +8837,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>857215</v>
+        <v>857104</v>
       </c>
       <c r="R83" t="n">
-        <v>7485457</v>
+        <v>7485447</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8891,12 +8891,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8907,45 +8907,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126888931</v>
+        <v>126894601</v>
       </c>
       <c r="B84" t="n">
-        <v>91900</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>856896</v>
+        <v>857215</v>
       </c>
       <c r="R84" t="n">
-        <v>7485431</v>
+        <v>7485457</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8992,12 +8992,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9109,7 +9109,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126894590</v>
+        <v>126888929</v>
       </c>
       <c r="B86" t="n">
         <v>98443</v>
@@ -9140,14 +9140,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>857265</v>
+        <v>856800</v>
       </c>
       <c r="R86" t="n">
-        <v>7485680</v>
+        <v>7485540</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9194,12 +9194,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9210,7 +9210,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126888929</v>
+        <v>126894590</v>
       </c>
       <c r="B87" t="n">
         <v>98443</v>
@@ -9241,14 +9241,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>856800</v>
+        <v>857265</v>
       </c>
       <c r="R87" t="n">
-        <v>7485540</v>
+        <v>7485680</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9295,12 +9295,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9408,32 +9408,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126895917</v>
+        <v>126889034</v>
       </c>
       <c r="B89" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9443,13 +9443,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>857220</v>
+        <v>856998</v>
       </c>
       <c r="R89" t="n">
-        <v>7485407</v>
+        <v>7485630</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9493,12 +9493,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9610,32 +9610,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126889034</v>
+        <v>126895917</v>
       </c>
       <c r="B91" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9645,13 +9645,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>856998</v>
+        <v>857220</v>
       </c>
       <c r="R91" t="n">
-        <v>7485630</v>
+        <v>7485407</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9695,12 +9695,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9711,48 +9711,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126893327</v>
+        <v>126895962</v>
       </c>
       <c r="B92" t="n">
-        <v>91310</v>
+        <v>91326</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4660</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>857141</v>
+        <v>856927</v>
       </c>
       <c r="R92" t="n">
-        <v>7485413</v>
+        <v>7485482</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9796,26 +9796,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126889025</v>
+        <v>126893327</v>
       </c>
       <c r="B93" t="n">
-        <v>80146</v>
+        <v>91310</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9823,21 +9819,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>4660</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9847,13 +9843,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>856955</v>
+        <v>857141</v>
       </c>
       <c r="R93" t="n">
-        <v>7485682</v>
+        <v>7485413</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9897,12 +9893,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -9913,48 +9909,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126895962</v>
+        <v>126889025</v>
       </c>
       <c r="B94" t="n">
-        <v>91326</v>
+        <v>80146</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>856927</v>
+        <v>856955</v>
       </c>
       <c r="R94" t="n">
-        <v>7485482</v>
+        <v>7485682</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9998,44 +9994,48 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126889050</v>
+        <v>126893333</v>
       </c>
       <c r="B95" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10045,13 +10045,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>857208</v>
+        <v>856968</v>
       </c>
       <c r="R95" t="n">
-        <v>7485545</v>
+        <v>7485570</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10095,12 +10095,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10111,32 +10111,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126893333</v>
+        <v>126889050</v>
       </c>
       <c r="B96" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>856968</v>
+        <v>857208</v>
       </c>
       <c r="R96" t="n">
-        <v>7485570</v>
+        <v>7485545</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10196,12 +10196,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10920,32 +10920,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126889036</v>
+        <v>126893338</v>
       </c>
       <c r="B104" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10955,13 +10955,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>857182</v>
+        <v>856954</v>
       </c>
       <c r="R104" t="n">
-        <v>7485442</v>
+        <v>7485603</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11005,12 +11005,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11021,10 +11021,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126895966</v>
+        <v>126889036</v>
       </c>
       <c r="B105" t="n">
-        <v>80153</v>
+        <v>80021</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11032,40 +11032,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>856849</v>
+        <v>857182</v>
       </c>
       <c r="R105" t="n">
-        <v>7485405</v>
+        <v>7485442</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11103,29 +11100,32 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126893322</v>
+        <v>126889037</v>
       </c>
       <c r="B106" t="n">
-        <v>80146</v>
+        <v>80021</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11133,21 +11133,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11157,13 +11157,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>857015</v>
+        <v>857094</v>
       </c>
       <c r="R106" t="n">
-        <v>7485514</v>
+        <v>7485517</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11207,12 +11207,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11223,10 +11223,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126889037</v>
+        <v>126895966</v>
       </c>
       <c r="B107" t="n">
-        <v>80021</v>
+        <v>80153</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11234,37 +11234,40 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>857094</v>
+        <v>856849</v>
       </c>
       <c r="R107" t="n">
-        <v>7485517</v>
+        <v>7485405</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11302,54 +11305,51 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126893338</v>
+        <v>126893322</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11359,10 +11359,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>856954</v>
+        <v>857015</v>
       </c>
       <c r="R108" t="n">
-        <v>7485603</v>
+        <v>7485514</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11425,48 +11425,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126893324</v>
+        <v>126895975</v>
       </c>
       <c r="B109" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>856949</v>
+        <v>856864</v>
       </c>
       <c r="R109" t="n">
-        <v>7485588</v>
+        <v>7485417</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11510,48 +11510,44 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126893334</v>
+        <v>126893324</v>
       </c>
       <c r="B110" t="n">
-        <v>98443</v>
+        <v>80146</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11561,10 +11557,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>856938</v>
+        <v>856949</v>
       </c>
       <c r="R110" t="n">
-        <v>7485632</v>
+        <v>7485588</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11627,48 +11623,48 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126895975</v>
+        <v>126893334</v>
       </c>
       <c r="B111" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>856864</v>
+        <v>856938</v>
       </c>
       <c r="R111" t="n">
-        <v>7485417</v>
+        <v>7485632</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11712,22 +11708,26 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126894585</v>
+        <v>126893320</v>
       </c>
       <c r="B112" t="n">
-        <v>97327</v>
+        <v>80146</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11735,37 +11735,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>857167</v>
+        <v>857058</v>
       </c>
       <c r="R112" t="n">
-        <v>7485432</v>
+        <v>7485807</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11809,12 +11809,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -11825,10 +11825,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126893320</v>
+        <v>126894585</v>
       </c>
       <c r="B113" t="n">
-        <v>80146</v>
+        <v>97327</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11836,37 +11836,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>857058</v>
+        <v>857167</v>
       </c>
       <c r="R113" t="n">
-        <v>7485807</v>
+        <v>7485432</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11910,12 +11910,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12027,10 +12027,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126895965</v>
+        <v>126889027</v>
       </c>
       <c r="B115" t="n">
-        <v>80153</v>
+        <v>80146</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12038,37 +12038,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>856897</v>
+        <v>856947</v>
       </c>
       <c r="R115" t="n">
-        <v>7485429</v>
+        <v>7485678</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12112,60 +12112,64 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126894597</v>
+        <v>126895965</v>
       </c>
       <c r="B116" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>857222</v>
+        <v>856897</v>
       </c>
       <c r="R116" t="n">
-        <v>7485544</v>
+        <v>7485429</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12209,64 +12213,60 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126894600</v>
+        <v>126895970</v>
       </c>
       <c r="B117" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>857163</v>
+        <v>856849</v>
       </c>
       <c r="R117" t="n">
-        <v>7485497</v>
+        <v>7485559</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12310,61 +12310,57 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126889027</v>
+        <v>126894592</v>
       </c>
       <c r="B118" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>856947</v>
+        <v>857255</v>
       </c>
       <c r="R118" t="n">
-        <v>7485678</v>
+        <v>7485644</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12411,12 +12407,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12427,48 +12423,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126895970</v>
+        <v>126894597</v>
       </c>
       <c r="B119" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>856849</v>
+        <v>857222</v>
       </c>
       <c r="R119" t="n">
-        <v>7485559</v>
+        <v>7485544</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12512,44 +12508,48 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126894592</v>
+        <v>126894600</v>
       </c>
       <c r="B120" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12559,10 +12559,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>857255</v>
+        <v>857163</v>
       </c>
       <c r="R120" t="n">
-        <v>7485644</v>
+        <v>7485497</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13055,32 +13055,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126899816</v>
+        <v>126899894</v>
       </c>
       <c r="B125" t="n">
-        <v>80153</v>
+        <v>75138</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>856947</v>
+        <v>856906</v>
       </c>
       <c r="R125" t="n">
-        <v>7485478</v>
+        <v>7485559</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13145,7 +13145,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13156,32 +13156,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126899894</v>
+        <v>126899816</v>
       </c>
       <c r="B126" t="n">
-        <v>75138</v>
+        <v>80153</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13191,10 +13191,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>856906</v>
+        <v>856947</v>
       </c>
       <c r="R126" t="n">
-        <v>7485559</v>
+        <v>7485478</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -15205,38 +15205,52 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127150856</v>
+        <v>127155655</v>
       </c>
       <c r="B145" t="n">
-        <v>56849</v>
+        <v>41361</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100138</v>
+        <v>215713</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -15245,13 +15259,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R145" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15280,7 +15294,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15290,7 +15304,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15313,60 +15327,42 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127155655</v>
+        <v>127150856</v>
       </c>
       <c r="B146" t="n">
-        <v>41361</v>
+        <v>56849</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>215713</v>
+        <v>100138</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -15375,13 +15371,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R146" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S146" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15410,7 +15406,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15420,7 +15416,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15443,7 +15439,11 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY146" t="inlineStr"/>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16119,51 +16119,48 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126895800</v>
+        <v>127272276</v>
       </c>
       <c r="B153" t="n">
-        <v>79014</v>
+        <v>80083</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>856984</v>
+        <v>856765</v>
       </c>
       <c r="R153" t="n">
-        <v>7485301</v>
+        <v>7485445</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16190,18 +16187,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16224,48 +16230,51 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127272276</v>
+        <v>126895800</v>
       </c>
       <c r="B154" t="n">
-        <v>80083</v>
+        <v>79014</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>856765</v>
+        <v>856984</v>
       </c>
       <c r="R154" t="n">
-        <v>7485445</v>
+        <v>7485301</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16292,27 +16301,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -1877,32 +1877,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126728181</v>
+        <v>126728179</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>857024</v>
+        <v>857020</v>
       </c>
       <c r="R14" t="n">
-        <v>7485613</v>
+        <v>7485779</v>
       </c>
       <c r="S14" t="n">
         <v>14</v>
@@ -1974,45 +1974,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126722469</v>
+        <v>126722237</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>857037</v>
+        <v>856991</v>
       </c>
       <c r="R15" t="n">
-        <v>7485805</v>
+        <v>7485798</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,32 +2080,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126728179</v>
+        <v>126728181</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>857020</v>
+        <v>857024</v>
       </c>
       <c r="R16" t="n">
-        <v>7485779</v>
+        <v>7485613</v>
       </c>
       <c r="S16" t="n">
         <v>14</v>
@@ -2168,54 +2177,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126722237</v>
+        <v>126722469</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>856991</v>
+        <v>857037</v>
       </c>
       <c r="R17" t="n">
-        <v>7485798</v>
+        <v>7485805</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889016</v>
+        <v>126893335</v>
       </c>
       <c r="B31" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>857042</v>
+        <v>857254</v>
       </c>
       <c r="R31" t="n">
-        <v>7485656</v>
+        <v>7485706</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3638,12 +3638,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3654,7 +3654,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893321</v>
+        <v>126889016</v>
       </c>
       <c r="B32" t="n">
         <v>80146</v>
@@ -3689,13 +3689,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>857154</v>
+        <v>857042</v>
       </c>
       <c r="R32" t="n">
-        <v>7485805</v>
+        <v>7485656</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3739,12 +3739,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3755,7 +3755,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126895913</v>
+        <v>126893321</v>
       </c>
       <c r="B33" t="n">
         <v>80146</v>
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>857071</v>
+        <v>857154</v>
       </c>
       <c r="R33" t="n">
-        <v>7485419</v>
+        <v>7485805</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3840,12 +3840,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3856,32 +3856,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126893335</v>
+        <v>126895913</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857254</v>
+        <v>857071</v>
       </c>
       <c r="R34" t="n">
-        <v>7485706</v>
+        <v>7485419</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3941,12 +3941,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -6386,32 +6386,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126889013</v>
+        <v>126889052</v>
       </c>
       <c r="B59" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>857038</v>
+        <v>857206</v>
       </c>
       <c r="R59" t="n">
-        <v>7485632</v>
+        <v>7485553</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6487,7 +6487,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126894581</v>
+        <v>126889013</v>
       </c>
       <c r="B60" t="n">
         <v>80146</v>
@@ -6518,14 +6518,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>857009</v>
+        <v>857038</v>
       </c>
       <c r="R60" t="n">
-        <v>7485612</v>
+        <v>7485632</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6572,12 +6572,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6588,45 +6588,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126889052</v>
+        <v>126894581</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>857206</v>
+        <v>857009</v>
       </c>
       <c r="R61" t="n">
-        <v>7485553</v>
+        <v>7485612</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6673,12 +6673,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6790,32 +6790,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126895921</v>
+        <v>126895915</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6825,10 +6825,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>857123</v>
+        <v>857242</v>
       </c>
       <c r="R63" t="n">
-        <v>7485402</v>
+        <v>7485724</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -6891,48 +6891,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126895961</v>
+        <v>126889041</v>
       </c>
       <c r="B64" t="n">
-        <v>75138</v>
+        <v>98443</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>856840</v>
+        <v>856978</v>
       </c>
       <c r="R64" t="n">
-        <v>7485479</v>
+        <v>7485792</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6976,60 +6976,64 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126895915</v>
+        <v>126894583</v>
       </c>
       <c r="B65" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>857242</v>
+        <v>856988</v>
       </c>
       <c r="R65" t="n">
-        <v>7485724</v>
+        <v>7485572</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7073,12 +7077,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7089,32 +7093,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126889041</v>
+        <v>126889032</v>
       </c>
       <c r="B66" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7124,10 +7128,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>856978</v>
+        <v>857038</v>
       </c>
       <c r="R66" t="n">
-        <v>7485792</v>
+        <v>7485636</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7190,48 +7194,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126894583</v>
+        <v>126895921</v>
       </c>
       <c r="B67" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>856988</v>
+        <v>857123</v>
       </c>
       <c r="R67" t="n">
-        <v>7485572</v>
+        <v>7485402</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7275,12 +7279,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7291,48 +7295,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126889032</v>
+        <v>126895961</v>
       </c>
       <c r="B68" t="n">
-        <v>98464</v>
+        <v>75138</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>857038</v>
+        <v>856840</v>
       </c>
       <c r="R68" t="n">
-        <v>7485636</v>
+        <v>7485479</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7376,48 +7380,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126895920</v>
+        <v>126895910</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>857173</v>
+        <v>856984</v>
       </c>
       <c r="R69" t="n">
-        <v>7485506</v>
+        <v>7485600</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -7493,32 +7493,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126895922</v>
+        <v>126889021</v>
       </c>
       <c r="B70" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>856981</v>
+        <v>857000</v>
       </c>
       <c r="R70" t="n">
-        <v>7485578</v>
+        <v>7485629</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7578,12 +7578,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7594,7 +7594,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126895910</v>
+        <v>126889024</v>
       </c>
       <c r="B71" t="n">
         <v>80146</v>
@@ -7629,13 +7629,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>856984</v>
+        <v>856962</v>
       </c>
       <c r="R71" t="n">
-        <v>7485600</v>
+        <v>7485641</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7679,12 +7679,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7695,32 +7695,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126889021</v>
+        <v>126889045</v>
       </c>
       <c r="B72" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7730,10 +7730,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>857000</v>
+        <v>857084</v>
       </c>
       <c r="R72" t="n">
-        <v>7485629</v>
+        <v>7485530</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7796,32 +7796,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126889024</v>
+        <v>126889047</v>
       </c>
       <c r="B73" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>856962</v>
+        <v>857010</v>
       </c>
       <c r="R73" t="n">
-        <v>7485641</v>
+        <v>7485585</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7897,32 +7897,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126889045</v>
+        <v>126895920</v>
       </c>
       <c r="B74" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7932,13 +7932,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>857084</v>
+        <v>857173</v>
       </c>
       <c r="R74" t="n">
-        <v>7485530</v>
+        <v>7485506</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7982,12 +7982,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -7998,32 +7998,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126889047</v>
+        <v>126895922</v>
       </c>
       <c r="B75" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8033,13 +8033,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>857010</v>
+        <v>856981</v>
       </c>
       <c r="R75" t="n">
-        <v>7485585</v>
+        <v>7485578</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8083,12 +8083,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8705,32 +8705,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126888931</v>
+        <v>126893339</v>
       </c>
       <c r="B82" t="n">
-        <v>91900</v>
+        <v>79014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8740,13 +8740,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>856896</v>
+        <v>857104</v>
       </c>
       <c r="R82" t="n">
-        <v>7485431</v>
+        <v>7485447</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8790,12 +8790,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8806,7 +8806,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126893339</v>
+        <v>126894601</v>
       </c>
       <c r="B83" t="n">
         <v>79014</v>
@@ -8837,17 +8837,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>857104</v>
+        <v>857215</v>
       </c>
       <c r="R83" t="n">
-        <v>7485447</v>
+        <v>7485457</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8891,12 +8891,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8907,45 +8907,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126894601</v>
+        <v>126889019</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>857215</v>
+        <v>857016</v>
       </c>
       <c r="R84" t="n">
-        <v>7485457</v>
+        <v>7485635</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8992,12 +8992,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9008,32 +9008,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126889019</v>
+        <v>126888931</v>
       </c>
       <c r="B85" t="n">
-        <v>80146</v>
+        <v>91900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9043,10 +9043,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>857016</v>
+        <v>856896</v>
       </c>
       <c r="R85" t="n">
-        <v>7485635</v>
+        <v>7485431</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9093,12 +9093,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9311,48 +9311,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126895973</v>
+        <v>126895917</v>
       </c>
       <c r="B88" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>856707</v>
+        <v>857220</v>
       </c>
       <c r="R88" t="n">
-        <v>7485577</v>
+        <v>7485407</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9396,22 +9396,26 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126889034</v>
+        <v>126889017</v>
       </c>
       <c r="B89" t="n">
-        <v>98464</v>
+        <v>80146</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9419,21 +9423,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9443,10 +9447,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>856998</v>
+        <v>857021</v>
       </c>
       <c r="R89" t="n">
-        <v>7485630</v>
+        <v>7485648</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9509,48 +9513,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126889017</v>
+        <v>126895973</v>
       </c>
       <c r="B90" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>857021</v>
+        <v>856707</v>
       </c>
       <c r="R90" t="n">
-        <v>7485648</v>
+        <v>7485577</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9594,48 +9598,44 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126895917</v>
+        <v>126889034</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9645,13 +9645,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>857220</v>
+        <v>856998</v>
       </c>
       <c r="R91" t="n">
-        <v>7485407</v>
+        <v>7485630</v>
       </c>
       <c r="S91" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9695,12 +9695,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10010,32 +10010,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126893333</v>
+        <v>126889050</v>
       </c>
       <c r="B95" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10045,13 +10045,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>856968</v>
+        <v>857208</v>
       </c>
       <c r="R95" t="n">
-        <v>7485570</v>
+        <v>7485545</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10095,12 +10095,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10111,32 +10111,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126889050</v>
+        <v>126893323</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>857208</v>
+        <v>856995</v>
       </c>
       <c r="R96" t="n">
-        <v>7485545</v>
+        <v>7485538</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10196,12 +10196,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10212,7 +10212,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126893323</v>
+        <v>126893325</v>
       </c>
       <c r="B97" t="n">
         <v>80146</v>
@@ -10247,10 +10247,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>856995</v>
+        <v>856884</v>
       </c>
       <c r="R97" t="n">
-        <v>7485538</v>
+        <v>7485698</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10313,7 +10313,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126893325</v>
+        <v>126895914</v>
       </c>
       <c r="B98" t="n">
         <v>80146</v>
@@ -10348,13 +10348,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>856884</v>
+        <v>856958</v>
       </c>
       <c r="R98" t="n">
-        <v>7485698</v>
+        <v>7485679</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10398,12 +10398,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10414,32 +10414,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126895914</v>
+        <v>126893333</v>
       </c>
       <c r="B99" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10449,13 +10449,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>856958</v>
+        <v>856968</v>
       </c>
       <c r="R99" t="n">
-        <v>7485679</v>
+        <v>7485570</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10499,12 +10499,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -1877,32 +1877,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126728179</v>
+        <v>126728181</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>857020</v>
+        <v>857024</v>
       </c>
       <c r="R14" t="n">
-        <v>7485779</v>
+        <v>7485613</v>
       </c>
       <c r="S14" t="n">
         <v>14</v>
@@ -1974,54 +1974,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126722237</v>
+        <v>126722469</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>856991</v>
+        <v>857037</v>
       </c>
       <c r="R15" t="n">
-        <v>7485798</v>
+        <v>7485805</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,32 +2071,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126728181</v>
+        <v>126728179</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>857024</v>
+        <v>857020</v>
       </c>
       <c r="R16" t="n">
-        <v>7485613</v>
+        <v>7485779</v>
       </c>
       <c r="S16" t="n">
         <v>14</v>
@@ -2177,45 +2168,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126722469</v>
+        <v>126722237</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>857037</v>
+        <v>856991</v>
       </c>
       <c r="R17" t="n">
-        <v>7485805</v>
+        <v>7485798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,45 +2371,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126722312</v>
+        <v>126722838</v>
       </c>
       <c r="B19" t="n">
-        <v>91276</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>857016</v>
+        <v>857027</v>
       </c>
       <c r="R19" t="n">
-        <v>7485810</v>
+        <v>7485680</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2468,7 +2477,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126722838</v>
+        <v>126722552</v>
       </c>
       <c r="B20" t="n">
         <v>98443</v>
@@ -2496,26 +2505,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Aihkivinsa, Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>857027</v>
+        <v>857113</v>
       </c>
       <c r="R20" t="n">
-        <v>7485680</v>
+        <v>7485787</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2574,32 +2574,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126722552</v>
+        <v>126722312</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>91276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>857113</v>
+        <v>857016</v>
       </c>
       <c r="R21" t="n">
-        <v>7485787</v>
+        <v>7485810</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126893335</v>
+        <v>126889016</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>857254</v>
+        <v>857042</v>
       </c>
       <c r="R31" t="n">
-        <v>7485706</v>
+        <v>7485656</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3638,12 +3638,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3654,7 +3654,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889016</v>
+        <v>126893321</v>
       </c>
       <c r="B32" t="n">
         <v>80146</v>
@@ -3689,13 +3689,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>857042</v>
+        <v>857154</v>
       </c>
       <c r="R32" t="n">
-        <v>7485656</v>
+        <v>7485805</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3739,12 +3739,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3755,7 +3755,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126893321</v>
+        <v>126895913</v>
       </c>
       <c r="B33" t="n">
         <v>80146</v>
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>857154</v>
+        <v>857071</v>
       </c>
       <c r="R33" t="n">
-        <v>7485805</v>
+        <v>7485419</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3840,12 +3840,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3856,32 +3856,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126895913</v>
+        <v>126893335</v>
       </c>
       <c r="B34" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857071</v>
+        <v>857254</v>
       </c>
       <c r="R34" t="n">
-        <v>7485419</v>
+        <v>7485706</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3941,12 +3941,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -5880,48 +5880,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893336</v>
+        <v>126895972</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>857022</v>
+        <v>856725</v>
       </c>
       <c r="R54" t="n">
-        <v>7485521</v>
+        <v>7485571</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5965,48 +5965,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126888926</v>
+        <v>126893336</v>
       </c>
       <c r="B55" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,13 +6012,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>856904</v>
+        <v>857022</v>
       </c>
       <c r="R55" t="n">
-        <v>7485446</v>
+        <v>7485521</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6066,12 +6062,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6082,32 +6078,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893326</v>
+        <v>126888926</v>
       </c>
       <c r="B56" t="n">
-        <v>57654</v>
+        <v>80153</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6117,13 +6113,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>857089</v>
+        <v>856904</v>
       </c>
       <c r="R56" t="n">
-        <v>7485450</v>
+        <v>7485446</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6153,11 +6149,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6172,12 +6163,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6188,48 +6179,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126895972</v>
+        <v>126893326</v>
       </c>
       <c r="B57" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>856725</v>
+        <v>857089</v>
       </c>
       <c r="R57" t="n">
-        <v>7485571</v>
+        <v>7485450</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6259,6 +6250,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6273,15 +6269,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6386,32 +6386,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126889052</v>
+        <v>126889013</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>857206</v>
+        <v>857038</v>
       </c>
       <c r="R59" t="n">
-        <v>7485553</v>
+        <v>7485632</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6487,7 +6487,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126889013</v>
+        <v>126894581</v>
       </c>
       <c r="B60" t="n">
         <v>80146</v>
@@ -6518,14 +6518,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>857038</v>
+        <v>857009</v>
       </c>
       <c r="R60" t="n">
-        <v>7485632</v>
+        <v>7485612</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6572,12 +6572,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6588,45 +6588,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126894581</v>
+        <v>126889052</v>
       </c>
       <c r="B61" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>857009</v>
+        <v>857206</v>
       </c>
       <c r="R61" t="n">
-        <v>7485612</v>
+        <v>7485553</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6673,12 +6673,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6790,32 +6790,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126895915</v>
+        <v>126895921</v>
       </c>
       <c r="B63" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6825,10 +6825,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>857242</v>
+        <v>857123</v>
       </c>
       <c r="R63" t="n">
-        <v>7485724</v>
+        <v>7485402</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -6891,48 +6891,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126889041</v>
+        <v>126895961</v>
       </c>
       <c r="B64" t="n">
-        <v>98443</v>
+        <v>75138</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>856978</v>
+        <v>856840</v>
       </c>
       <c r="R64" t="n">
-        <v>7485792</v>
+        <v>7485479</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6976,64 +6976,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126894583</v>
+        <v>126895915</v>
       </c>
       <c r="B65" t="n">
-        <v>98464</v>
+        <v>98443</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>856988</v>
+        <v>857242</v>
       </c>
       <c r="R65" t="n">
-        <v>7485572</v>
+        <v>7485724</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7077,12 +7073,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7093,32 +7089,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126889032</v>
+        <v>126889041</v>
       </c>
       <c r="B66" t="n">
-        <v>98464</v>
+        <v>98443</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7128,10 +7124,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>857038</v>
+        <v>856978</v>
       </c>
       <c r="R66" t="n">
-        <v>7485636</v>
+        <v>7485792</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7194,48 +7190,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126895921</v>
+        <v>126894583</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>857123</v>
+        <v>856988</v>
       </c>
       <c r="R67" t="n">
-        <v>7485402</v>
+        <v>7485572</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7279,12 +7275,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7295,48 +7291,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126895961</v>
+        <v>126889032</v>
       </c>
       <c r="B68" t="n">
-        <v>75138</v>
+        <v>98464</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>856840</v>
+        <v>857038</v>
       </c>
       <c r="R68" t="n">
-        <v>7485479</v>
+        <v>7485636</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7380,15 +7376,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8705,32 +8705,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126893339</v>
+        <v>126888931</v>
       </c>
       <c r="B82" t="n">
-        <v>79014</v>
+        <v>91900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8740,13 +8740,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>857104</v>
+        <v>856896</v>
       </c>
       <c r="R82" t="n">
-        <v>7485447</v>
+        <v>7485431</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8790,12 +8790,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8806,7 +8806,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126894601</v>
+        <v>126893339</v>
       </c>
       <c r="B83" t="n">
         <v>79014</v>
@@ -8837,17 +8837,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>857215</v>
+        <v>857104</v>
       </c>
       <c r="R83" t="n">
-        <v>7485457</v>
+        <v>7485447</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8891,12 +8891,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8907,45 +8907,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126889019</v>
+        <v>126894601</v>
       </c>
       <c r="B84" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>857016</v>
+        <v>857215</v>
       </c>
       <c r="R84" t="n">
-        <v>7485635</v>
+        <v>7485457</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8992,12 +8992,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9008,32 +9008,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126888931</v>
+        <v>126889019</v>
       </c>
       <c r="B85" t="n">
-        <v>91900</v>
+        <v>80146</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9043,10 +9043,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>856896</v>
+        <v>857016</v>
       </c>
       <c r="R85" t="n">
-        <v>7485431</v>
+        <v>7485635</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9093,12 +9093,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -10010,32 +10010,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126889050</v>
+        <v>126893333</v>
       </c>
       <c r="B95" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10045,13 +10045,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>857208</v>
+        <v>856968</v>
       </c>
       <c r="R95" t="n">
-        <v>7485545</v>
+        <v>7485570</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10095,12 +10095,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10111,32 +10111,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126893323</v>
+        <v>126889050</v>
       </c>
       <c r="B96" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>856995</v>
+        <v>857208</v>
       </c>
       <c r="R96" t="n">
-        <v>7485538</v>
+        <v>7485545</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10196,12 +10196,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10212,7 +10212,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126893325</v>
+        <v>126893323</v>
       </c>
       <c r="B97" t="n">
         <v>80146</v>
@@ -10247,10 +10247,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>856884</v>
+        <v>856995</v>
       </c>
       <c r="R97" t="n">
-        <v>7485698</v>
+        <v>7485538</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10313,7 +10313,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126895914</v>
+        <v>126893325</v>
       </c>
       <c r="B98" t="n">
         <v>80146</v>
@@ -10348,13 +10348,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>856958</v>
+        <v>856884</v>
       </c>
       <c r="R98" t="n">
-        <v>7485679</v>
+        <v>7485698</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10398,12 +10398,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10414,32 +10414,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126893333</v>
+        <v>126895914</v>
       </c>
       <c r="B99" t="n">
-        <v>98443</v>
+        <v>80146</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10449,13 +10449,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>856968</v>
+        <v>856958</v>
       </c>
       <c r="R99" t="n">
-        <v>7485570</v>
+        <v>7485679</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10499,12 +10499,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11724,32 +11724,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126893320</v>
+        <v>126893329</v>
       </c>
       <c r="B112" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11759,10 +11759,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>857058</v>
+        <v>857202</v>
       </c>
       <c r="R112" t="n">
-        <v>7485807</v>
+        <v>7485431</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11926,32 +11926,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126893329</v>
+        <v>126893320</v>
       </c>
       <c r="B114" t="n">
-        <v>98443</v>
+        <v>80146</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11961,10 +11961,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>857202</v>
+        <v>857058</v>
       </c>
       <c r="R114" t="n">
-        <v>7485431</v>
+        <v>7485807</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12027,45 +12027,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126889027</v>
+        <v>126894597</v>
       </c>
       <c r="B115" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>856947</v>
+        <v>857222</v>
       </c>
       <c r="R115" t="n">
-        <v>7485678</v>
+        <v>7485544</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12112,12 +12112,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12128,48 +12128,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126895965</v>
+        <v>126894600</v>
       </c>
       <c r="B116" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>856897</v>
+        <v>857163</v>
       </c>
       <c r="R116" t="n">
-        <v>7485429</v>
+        <v>7485497</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12213,60 +12213,64 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126895970</v>
+        <v>126889027</v>
       </c>
       <c r="B117" t="n">
-        <v>98443</v>
+        <v>80146</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>856849</v>
+        <v>856947</v>
       </c>
       <c r="R117" t="n">
-        <v>7485559</v>
+        <v>7485678</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12310,60 +12314,64 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126894592</v>
+        <v>126895965</v>
       </c>
       <c r="B118" t="n">
-        <v>98443</v>
+        <v>80153</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>857255</v>
+        <v>856897</v>
       </c>
       <c r="R118" t="n">
-        <v>7485644</v>
+        <v>7485429</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12407,64 +12415,60 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126894597</v>
+        <v>126895970</v>
       </c>
       <c r="B119" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>857222</v>
+        <v>856849</v>
       </c>
       <c r="R119" t="n">
-        <v>7485544</v>
+        <v>7485559</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12508,48 +12512,44 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126894600</v>
+        <v>126894592</v>
       </c>
       <c r="B120" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12559,10 +12559,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>857163</v>
+        <v>857255</v>
       </c>
       <c r="R120" t="n">
-        <v>7485497</v>
+        <v>7485644</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14218,45 +14218,57 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126899901</v>
+        <v>126899819</v>
       </c>
       <c r="B136" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>856929</v>
+        <v>856846</v>
       </c>
       <c r="R136" t="n">
-        <v>7485563</v>
+        <v>7485645</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14297,6 +14309,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14308,7 +14321,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14319,57 +14332,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126899819</v>
+        <v>126899901</v>
       </c>
       <c r="B137" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>856846</v>
+        <v>856929</v>
       </c>
       <c r="R137" t="n">
-        <v>7485645</v>
+        <v>7485563</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14410,7 +14411,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889016</v>
+        <v>126893335</v>
       </c>
       <c r="B31" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>857042</v>
+        <v>857254</v>
       </c>
       <c r="R31" t="n">
-        <v>7485656</v>
+        <v>7485706</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3638,12 +3638,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3654,48 +3654,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893321</v>
+        <v>126894596</v>
       </c>
       <c r="B32" t="n">
-        <v>80146</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>857154</v>
+        <v>857232</v>
       </c>
       <c r="R32" t="n">
-        <v>7485805</v>
+        <v>7485521</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3739,12 +3739,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3755,10 +3755,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126895913</v>
+        <v>126889016</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>857071</v>
+        <v>857042</v>
       </c>
       <c r="R33" t="n">
-        <v>7485419</v>
+        <v>7485656</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3840,12 +3840,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3856,32 +3856,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126893335</v>
+        <v>126893321</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>80150</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857254</v>
+        <v>857154</v>
       </c>
       <c r="R34" t="n">
-        <v>7485706</v>
+        <v>7485805</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3957,48 +3957,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126894596</v>
+        <v>126895913</v>
       </c>
       <c r="B35" t="n">
-        <v>98443</v>
+        <v>80150</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>857232</v>
+        <v>857071</v>
       </c>
       <c r="R35" t="n">
-        <v>7485521</v>
+        <v>7485419</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4058,10 +4058,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126893328</v>
+        <v>126894580</v>
       </c>
       <c r="B36" t="n">
-        <v>80153</v>
+        <v>80150</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4069,37 +4069,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>856959</v>
+        <v>857065</v>
       </c>
       <c r="R36" t="n">
-        <v>7485620</v>
+        <v>7485568</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4143,12 +4143,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4159,10 +4159,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126894580</v>
+        <v>126893328</v>
       </c>
       <c r="B37" t="n">
-        <v>80146</v>
+        <v>80157</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4170,37 +4170,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>857065</v>
+        <v>856959</v>
       </c>
       <c r="R37" t="n">
-        <v>7485568</v>
+        <v>7485620</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4244,12 +4244,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4263,7 +4263,7 @@
         <v>126893330</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>126895971</v>
       </c>
       <c r="B39" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>126894589</v>
       </c>
       <c r="B40" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>126889022</v>
       </c>
       <c r="B41" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>126894594</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>126889042</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>126894588</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>126895969</v>
       </c>
       <c r="B45" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>126893332</v>
       </c>
       <c r="B46" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126894582</v>
+        <v>126895963</v>
       </c>
       <c r="B47" t="n">
-        <v>80146</v>
+        <v>98468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5177,37 +5177,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>856922</v>
+        <v>856930</v>
       </c>
       <c r="R47" t="n">
-        <v>7485635</v>
+        <v>7485560</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>på Sälg</t>
+          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5256,26 +5256,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>126895968</v>
       </c>
       <c r="B48" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5377,7 +5373,7 @@
         <v>126889044</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5478,7 +5474,7 @@
         <v>126888927</v>
       </c>
       <c r="B50" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5579,7 +5575,7 @@
         <v>126895916</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5680,7 +5676,7 @@
         <v>126888930</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5778,10 +5774,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126895963</v>
+        <v>126894582</v>
       </c>
       <c r="B53" t="n">
-        <v>98464</v>
+        <v>80150</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5789,37 +5785,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>856930</v>
+        <v>856922</v>
       </c>
       <c r="R53" t="n">
-        <v>7485560</v>
+        <v>7485635</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5853,7 +5849,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
+          <t>på Sälg</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5868,22 +5864,26 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>126895972</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>126893336</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6078,32 +6078,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126888926</v>
+        <v>126893326</v>
       </c>
       <c r="B56" t="n">
-        <v>80153</v>
+        <v>57658</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,13 +6113,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>856904</v>
+        <v>857089</v>
       </c>
       <c r="R56" t="n">
-        <v>7485446</v>
+        <v>7485450</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6149,6 +6149,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6163,12 +6168,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6179,32 +6184,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126893326</v>
+        <v>126888926</v>
       </c>
       <c r="B57" t="n">
-        <v>57654</v>
+        <v>80157</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6214,13 +6219,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>857089</v>
+        <v>856904</v>
       </c>
       <c r="R57" t="n">
-        <v>7485450</v>
+        <v>7485446</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6250,11 +6255,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6269,12 +6269,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6288,7 +6288,7 @@
         <v>126893319</v>
       </c>
       <c r="B58" t="n">
-        <v>91501</v>
+        <v>91505</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>126889013</v>
       </c>
       <c r="B59" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>126894581</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>126889052</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>126888928</v>
       </c>
       <c r="B62" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>126895921</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6891,48 +6891,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126895961</v>
+        <v>126895915</v>
       </c>
       <c r="B64" t="n">
-        <v>75138</v>
+        <v>98447</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>856840</v>
+        <v>857242</v>
       </c>
       <c r="R64" t="n">
-        <v>7485479</v>
+        <v>7485724</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6976,22 +6976,26 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126895915</v>
+        <v>126889041</v>
       </c>
       <c r="B65" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7023,13 +7027,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>857242</v>
+        <v>856978</v>
       </c>
       <c r="R65" t="n">
-        <v>7485724</v>
+        <v>7485792</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7073,12 +7077,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7089,48 +7093,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126889041</v>
+        <v>126895961</v>
       </c>
       <c r="B66" t="n">
-        <v>98443</v>
+        <v>75142</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>856978</v>
+        <v>856840</v>
       </c>
       <c r="R66" t="n">
-        <v>7485792</v>
+        <v>7485479</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7174,26 +7178,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>126894583</v>
       </c>
       <c r="B67" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>126889032</v>
       </c>
       <c r="B68" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>126895910</v>
       </c>
       <c r="B69" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7493,32 +7493,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126889021</v>
+        <v>126895920</v>
       </c>
       <c r="B70" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>857000</v>
+        <v>857173</v>
       </c>
       <c r="R70" t="n">
-        <v>7485629</v>
+        <v>7485506</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7578,12 +7578,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7594,32 +7594,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126889024</v>
+        <v>126895922</v>
       </c>
       <c r="B71" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7629,13 +7629,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>856962</v>
+        <v>856981</v>
       </c>
       <c r="R71" t="n">
-        <v>7485641</v>
+        <v>7485578</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7679,12 +7679,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7695,32 +7695,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126889045</v>
+        <v>126889021</v>
       </c>
       <c r="B72" t="n">
-        <v>98443</v>
+        <v>80150</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7730,10 +7730,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>857084</v>
+        <v>857000</v>
       </c>
       <c r="R72" t="n">
-        <v>7485530</v>
+        <v>7485629</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7796,32 +7796,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126889047</v>
+        <v>126889024</v>
       </c>
       <c r="B73" t="n">
-        <v>98443</v>
+        <v>80150</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>857010</v>
+        <v>856962</v>
       </c>
       <c r="R73" t="n">
-        <v>7485585</v>
+        <v>7485641</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7897,32 +7897,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126895920</v>
+        <v>126889045</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7932,13 +7932,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>857173</v>
+        <v>857084</v>
       </c>
       <c r="R74" t="n">
-        <v>7485506</v>
+        <v>7485530</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7982,12 +7982,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -7998,32 +7998,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126895922</v>
+        <v>126889047</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8033,13 +8033,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>856981</v>
+        <v>857010</v>
       </c>
       <c r="R75" t="n">
-        <v>7485578</v>
+        <v>7485585</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8083,12 +8083,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8102,7 +8102,7 @@
         <v>126889029</v>
       </c>
       <c r="B76" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8200,32 +8200,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126894584</v>
+        <v>126894602</v>
       </c>
       <c r="B77" t="n">
-        <v>97327</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>857231</v>
+        <v>857075</v>
       </c>
       <c r="R77" t="n">
-        <v>7485574</v>
+        <v>7485539</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8301,10 +8301,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126889039</v>
+        <v>126894584</v>
       </c>
       <c r="B78" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8332,14 +8332,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>857184</v>
+        <v>857231</v>
       </c>
       <c r="R78" t="n">
-        <v>7485414</v>
+        <v>7485574</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8386,12 +8386,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8402,45 +8402,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126894602</v>
+        <v>126889039</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>97331</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>857075</v>
+        <v>857184</v>
       </c>
       <c r="R79" t="n">
-        <v>7485539</v>
+        <v>7485414</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8487,12 +8487,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8503,32 +8503,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126895918</v>
+        <v>126895912</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>80150</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>857150</v>
+        <v>857018</v>
       </c>
       <c r="R80" t="n">
-        <v>7485418</v>
+        <v>7485408</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -8604,32 +8604,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126895912</v>
+        <v>126895918</v>
       </c>
       <c r="B81" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>857018</v>
+        <v>857150</v>
       </c>
       <c r="R81" t="n">
-        <v>7485408</v>
+        <v>7485418</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -8708,7 +8708,7 @@
         <v>126888931</v>
       </c>
       <c r="B82" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>126893339</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>126894601</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>126889019</v>
       </c>
       <c r="B85" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>126888929</v>
       </c>
       <c r="B86" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>126894590</v>
       </c>
       <c r="B87" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>126895917</v>
       </c>
       <c r="B88" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>126889017</v>
       </c>
       <c r="B89" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>126895973</v>
       </c>
       <c r="B90" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>126889034</v>
       </c>
       <c r="B91" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9711,48 +9711,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126895962</v>
+        <v>126893327</v>
       </c>
       <c r="B92" t="n">
-        <v>91326</v>
+        <v>91314</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>856927</v>
+        <v>857141</v>
       </c>
       <c r="R92" t="n">
-        <v>7485482</v>
+        <v>7485413</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9796,22 +9796,26 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126893327</v>
+        <v>126889025</v>
       </c>
       <c r="B93" t="n">
-        <v>91310</v>
+        <v>80150</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9819,21 +9823,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4660</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9843,13 +9847,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>857141</v>
+        <v>856955</v>
       </c>
       <c r="R93" t="n">
-        <v>7485413</v>
+        <v>7485682</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9893,12 +9897,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -9909,48 +9913,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126889025</v>
+        <v>126895962</v>
       </c>
       <c r="B94" t="n">
-        <v>80146</v>
+        <v>91330</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>856955</v>
+        <v>856927</v>
       </c>
       <c r="R94" t="n">
-        <v>7485682</v>
+        <v>7485482</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9994,48 +9998,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126893333</v>
+        <v>126893323</v>
       </c>
       <c r="B95" t="n">
-        <v>98443</v>
+        <v>80150</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10045,10 +10045,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>856968</v>
+        <v>856995</v>
       </c>
       <c r="R95" t="n">
-        <v>7485570</v>
+        <v>7485538</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10111,32 +10111,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126889050</v>
+        <v>126893325</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>80150</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>857208</v>
+        <v>856884</v>
       </c>
       <c r="R96" t="n">
-        <v>7485545</v>
+        <v>7485698</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10196,12 +10196,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10212,10 +10212,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126893323</v>
+        <v>126895914</v>
       </c>
       <c r="B97" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10247,13 +10247,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>856995</v>
+        <v>856958</v>
       </c>
       <c r="R97" t="n">
-        <v>7485538</v>
+        <v>7485679</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10297,12 +10297,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10313,32 +10313,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126893325</v>
+        <v>126889050</v>
       </c>
       <c r="B98" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10348,13 +10348,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>856884</v>
+        <v>857208</v>
       </c>
       <c r="R98" t="n">
-        <v>7485698</v>
+        <v>7485545</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10398,12 +10398,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10414,32 +10414,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126895914</v>
+        <v>126893333</v>
       </c>
       <c r="B99" t="n">
-        <v>80146</v>
+        <v>98447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10449,13 +10449,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>856958</v>
+        <v>856968</v>
       </c>
       <c r="R99" t="n">
-        <v>7485679</v>
+        <v>7485570</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10499,12 +10499,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10518,7 +10518,7 @@
         <v>126895911</v>
       </c>
       <c r="B100" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>126894595</v>
       </c>
       <c r="B101" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>126889049</v>
       </c>
       <c r="B102" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>126895967</v>
       </c>
       <c r="B103" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>126893338</v>
       </c>
       <c r="B104" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>126889036</v>
       </c>
       <c r="B105" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11122,10 +11122,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126889037</v>
+        <v>126893322</v>
       </c>
       <c r="B106" t="n">
-        <v>80021</v>
+        <v>80150</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11133,21 +11133,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11157,13 +11157,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>857094</v>
+        <v>857015</v>
       </c>
       <c r="R106" t="n">
-        <v>7485517</v>
+        <v>7485514</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11207,12 +11207,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11223,10 +11223,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126895966</v>
+        <v>126889037</v>
       </c>
       <c r="B107" t="n">
-        <v>80153</v>
+        <v>80025</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11234,40 +11234,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>856849</v>
+        <v>857094</v>
       </c>
       <c r="R107" t="n">
-        <v>7485405</v>
+        <v>7485517</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11305,29 +11302,32 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126893322</v>
+        <v>126895966</v>
       </c>
       <c r="B108" t="n">
-        <v>80146</v>
+        <v>80157</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11335,37 +11335,40 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>857015</v>
+        <v>856849</v>
       </c>
       <c r="R108" t="n">
-        <v>7485514</v>
+        <v>7485405</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11403,70 +11406,67 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126895975</v>
+        <v>126893334</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>856864</v>
+        <v>856938</v>
       </c>
       <c r="R109" t="n">
-        <v>7485417</v>
+        <v>7485632</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11510,60 +11510,64 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126893324</v>
+        <v>126895975</v>
       </c>
       <c r="B110" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>856949</v>
+        <v>856864</v>
       </c>
       <c r="R110" t="n">
-        <v>7485588</v>
+        <v>7485417</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11607,48 +11611,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126893334</v>
+        <v>126893324</v>
       </c>
       <c r="B111" t="n">
-        <v>98443</v>
+        <v>80150</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11658,10 +11658,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>856938</v>
+        <v>856949</v>
       </c>
       <c r="R111" t="n">
-        <v>7485632</v>
+        <v>7485588</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11727,7 +11727,7 @@
         <v>126893329</v>
       </c>
       <c r="B112" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126894585</v>
+        <v>126893320</v>
       </c>
       <c r="B113" t="n">
-        <v>97327</v>
+        <v>80150</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11836,37 +11836,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>857167</v>
+        <v>857058</v>
       </c>
       <c r="R113" t="n">
-        <v>7485432</v>
+        <v>7485807</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11910,12 +11910,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -11926,10 +11926,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126893320</v>
+        <v>126894585</v>
       </c>
       <c r="B114" t="n">
-        <v>80146</v>
+        <v>97331</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11937,37 +11937,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>857058</v>
+        <v>857167</v>
       </c>
       <c r="R114" t="n">
-        <v>7485807</v>
+        <v>7485432</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12011,12 +12011,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12030,7 +12030,7 @@
         <v>126894597</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>126894600</v>
       </c>
       <c r="B116" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>126889027</v>
       </c>
       <c r="B117" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>126895965</v>
       </c>
       <c r="B118" t="n">
-        <v>80153</v>
+        <v>80157</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>126895970</v>
       </c>
       <c r="B119" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>126894592</v>
       </c>
       <c r="B120" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>126889014</v>
       </c>
       <c r="B121" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>126889030</v>
       </c>
       <c r="B122" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>126899900</v>
       </c>
       <c r="B123" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>126899898</v>
       </c>
       <c r="B124" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>126899894</v>
       </c>
       <c r="B125" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>126899816</v>
       </c>
       <c r="B126" t="n">
-        <v>80153</v>
+        <v>80157</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>126899814</v>
       </c>
       <c r="B127" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>126899815</v>
       </c>
       <c r="B128" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>126899897</v>
       </c>
       <c r="B129" t="n">
-        <v>80153</v>
+        <v>80157</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13560,45 +13560,57 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126899896</v>
+        <v>126899818</v>
       </c>
       <c r="B130" t="n">
-        <v>80146</v>
+        <v>98447</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>856908</v>
+        <v>856921</v>
       </c>
       <c r="R130" t="n">
-        <v>7485414</v>
+        <v>7485611</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13639,6 +13651,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13650,7 +13663,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13661,57 +13674,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126899818</v>
+        <v>126899896</v>
       </c>
       <c r="B131" t="n">
-        <v>98443</v>
+        <v>80150</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>856921</v>
+        <v>856908</v>
       </c>
       <c r="R131" t="n">
-        <v>7485611</v>
+        <v>7485414</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13752,7 +13753,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -13778,7 +13778,7 @@
         <v>126899899</v>
       </c>
       <c r="B132" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>126899817</v>
       </c>
       <c r="B133" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>126899820</v>
       </c>
       <c r="B134" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>126899902</v>
       </c>
       <c r="B135" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14218,57 +14218,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126899819</v>
+        <v>126899901</v>
       </c>
       <c r="B136" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>856846</v>
+        <v>856929</v>
       </c>
       <c r="R136" t="n">
-        <v>7485645</v>
+        <v>7485563</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14309,7 +14297,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14321,7 +14308,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14332,45 +14319,57 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126899901</v>
+        <v>126899819</v>
       </c>
       <c r="B137" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>856929</v>
+        <v>856846</v>
       </c>
       <c r="R137" t="n">
-        <v>7485563</v>
+        <v>7485645</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14411,6 +14410,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14436,7 +14436,7 @@
         <v>126899895</v>
       </c>
       <c r="B138" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>126882460</v>
       </c>
       <c r="B139" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14650,49 +14650,37 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126883898</v>
+        <v>126895795</v>
       </c>
       <c r="B140" t="n">
-        <v>98443</v>
+        <v>97325</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -14701,13 +14689,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>856979</v>
+        <v>856787</v>
       </c>
       <c r="R140" t="n">
-        <v>7485287</v>
+        <v>7485429</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14734,19 +14722,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>13:19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14778,37 +14756,49 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126895795</v>
+        <v>126883898</v>
       </c>
       <c r="B141" t="n">
-        <v>97321</v>
+        <v>98447</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -14817,13 +14807,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>856787</v>
+        <v>856979</v>
       </c>
       <c r="R141" t="n">
-        <v>7485429</v>
+        <v>7485287</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14850,9 +14840,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14887,7 +14887,7 @@
         <v>126895801</v>
       </c>
       <c r="B142" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>127272114</v>
       </c>
       <c r="B143" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>126895799</v>
       </c>
       <c r="B144" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>127155655</v>
       </c>
       <c r="B145" t="n">
-        <v>41361</v>
+        <v>41365</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>127150856</v>
       </c>
       <c r="B146" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>126895794</v>
       </c>
       <c r="B147" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>126883438</v>
       </c>
       <c r="B148" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15660,52 +15660,57 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126895796</v>
+        <v>126882171</v>
       </c>
       <c r="B149" t="n">
-        <v>97321</v>
+        <v>98447</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>856693</v>
+        <v>856765</v>
       </c>
       <c r="R149" t="n">
-        <v>7485505</v>
+        <v>7485445</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15732,18 +15737,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15755,7 +15769,7 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -15766,57 +15780,52 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126882171</v>
+        <v>126895796</v>
       </c>
       <c r="B150" t="n">
-        <v>98443</v>
+        <v>97325</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>856765</v>
+        <v>856693</v>
       </c>
       <c r="R150" t="n">
-        <v>7485445</v>
+        <v>7485505</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15843,27 +15852,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15886,10 +15886,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126883505</v>
+        <v>126895798</v>
       </c>
       <c r="B151" t="n">
-        <v>91291</v>
+        <v>97331</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15897,37 +15897,41 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R151" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15954,49 +15958,20 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -16009,14 +15984,18 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY151" t="inlineStr"/>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126895798</v>
+        <v>126883505</v>
       </c>
       <c r="B152" t="n">
-        <v>97327</v>
+        <v>91295</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16024,41 +16003,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R152" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16085,20 +16060,49 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16108,21 +16112,17 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
         <v>127272276</v>
       </c>
       <c r="B153" t="n">
-        <v>80083</v>
+        <v>80087</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>126895800</v>
       </c>
       <c r="B154" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>126882331</v>
       </c>
       <c r="B155" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126893335</v>
+        <v>126889016</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>857254</v>
+        <v>857042</v>
       </c>
       <c r="R31" t="n">
-        <v>7485706</v>
+        <v>7485656</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3638,12 +3638,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3654,48 +3654,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126894596</v>
+        <v>126893321</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>857232</v>
+        <v>857154</v>
       </c>
       <c r="R32" t="n">
-        <v>7485521</v>
+        <v>7485805</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3739,12 +3739,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3755,7 +3755,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126889016</v>
+        <v>126895913</v>
       </c>
       <c r="B33" t="n">
         <v>80150</v>
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>857042</v>
+        <v>857071</v>
       </c>
       <c r="R33" t="n">
-        <v>7485656</v>
+        <v>7485419</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3840,12 +3840,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3856,32 +3856,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126893321</v>
+        <v>126893335</v>
       </c>
       <c r="B34" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857154</v>
+        <v>857254</v>
       </c>
       <c r="R34" t="n">
-        <v>7485805</v>
+        <v>7485706</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3957,48 +3957,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126895913</v>
+        <v>126894596</v>
       </c>
       <c r="B35" t="n">
-        <v>80150</v>
+        <v>98447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>857071</v>
+        <v>857232</v>
       </c>
       <c r="R35" t="n">
-        <v>7485419</v>
+        <v>7485521</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4058,10 +4058,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126894580</v>
+        <v>126893328</v>
       </c>
       <c r="B36" t="n">
-        <v>80150</v>
+        <v>80157</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4069,37 +4069,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>857065</v>
+        <v>856959</v>
       </c>
       <c r="R36" t="n">
-        <v>7485568</v>
+        <v>7485620</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4143,12 +4143,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4159,10 +4159,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126893328</v>
+        <v>126894580</v>
       </c>
       <c r="B37" t="n">
-        <v>80157</v>
+        <v>80150</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4170,37 +4170,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>856959</v>
+        <v>857065</v>
       </c>
       <c r="R37" t="n">
-        <v>7485620</v>
+        <v>7485568</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4244,12 +4244,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -5166,32 +5166,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126895963</v>
+        <v>126895968</v>
       </c>
       <c r="B47" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>856930</v>
+        <v>856872</v>
       </c>
       <c r="R47" t="n">
-        <v>7485560</v>
+        <v>7485620</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
+          <t>Flera blommande ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5268,7 +5268,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126895968</v>
+        <v>126889044</v>
       </c>
       <c r="B48" t="n">
         <v>98447</v>
@@ -5299,17 +5299,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>856872</v>
+        <v>857220</v>
       </c>
       <c r="R48" t="n">
-        <v>7485620</v>
+        <v>7485601</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5339,11 +5339,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Flera blommande ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5358,19 +5353,23 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126889044</v>
+        <v>126888927</v>
       </c>
       <c r="B49" t="n">
         <v>98447</v>
@@ -5405,10 +5404,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>857220</v>
+        <v>856896</v>
       </c>
       <c r="R49" t="n">
-        <v>7485601</v>
+        <v>7485538</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5455,12 +5454,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5471,7 +5470,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126888927</v>
+        <v>126895916</v>
       </c>
       <c r="B50" t="n">
         <v>98447</v>
@@ -5506,13 +5505,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>856896</v>
+        <v>857225</v>
       </c>
       <c r="R50" t="n">
-        <v>7485538</v>
+        <v>7485668</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5556,12 +5555,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5572,7 +5571,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126895916</v>
+        <v>126888930</v>
       </c>
       <c r="B51" t="n">
         <v>98447</v>
@@ -5607,13 +5606,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>857225</v>
+        <v>856694</v>
       </c>
       <c r="R51" t="n">
-        <v>7485668</v>
+        <v>7485592</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5657,12 +5656,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5673,45 +5672,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126888930</v>
+        <v>126894582</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>856694</v>
+        <v>856922</v>
       </c>
       <c r="R52" t="n">
-        <v>7485592</v>
+        <v>7485635</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5746,6 +5745,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>på Sälg</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5758,12 +5762,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5774,10 +5778,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126894582</v>
+        <v>126895963</v>
       </c>
       <c r="B53" t="n">
-        <v>80150</v>
+        <v>98468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5785,37 +5789,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>856922</v>
+        <v>856930</v>
       </c>
       <c r="R53" t="n">
-        <v>7485635</v>
+        <v>7485560</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5849,7 +5853,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>på Sälg</t>
+          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5864,64 +5868,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126895972</v>
+        <v>126893336</v>
       </c>
       <c r="B54" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>856725</v>
+        <v>857022</v>
       </c>
       <c r="R54" t="n">
-        <v>7485571</v>
+        <v>7485521</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5965,22 +5965,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893336</v>
+        <v>126893326</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5988,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6012,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>857022</v>
+        <v>857089</v>
       </c>
       <c r="R55" t="n">
-        <v>7485521</v>
+        <v>7485450</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6048,6 +6052,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6078,48 +6087,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893326</v>
+        <v>126895972</v>
       </c>
       <c r="B56" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>857089</v>
+        <v>856725</v>
       </c>
       <c r="R56" t="n">
-        <v>7485450</v>
+        <v>7485571</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6149,11 +6158,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6168,19 +6172,15 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6285,10 +6285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126893319</v>
+        <v>126889052</v>
       </c>
       <c r="B58" t="n">
-        <v>91505</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6296,21 +6296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6320,13 +6320,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>857122</v>
+        <v>857206</v>
       </c>
       <c r="R58" t="n">
-        <v>7485443</v>
+        <v>7485553</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6370,12 +6370,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6386,32 +6386,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126889013</v>
+        <v>126893319</v>
       </c>
       <c r="B59" t="n">
-        <v>80150</v>
+        <v>91505</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>1588</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6421,13 +6421,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>857038</v>
+        <v>857122</v>
       </c>
       <c r="R59" t="n">
-        <v>7485632</v>
+        <v>7485443</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6471,12 +6471,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6487,7 +6487,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126894581</v>
+        <v>126889013</v>
       </c>
       <c r="B60" t="n">
         <v>80150</v>
@@ -6518,14 +6518,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>857009</v>
+        <v>857038</v>
       </c>
       <c r="R60" t="n">
-        <v>7485612</v>
+        <v>7485632</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6572,12 +6572,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6588,45 +6588,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126889052</v>
+        <v>126894581</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>857206</v>
+        <v>857009</v>
       </c>
       <c r="R61" t="n">
-        <v>7485553</v>
+        <v>7485612</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6673,12 +6673,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6790,10 +6790,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126895921</v>
+        <v>126895961</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6801,37 +6801,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>857123</v>
+        <v>856840</v>
       </c>
       <c r="R63" t="n">
-        <v>7485402</v>
+        <v>7485479</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6875,48 +6875,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126895915</v>
+        <v>126895921</v>
       </c>
       <c r="B64" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6926,10 +6922,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>857242</v>
+        <v>857123</v>
       </c>
       <c r="R64" t="n">
-        <v>7485724</v>
+        <v>7485402</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -6992,45 +6988,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126889041</v>
+        <v>126894583</v>
       </c>
       <c r="B65" t="n">
-        <v>98447</v>
+        <v>98468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>856978</v>
+        <v>856988</v>
       </c>
       <c r="R65" t="n">
-        <v>7485792</v>
+        <v>7485572</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7077,12 +7073,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7093,48 +7089,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126895961</v>
+        <v>126889032</v>
       </c>
       <c r="B66" t="n">
-        <v>75142</v>
+        <v>98468</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>856840</v>
+        <v>857038</v>
       </c>
       <c r="R66" t="n">
-        <v>7485479</v>
+        <v>7485636</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7178,60 +7174,64 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126894583</v>
+        <v>126895915</v>
       </c>
       <c r="B67" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>856988</v>
+        <v>857242</v>
       </c>
       <c r="R67" t="n">
-        <v>7485572</v>
+        <v>7485724</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7275,12 +7275,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7291,32 +7291,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126889032</v>
+        <v>126889041</v>
       </c>
       <c r="B68" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>857038</v>
+        <v>856978</v>
       </c>
       <c r="R68" t="n">
-        <v>7485636</v>
+        <v>7485792</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7493,32 +7493,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126895920</v>
+        <v>126889021</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>857173</v>
+        <v>857000</v>
       </c>
       <c r="R70" t="n">
-        <v>7485506</v>
+        <v>7485629</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7578,12 +7578,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7594,32 +7594,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126895922</v>
+        <v>126889024</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7629,13 +7629,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>856981</v>
+        <v>856962</v>
       </c>
       <c r="R71" t="n">
-        <v>7485578</v>
+        <v>7485641</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7679,12 +7679,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7695,32 +7695,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126889021</v>
+        <v>126895920</v>
       </c>
       <c r="B72" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7730,13 +7730,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>857000</v>
+        <v>857173</v>
       </c>
       <c r="R72" t="n">
-        <v>7485629</v>
+        <v>7485506</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7780,12 +7780,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7796,32 +7796,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126889024</v>
+        <v>126895922</v>
       </c>
       <c r="B73" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7831,13 +7831,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>856962</v>
+        <v>856981</v>
       </c>
       <c r="R73" t="n">
-        <v>7485641</v>
+        <v>7485578</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7881,12 +7881,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7897,32 +7897,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126889045</v>
+        <v>126889029</v>
       </c>
       <c r="B74" t="n">
-        <v>98447</v>
+        <v>98468</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>857084</v>
+        <v>857083</v>
       </c>
       <c r="R74" t="n">
-        <v>7485530</v>
+        <v>7485527</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7998,7 +7998,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126889047</v>
+        <v>126889045</v>
       </c>
       <c r="B75" t="n">
         <v>98447</v>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>857010</v>
+        <v>857084</v>
       </c>
       <c r="R75" t="n">
-        <v>7485585</v>
+        <v>7485530</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8099,32 +8099,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126889029</v>
+        <v>126889047</v>
       </c>
       <c r="B76" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>857083</v>
+        <v>857010</v>
       </c>
       <c r="R76" t="n">
-        <v>7485527</v>
+        <v>7485585</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8806,32 +8806,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126893339</v>
+        <v>126889019</v>
       </c>
       <c r="B83" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8841,13 +8841,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>857104</v>
+        <v>857016</v>
       </c>
       <c r="R83" t="n">
-        <v>7485447</v>
+        <v>7485635</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8891,12 +8891,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8907,7 +8907,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126894601</v>
+        <v>126893339</v>
       </c>
       <c r="B84" t="n">
         <v>79018</v>
@@ -8938,17 +8938,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>857215</v>
+        <v>857104</v>
       </c>
       <c r="R84" t="n">
-        <v>7485457</v>
+        <v>7485447</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8992,12 +8992,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9008,45 +9008,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126889019</v>
+        <v>126894601</v>
       </c>
       <c r="B85" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>857016</v>
+        <v>857215</v>
       </c>
       <c r="R85" t="n">
-        <v>7485635</v>
+        <v>7485457</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9093,12 +9093,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9711,48 +9711,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126893327</v>
+        <v>126895962</v>
       </c>
       <c r="B92" t="n">
-        <v>91314</v>
+        <v>91330</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4660</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>857141</v>
+        <v>856927</v>
       </c>
       <c r="R92" t="n">
-        <v>7485413</v>
+        <v>7485482</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9796,26 +9796,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126889025</v>
+        <v>126893327</v>
       </c>
       <c r="B93" t="n">
-        <v>80150</v>
+        <v>91314</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9823,21 +9819,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>4660</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9847,13 +9843,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>856955</v>
+        <v>857141</v>
       </c>
       <c r="R93" t="n">
-        <v>7485682</v>
+        <v>7485413</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9897,12 +9893,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -9913,48 +9909,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126895962</v>
+        <v>126889025</v>
       </c>
       <c r="B94" t="n">
-        <v>91330</v>
+        <v>80150</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>856927</v>
+        <v>856955</v>
       </c>
       <c r="R94" t="n">
-        <v>7485482</v>
+        <v>7485682</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9998,15 +9994,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10515,48 +10515,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126895911</v>
+        <v>126894595</v>
       </c>
       <c r="B100" t="n">
-        <v>80150</v>
+        <v>98447</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>856885</v>
+        <v>857231</v>
       </c>
       <c r="R100" t="n">
-        <v>7485704</v>
+        <v>7485574</v>
       </c>
       <c r="S100" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10586,11 +10586,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10605,12 +10600,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10621,7 +10616,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126894595</v>
+        <v>126889049</v>
       </c>
       <c r="B101" t="n">
         <v>98447</v>
@@ -10652,14 +10647,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>857231</v>
+        <v>857013</v>
       </c>
       <c r="R101" t="n">
-        <v>7485574</v>
+        <v>7485581</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10706,12 +10701,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10722,7 +10717,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126889049</v>
+        <v>126895967</v>
       </c>
       <c r="B102" t="n">
         <v>98447</v>
@@ -10753,17 +10748,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>857013</v>
+        <v>856932</v>
       </c>
       <c r="R102" t="n">
-        <v>7485581</v>
+        <v>7485559</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10807,64 +10802,60 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126895967</v>
+        <v>126895911</v>
       </c>
       <c r="B103" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>856932</v>
+        <v>856885</v>
       </c>
       <c r="R103" t="n">
-        <v>7485559</v>
+        <v>7485704</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10894,6 +10885,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10908,60 +10904,67 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr"/>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126893338</v>
+        <v>126895966</v>
       </c>
       <c r="B104" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>856954</v>
+        <v>856849</v>
       </c>
       <c r="R104" t="n">
-        <v>7485603</v>
+        <v>7485405</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10999,25 +11002,22 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11324,51 +11324,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126895966</v>
+        <v>126893338</v>
       </c>
       <c r="B108" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>856849</v>
+        <v>856954</v>
       </c>
       <c r="R108" t="n">
-        <v>7485405</v>
+        <v>7485603</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11406,51 +11403,54 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126893334</v>
+        <v>126893324</v>
       </c>
       <c r="B109" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11460,10 +11460,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>856938</v>
+        <v>856949</v>
       </c>
       <c r="R109" t="n">
-        <v>7485632</v>
+        <v>7485588</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11623,32 +11623,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126893324</v>
+        <v>126893334</v>
       </c>
       <c r="B111" t="n">
-        <v>80150</v>
+        <v>98447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11658,10 +11658,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>856949</v>
+        <v>856938</v>
       </c>
       <c r="R111" t="n">
-        <v>7485588</v>
+        <v>7485632</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11724,32 +11724,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126893329</v>
+        <v>126893320</v>
       </c>
       <c r="B112" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11759,10 +11759,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>857202</v>
+        <v>857058</v>
       </c>
       <c r="R112" t="n">
-        <v>7485431</v>
+        <v>7485807</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126893320</v>
+        <v>126894585</v>
       </c>
       <c r="B113" t="n">
-        <v>80150</v>
+        <v>97331</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11836,37 +11836,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>857058</v>
+        <v>857167</v>
       </c>
       <c r="R113" t="n">
-        <v>7485807</v>
+        <v>7485432</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11910,12 +11910,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -11926,48 +11926,48 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126894585</v>
+        <v>126893329</v>
       </c>
       <c r="B114" t="n">
-        <v>97331</v>
+        <v>98447</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>857167</v>
+        <v>857202</v>
       </c>
       <c r="R114" t="n">
-        <v>7485432</v>
+        <v>7485431</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12011,12 +12011,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12027,48 +12027,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126894597</v>
+        <v>126895965</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>857222</v>
+        <v>856897</v>
       </c>
       <c r="R115" t="n">
-        <v>7485544</v>
+        <v>7485429</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12112,61 +12112,57 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126894600</v>
+        <v>126889027</v>
       </c>
       <c r="B116" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>857163</v>
+        <v>856947</v>
       </c>
       <c r="R116" t="n">
-        <v>7485497</v>
+        <v>7485678</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12213,12 +12209,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12229,45 +12225,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126889027</v>
+        <v>126894597</v>
       </c>
       <c r="B117" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>856947</v>
+        <v>857222</v>
       </c>
       <c r="R117" t="n">
-        <v>7485678</v>
+        <v>7485544</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12314,12 +12310,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12330,48 +12326,48 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126895965</v>
+        <v>126894600</v>
       </c>
       <c r="B118" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>856897</v>
+        <v>857163</v>
       </c>
       <c r="R118" t="n">
-        <v>7485429</v>
+        <v>7485497</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12415,15 +12411,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13055,32 +13055,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126899894</v>
+        <v>126899816</v>
       </c>
       <c r="B125" t="n">
-        <v>75142</v>
+        <v>80157</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>856906</v>
+        <v>856947</v>
       </c>
       <c r="R125" t="n">
-        <v>7485559</v>
+        <v>7485478</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13145,7 +13145,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13156,32 +13156,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126899816</v>
+        <v>126899894</v>
       </c>
       <c r="B126" t="n">
-        <v>80157</v>
+        <v>75142</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13191,10 +13191,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>856947</v>
+        <v>856906</v>
       </c>
       <c r="R126" t="n">
-        <v>7485478</v>
+        <v>7485559</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13560,57 +13560,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126899818</v>
+        <v>126899896</v>
       </c>
       <c r="B130" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>856921</v>
+        <v>856908</v>
       </c>
       <c r="R130" t="n">
-        <v>7485611</v>
+        <v>7485414</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13651,7 +13639,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13663,7 +13650,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13674,45 +13661,57 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126899896</v>
+        <v>126899818</v>
       </c>
       <c r="B131" t="n">
-        <v>80150</v>
+        <v>98447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>856908</v>
+        <v>856921</v>
       </c>
       <c r="R131" t="n">
-        <v>7485414</v>
+        <v>7485611</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13753,6 +13752,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -3856,48 +3856,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126893335</v>
+        <v>126894596</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857254</v>
+        <v>857232</v>
       </c>
       <c r="R34" t="n">
-        <v>7485706</v>
+        <v>7485521</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3941,12 +3941,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -3957,48 +3957,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126894596</v>
+        <v>126893335</v>
       </c>
       <c r="B35" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>857232</v>
+        <v>857254</v>
       </c>
       <c r="R35" t="n">
-        <v>7485521</v>
+        <v>7485706</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -5166,48 +5166,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126895968</v>
+        <v>126894582</v>
       </c>
       <c r="B47" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>856872</v>
+        <v>856922</v>
       </c>
       <c r="R47" t="n">
-        <v>7485620</v>
+        <v>7485635</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Flera blommande ex</t>
+          <t>på Sälg</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5256,19 +5256,23 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126889044</v>
+        <v>126895968</v>
       </c>
       <c r="B48" t="n">
         <v>98447</v>
@@ -5299,17 +5303,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>857220</v>
+        <v>856872</v>
       </c>
       <c r="R48" t="n">
-        <v>7485601</v>
+        <v>7485620</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5339,6 +5343,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Flera blommande ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5353,23 +5362,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126888927</v>
+        <v>126889044</v>
       </c>
       <c r="B49" t="n">
         <v>98447</v>
@@ -5404,10 +5409,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>856896</v>
+        <v>857220</v>
       </c>
       <c r="R49" t="n">
-        <v>7485538</v>
+        <v>7485601</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5454,12 +5459,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5470,7 +5475,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126895916</v>
+        <v>126888927</v>
       </c>
       <c r="B50" t="n">
         <v>98447</v>
@@ -5505,13 +5510,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>857225</v>
+        <v>856896</v>
       </c>
       <c r="R50" t="n">
-        <v>7485668</v>
+        <v>7485538</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5555,12 +5560,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5571,7 +5576,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126888930</v>
+        <v>126895916</v>
       </c>
       <c r="B51" t="n">
         <v>98447</v>
@@ -5606,13 +5611,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>856694</v>
+        <v>857225</v>
       </c>
       <c r="R51" t="n">
-        <v>7485592</v>
+        <v>7485668</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5656,12 +5661,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5672,45 +5677,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126894582</v>
+        <v>126888930</v>
       </c>
       <c r="B52" t="n">
-        <v>80150</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>856922</v>
+        <v>856694</v>
       </c>
       <c r="R52" t="n">
-        <v>7485635</v>
+        <v>7485592</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5745,11 +5750,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>på Sälg</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5762,12 +5762,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -7897,32 +7897,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126889029</v>
+        <v>126889045</v>
       </c>
       <c r="B74" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>857083</v>
+        <v>857084</v>
       </c>
       <c r="R74" t="n">
-        <v>7485527</v>
+        <v>7485530</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7998,7 +7998,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126889045</v>
+        <v>126889047</v>
       </c>
       <c r="B75" t="n">
         <v>98447</v>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>857084</v>
+        <v>857010</v>
       </c>
       <c r="R75" t="n">
-        <v>7485530</v>
+        <v>7485585</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8099,32 +8099,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126889047</v>
+        <v>126889029</v>
       </c>
       <c r="B76" t="n">
-        <v>98447</v>
+        <v>98468</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>857010</v>
+        <v>857083</v>
       </c>
       <c r="R76" t="n">
-        <v>7485585</v>
+        <v>7485527</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8705,10 +8705,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126888931</v>
+        <v>126888929</v>
       </c>
       <c r="B82" t="n">
-        <v>91904</v>
+        <v>98447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8716,21 +8716,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>856896</v>
+        <v>856800</v>
       </c>
       <c r="R82" t="n">
-        <v>7485431</v>
+        <v>7485540</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8806,45 +8806,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126889019</v>
+        <v>126894590</v>
       </c>
       <c r="B83" t="n">
-        <v>80150</v>
+        <v>98447</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>857016</v>
+        <v>857265</v>
       </c>
       <c r="R83" t="n">
-        <v>7485635</v>
+        <v>7485680</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8891,12 +8891,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8907,32 +8907,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126893339</v>
+        <v>126888931</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>91904</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8942,13 +8942,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>857104</v>
+        <v>856896</v>
       </c>
       <c r="R84" t="n">
-        <v>7485447</v>
+        <v>7485431</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8992,12 +8992,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9008,45 +9008,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126894601</v>
+        <v>126889019</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>857215</v>
+        <v>857016</v>
       </c>
       <c r="R85" t="n">
-        <v>7485457</v>
+        <v>7485635</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9093,12 +9093,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9109,32 +9109,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126888929</v>
+        <v>126893339</v>
       </c>
       <c r="B86" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9144,13 +9144,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>856800</v>
+        <v>857104</v>
       </c>
       <c r="R86" t="n">
-        <v>7485540</v>
+        <v>7485447</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9194,12 +9194,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9210,32 +9210,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126894590</v>
+        <v>126894601</v>
       </c>
       <c r="B87" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9245,10 +9245,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>857265</v>
+        <v>857215</v>
       </c>
       <c r="R87" t="n">
-        <v>7485680</v>
+        <v>7485457</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -14650,37 +14650,49 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126895795</v>
+        <v>126883898</v>
       </c>
       <c r="B140" t="n">
-        <v>97325</v>
+        <v>98447</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -14689,13 +14701,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>856787</v>
+        <v>856979</v>
       </c>
       <c r="R140" t="n">
-        <v>7485429</v>
+        <v>7485287</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14722,9 +14734,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14756,49 +14778,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126883898</v>
+        <v>126895795</v>
       </c>
       <c r="B141" t="n">
-        <v>98447</v>
+        <v>97325</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -14807,13 +14817,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>856979</v>
+        <v>856787</v>
       </c>
       <c r="R141" t="n">
-        <v>7485287</v>
+        <v>7485429</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14840,19 +14850,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>13:19</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15886,10 +15886,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126895798</v>
+        <v>126883505</v>
       </c>
       <c r="B151" t="n">
-        <v>97331</v>
+        <v>91295</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15897,41 +15897,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R151" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15958,20 +15954,49 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -15984,18 +16009,14 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126883505</v>
+        <v>126895798</v>
       </c>
       <c r="B152" t="n">
-        <v>91295</v>
+        <v>97331</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16003,37 +16024,41 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R152" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16060,49 +16085,20 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16115,52 +16111,59 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY152" t="inlineStr"/>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127272276</v>
+        <v>126895800</v>
       </c>
       <c r="B153" t="n">
-        <v>80087</v>
+        <v>79018</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>856765</v>
+        <v>856984</v>
       </c>
       <c r="R153" t="n">
-        <v>7485445</v>
+        <v>7485301</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16187,27 +16190,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16230,51 +16224,48 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126895800</v>
+        <v>127272276</v>
       </c>
       <c r="B154" t="n">
-        <v>79018</v>
+        <v>80087</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>856984</v>
+        <v>856765</v>
       </c>
       <c r="R154" t="n">
-        <v>7485301</v>
+        <v>7485445</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16301,18 +16292,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -5880,32 +5880,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893336</v>
+        <v>126888926</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>857022</v>
+        <v>856904</v>
       </c>
       <c r="R54" t="n">
-        <v>7485521</v>
+        <v>7485446</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5965,12 +5965,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893326</v>
+        <v>126893336</v>
       </c>
       <c r="B55" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>857089</v>
+        <v>857022</v>
       </c>
       <c r="R55" t="n">
-        <v>7485450</v>
+        <v>7485521</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6052,11 +6052,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6087,48 +6082,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126895972</v>
+        <v>126893326</v>
       </c>
       <c r="B56" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>856725</v>
+        <v>857089</v>
       </c>
       <c r="R56" t="n">
-        <v>7485571</v>
+        <v>7485450</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6158,6 +6153,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6172,60 +6172,64 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126888926</v>
+        <v>126895972</v>
       </c>
       <c r="B57" t="n">
-        <v>80157</v>
+        <v>98447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>856904</v>
+        <v>856725</v>
       </c>
       <c r="R57" t="n">
-        <v>7485446</v>
+        <v>7485571</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6269,19 +6273,15 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8503,32 +8503,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126895912</v>
+        <v>126895918</v>
       </c>
       <c r="B80" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>857018</v>
+        <v>857150</v>
       </c>
       <c r="R80" t="n">
-        <v>7485408</v>
+        <v>7485418</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -8604,32 +8604,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126895918</v>
+        <v>126895912</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>857150</v>
+        <v>857018</v>
       </c>
       <c r="R81" t="n">
-        <v>7485418</v>
+        <v>7485408</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -9311,32 +9311,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126895917</v>
+        <v>126889034</v>
       </c>
       <c r="B88" t="n">
-        <v>79018</v>
+        <v>98468</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>857220</v>
+        <v>856998</v>
       </c>
       <c r="R88" t="n">
-        <v>7485407</v>
+        <v>7485630</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9396,12 +9396,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9513,48 +9513,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126895973</v>
+        <v>126895917</v>
       </c>
       <c r="B90" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>856707</v>
+        <v>857220</v>
       </c>
       <c r="R90" t="n">
-        <v>7485577</v>
+        <v>7485407</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9598,60 +9598,64 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126889034</v>
+        <v>126895973</v>
       </c>
       <c r="B91" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>856998</v>
+        <v>856707</v>
       </c>
       <c r="R91" t="n">
-        <v>7485630</v>
+        <v>7485577</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9695,19 +9699,15 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10515,48 +10515,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126894595</v>
+        <v>126895911</v>
       </c>
       <c r="B100" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>857231</v>
+        <v>856885</v>
       </c>
       <c r="R100" t="n">
-        <v>7485574</v>
+        <v>7485704</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10586,6 +10586,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10600,12 +10605,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10616,7 +10621,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126889049</v>
+        <v>126894595</v>
       </c>
       <c r="B101" t="n">
         <v>98447</v>
@@ -10647,14 +10652,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>857013</v>
+        <v>857231</v>
       </c>
       <c r="R101" t="n">
-        <v>7485581</v>
+        <v>7485574</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10701,12 +10706,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10717,7 +10722,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126895967</v>
+        <v>126889049</v>
       </c>
       <c r="B102" t="n">
         <v>98447</v>
@@ -10748,17 +10753,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>856932</v>
+        <v>857013</v>
       </c>
       <c r="R102" t="n">
-        <v>7485559</v>
+        <v>7485581</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10802,60 +10807,64 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126895911</v>
+        <v>126895967</v>
       </c>
       <c r="B103" t="n">
-        <v>80150</v>
+        <v>98447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>856885</v>
+        <v>856932</v>
       </c>
       <c r="R103" t="n">
-        <v>7485704</v>
+        <v>7485559</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10885,11 +10894,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10904,19 +10908,15 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889016</v>
+        <v>126893335</v>
       </c>
       <c r="B31" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>857042</v>
+        <v>857254</v>
       </c>
       <c r="R31" t="n">
-        <v>7485656</v>
+        <v>7485706</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3638,12 +3638,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3654,7 +3654,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893321</v>
+        <v>126889016</v>
       </c>
       <c r="B32" t="n">
         <v>80150</v>
@@ -3689,13 +3689,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>857154</v>
+        <v>857042</v>
       </c>
       <c r="R32" t="n">
-        <v>7485805</v>
+        <v>7485656</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3739,12 +3739,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3755,7 +3755,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126895913</v>
+        <v>126893321</v>
       </c>
       <c r="B33" t="n">
         <v>80150</v>
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>857071</v>
+        <v>857154</v>
       </c>
       <c r="R33" t="n">
-        <v>7485419</v>
+        <v>7485805</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3840,12 +3840,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3856,48 +3856,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126894596</v>
+        <v>126895913</v>
       </c>
       <c r="B34" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857232</v>
+        <v>857071</v>
       </c>
       <c r="R34" t="n">
-        <v>7485521</v>
+        <v>7485419</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3941,12 +3941,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -3957,48 +3957,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126893335</v>
+        <v>126894596</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>857254</v>
+        <v>857232</v>
       </c>
       <c r="R35" t="n">
-        <v>7485706</v>
+        <v>7485521</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4263,7 +4263,7 @@
         <v>126893330</v>
       </c>
       <c r="B38" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>126895971</v>
       </c>
       <c r="B39" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>126894589</v>
       </c>
       <c r="B40" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>126894594</v>
       </c>
       <c r="B42" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>126889042</v>
       </c>
       <c r="B43" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>126894588</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>126895969</v>
       </c>
       <c r="B45" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>126893332</v>
       </c>
       <c r="B46" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126894582</v>
+        <v>126895963</v>
       </c>
       <c r="B47" t="n">
-        <v>80150</v>
+        <v>98469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5177,37 +5177,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>856922</v>
+        <v>856930</v>
       </c>
       <c r="R47" t="n">
-        <v>7485635</v>
+        <v>7485560</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>på Sälg</t>
+          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5256,64 +5256,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126895968</v>
+        <v>126894582</v>
       </c>
       <c r="B48" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>856872</v>
+        <v>856922</v>
       </c>
       <c r="R48" t="n">
-        <v>7485620</v>
+        <v>7485635</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5347,7 +5343,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Flera blommande ex</t>
+          <t>på Sälg</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5362,22 +5358,26 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126889044</v>
+        <v>126895968</v>
       </c>
       <c r="B49" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5405,17 +5405,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>857220</v>
+        <v>856872</v>
       </c>
       <c r="R49" t="n">
-        <v>7485601</v>
+        <v>7485620</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5445,6 +5445,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Flera blommande ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5459,26 +5464,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126888927</v>
+        <v>126889044</v>
       </c>
       <c r="B50" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5510,10 +5511,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>856896</v>
+        <v>857220</v>
       </c>
       <c r="R50" t="n">
-        <v>7485538</v>
+        <v>7485601</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5560,12 +5561,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5576,10 +5577,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126895916</v>
+        <v>126888927</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5611,13 +5612,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>857225</v>
+        <v>856896</v>
       </c>
       <c r="R51" t="n">
-        <v>7485668</v>
+        <v>7485538</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5661,12 +5662,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5677,10 +5678,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126888930</v>
+        <v>126895916</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5712,13 +5713,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>856694</v>
+        <v>857225</v>
       </c>
       <c r="R52" t="n">
-        <v>7485592</v>
+        <v>7485668</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5762,12 +5763,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5778,48 +5779,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126895963</v>
+        <v>126888930</v>
       </c>
       <c r="B53" t="n">
-        <v>98468</v>
+        <v>98448</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>856930</v>
+        <v>856694</v>
       </c>
       <c r="R53" t="n">
-        <v>7485560</v>
+        <v>7485592</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5849,11 +5850,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5868,15 +5864,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6082,48 +6082,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893326</v>
+        <v>126895972</v>
       </c>
       <c r="B56" t="n">
-        <v>57658</v>
+        <v>98448</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>857089</v>
+        <v>856725</v>
       </c>
       <c r="R56" t="n">
-        <v>7485450</v>
+        <v>7485571</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6153,11 +6153,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6172,64 +6167,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126895972</v>
+        <v>126893326</v>
       </c>
       <c r="B57" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>856725</v>
+        <v>857089</v>
       </c>
       <c r="R57" t="n">
-        <v>7485571</v>
+        <v>7485450</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6259,6 +6250,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6273,22 +6269,26 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126889052</v>
+        <v>126893319</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>91505</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6296,21 +6296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6320,13 +6320,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>857206</v>
+        <v>857122</v>
       </c>
       <c r="R58" t="n">
-        <v>7485553</v>
+        <v>7485443</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6370,12 +6370,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6386,32 +6386,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126893319</v>
+        <v>126889013</v>
       </c>
       <c r="B59" t="n">
-        <v>91505</v>
+        <v>80150</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1588</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6421,13 +6421,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>857122</v>
+        <v>857038</v>
       </c>
       <c r="R59" t="n">
-        <v>7485443</v>
+        <v>7485632</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6471,12 +6471,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6487,32 +6487,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126889013</v>
+        <v>126889052</v>
       </c>
       <c r="B60" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>857038</v>
+        <v>857206</v>
       </c>
       <c r="R60" t="n">
-        <v>7485632</v>
+        <v>7485553</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6588,45 +6588,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126894581</v>
+        <v>126888928</v>
       </c>
       <c r="B61" t="n">
-        <v>80150</v>
+        <v>98448</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>857009</v>
+        <v>856845</v>
       </c>
       <c r="R61" t="n">
-        <v>7485612</v>
+        <v>7485513</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6673,12 +6673,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6689,45 +6689,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126888928</v>
+        <v>126894581</v>
       </c>
       <c r="B62" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>856845</v>
+        <v>857009</v>
       </c>
       <c r="R62" t="n">
-        <v>7485513</v>
+        <v>7485612</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6774,12 +6774,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6887,48 +6887,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126895921</v>
+        <v>126894583</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>98469</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>857123</v>
+        <v>856988</v>
       </c>
       <c r="R64" t="n">
-        <v>7485402</v>
+        <v>7485572</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6972,12 +6972,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -6988,10 +6988,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126894583</v>
+        <v>126889032</v>
       </c>
       <c r="B65" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7019,14 +7019,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>856988</v>
+        <v>857038</v>
       </c>
       <c r="R65" t="n">
-        <v>7485572</v>
+        <v>7485636</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7073,12 +7073,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7089,32 +7089,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126889032</v>
+        <v>126895921</v>
       </c>
       <c r="B66" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7124,13 +7124,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>857038</v>
+        <v>857123</v>
       </c>
       <c r="R66" t="n">
-        <v>7485636</v>
+        <v>7485402</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7174,12 +7174,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7193,7 +7193,7 @@
         <v>126895915</v>
       </c>
       <c r="B67" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>126889041</v>
       </c>
       <c r="B68" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126895910</v>
+        <v>126889024</v>
       </c>
       <c r="B69" t="n">
         <v>80150</v>
@@ -7427,13 +7427,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>856984</v>
+        <v>856962</v>
       </c>
       <c r="R69" t="n">
-        <v>7485600</v>
+        <v>7485641</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7477,12 +7477,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7493,10 +7493,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126889021</v>
+        <v>126889029</v>
       </c>
       <c r="B70" t="n">
-        <v>80150</v>
+        <v>98469</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7504,21 +7504,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>857000</v>
+        <v>857083</v>
       </c>
       <c r="R70" t="n">
-        <v>7485629</v>
+        <v>7485527</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7594,7 +7594,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126889024</v>
+        <v>126895910</v>
       </c>
       <c r="B71" t="n">
         <v>80150</v>
@@ -7629,13 +7629,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>856962</v>
+        <v>856984</v>
       </c>
       <c r="R71" t="n">
-        <v>7485641</v>
+        <v>7485600</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7679,12 +7679,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7897,32 +7897,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126889045</v>
+        <v>126889021</v>
       </c>
       <c r="B74" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>857084</v>
+        <v>857000</v>
       </c>
       <c r="R74" t="n">
-        <v>7485530</v>
+        <v>7485629</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126889047</v>
+        <v>126889045</v>
       </c>
       <c r="B75" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>857010</v>
+        <v>857084</v>
       </c>
       <c r="R75" t="n">
-        <v>7485585</v>
+        <v>7485530</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8099,32 +8099,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126889029</v>
+        <v>126889047</v>
       </c>
       <c r="B76" t="n">
-        <v>98468</v>
+        <v>98448</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>857083</v>
+        <v>857010</v>
       </c>
       <c r="R76" t="n">
-        <v>7485527</v>
+        <v>7485585</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8503,32 +8503,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126895918</v>
+        <v>126895912</v>
       </c>
       <c r="B80" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>857150</v>
+        <v>857018</v>
       </c>
       <c r="R80" t="n">
-        <v>7485418</v>
+        <v>7485408</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -8604,32 +8604,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126895912</v>
+        <v>126895918</v>
       </c>
       <c r="B81" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>857018</v>
+        <v>857150</v>
       </c>
       <c r="R81" t="n">
-        <v>7485408</v>
+        <v>7485418</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -8705,32 +8705,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126888929</v>
+        <v>126889019</v>
       </c>
       <c r="B82" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>856800</v>
+        <v>857016</v>
       </c>
       <c r="R82" t="n">
-        <v>7485540</v>
+        <v>7485635</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8790,12 +8790,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8806,48 +8806,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126894590</v>
+        <v>126893339</v>
       </c>
       <c r="B83" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>857265</v>
+        <v>857104</v>
       </c>
       <c r="R83" t="n">
-        <v>7485680</v>
+        <v>7485447</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8891,12 +8891,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8907,45 +8907,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126888931</v>
+        <v>126894601</v>
       </c>
       <c r="B84" t="n">
-        <v>91904</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>856896</v>
+        <v>857215</v>
       </c>
       <c r="R84" t="n">
-        <v>7485431</v>
+        <v>7485457</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8992,12 +8992,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9008,32 +9008,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126889019</v>
+        <v>126888931</v>
       </c>
       <c r="B85" t="n">
-        <v>80150</v>
+        <v>91904</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9043,10 +9043,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>857016</v>
+        <v>856896</v>
       </c>
       <c r="R85" t="n">
-        <v>7485635</v>
+        <v>7485431</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9093,12 +9093,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9109,32 +9109,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126893339</v>
+        <v>126888929</v>
       </c>
       <c r="B86" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9144,13 +9144,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>857104</v>
+        <v>856800</v>
       </c>
       <c r="R86" t="n">
-        <v>7485447</v>
+        <v>7485540</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9194,12 +9194,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9210,32 +9210,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126894601</v>
+        <v>126894590</v>
       </c>
       <c r="B87" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9245,10 +9245,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>857215</v>
+        <v>857265</v>
       </c>
       <c r="R87" t="n">
-        <v>7485457</v>
+        <v>7485680</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9311,32 +9311,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126889034</v>
+        <v>126895917</v>
       </c>
       <c r="B88" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>856998</v>
+        <v>857220</v>
       </c>
       <c r="R88" t="n">
-        <v>7485630</v>
+        <v>7485407</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9396,12 +9396,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9412,10 +9412,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126889017</v>
+        <v>126889034</v>
       </c>
       <c r="B89" t="n">
-        <v>80150</v>
+        <v>98469</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9423,21 +9423,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>857021</v>
+        <v>856998</v>
       </c>
       <c r="R89" t="n">
-        <v>7485648</v>
+        <v>7485630</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9513,32 +9513,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126895917</v>
+        <v>126889017</v>
       </c>
       <c r="B90" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9548,13 +9548,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>857220</v>
+        <v>857021</v>
       </c>
       <c r="R90" t="n">
-        <v>7485407</v>
+        <v>7485648</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9598,12 +9598,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9617,7 +9617,7 @@
         <v>126895973</v>
       </c>
       <c r="B91" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9711,48 +9711,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126895962</v>
+        <v>126893327</v>
       </c>
       <c r="B92" t="n">
-        <v>91330</v>
+        <v>91314</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>856927</v>
+        <v>857141</v>
       </c>
       <c r="R92" t="n">
-        <v>7485482</v>
+        <v>7485413</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9796,60 +9796,64 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126893327</v>
+        <v>126895962</v>
       </c>
       <c r="B93" t="n">
-        <v>91314</v>
+        <v>91330</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4660</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>857141</v>
+        <v>856927</v>
       </c>
       <c r="R93" t="n">
-        <v>7485413</v>
+        <v>7485482</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9893,19 +9897,15 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10010,32 +10010,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126893323</v>
+        <v>126889050</v>
       </c>
       <c r="B95" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10045,13 +10045,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>856995</v>
+        <v>857208</v>
       </c>
       <c r="R95" t="n">
-        <v>7485538</v>
+        <v>7485545</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10095,12 +10095,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10313,32 +10313,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126889050</v>
+        <v>126893323</v>
       </c>
       <c r="B98" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10348,13 +10348,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>857208</v>
+        <v>856995</v>
       </c>
       <c r="R98" t="n">
-        <v>7485545</v>
+        <v>7485538</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10398,12 +10398,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10417,7 +10417,7 @@
         <v>126893333</v>
       </c>
       <c r="B99" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>126894595</v>
       </c>
       <c r="B101" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>126889049</v>
       </c>
       <c r="B102" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>126895967</v>
       </c>
       <c r="B103" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11021,10 +11021,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126889036</v>
+        <v>126893322</v>
       </c>
       <c r="B105" t="n">
-        <v>80025</v>
+        <v>80150</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11032,21 +11032,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11056,13 +11056,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>857182</v>
+        <v>857015</v>
       </c>
       <c r="R105" t="n">
-        <v>7485442</v>
+        <v>7485514</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11106,12 +11106,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11122,10 +11122,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126893322</v>
+        <v>126889037</v>
       </c>
       <c r="B106" t="n">
-        <v>80150</v>
+        <v>80025</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11133,21 +11133,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11157,13 +11157,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>857015</v>
+        <v>857094</v>
       </c>
       <c r="R106" t="n">
-        <v>7485514</v>
+        <v>7485517</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11207,12 +11207,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11223,32 +11223,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126889037</v>
+        <v>126893338</v>
       </c>
       <c r="B107" t="n">
-        <v>80025</v>
+        <v>79018</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11258,13 +11258,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>857094</v>
+        <v>856954</v>
       </c>
       <c r="R107" t="n">
-        <v>7485517</v>
+        <v>7485603</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11308,12 +11308,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11324,32 +11324,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126893338</v>
+        <v>126889036</v>
       </c>
       <c r="B108" t="n">
-        <v>79018</v>
+        <v>80025</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11359,13 +11359,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>856954</v>
+        <v>857182</v>
       </c>
       <c r="R108" t="n">
-        <v>7485603</v>
+        <v>7485442</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11409,12 +11409,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11425,48 +11425,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126893324</v>
+        <v>126895975</v>
       </c>
       <c r="B109" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>856949</v>
+        <v>856864</v>
       </c>
       <c r="R109" t="n">
-        <v>7485588</v>
+        <v>7485417</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11510,64 +11510,60 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126895975</v>
+        <v>126893324</v>
       </c>
       <c r="B110" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>856864</v>
+        <v>856949</v>
       </c>
       <c r="R110" t="n">
-        <v>7485417</v>
+        <v>7485588</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11611,22 +11607,26 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
         <v>126893334</v>
       </c>
       <c r="B111" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11724,32 +11724,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126893320</v>
+        <v>126893329</v>
       </c>
       <c r="B112" t="n">
-        <v>80150</v>
+        <v>98448</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11759,10 +11759,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>857058</v>
+        <v>857202</v>
       </c>
       <c r="R112" t="n">
-        <v>7485807</v>
+        <v>7485431</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126894585</v>
+        <v>126893320</v>
       </c>
       <c r="B113" t="n">
-        <v>97331</v>
+        <v>80150</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11836,37 +11836,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>857167</v>
+        <v>857058</v>
       </c>
       <c r="R113" t="n">
-        <v>7485432</v>
+        <v>7485807</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11910,12 +11910,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -11926,48 +11926,48 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126893329</v>
+        <v>126894585</v>
       </c>
       <c r="B114" t="n">
-        <v>98447</v>
+        <v>97331</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>857202</v>
+        <v>857167</v>
       </c>
       <c r="R114" t="n">
-        <v>7485431</v>
+        <v>7485432</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12011,12 +12011,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12027,48 +12027,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126895965</v>
+        <v>126894597</v>
       </c>
       <c r="B115" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>856897</v>
+        <v>857222</v>
       </c>
       <c r="R115" t="n">
-        <v>7485429</v>
+        <v>7485544</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12112,57 +12112,61 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126889027</v>
+        <v>126894600</v>
       </c>
       <c r="B116" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>856947</v>
+        <v>857163</v>
       </c>
       <c r="R116" t="n">
-        <v>7485678</v>
+        <v>7485497</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12209,12 +12213,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12225,45 +12229,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126894597</v>
+        <v>126889027</v>
       </c>
       <c r="B117" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>857222</v>
+        <v>856947</v>
       </c>
       <c r="R117" t="n">
-        <v>7485544</v>
+        <v>7485678</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12310,12 +12314,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12326,48 +12330,48 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126894600</v>
+        <v>126895965</v>
       </c>
       <c r="B118" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>857163</v>
+        <v>856897</v>
       </c>
       <c r="R118" t="n">
-        <v>7485497</v>
+        <v>7485429</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12411,26 +12415,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
         <v>126895970</v>
       </c>
       <c r="B119" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>126894592</v>
       </c>
       <c r="B120" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>126889030</v>
       </c>
       <c r="B122" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>126899900</v>
       </c>
       <c r="B123" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>126899898</v>
       </c>
       <c r="B124" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13055,32 +13055,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126899816</v>
+        <v>126899894</v>
       </c>
       <c r="B125" t="n">
-        <v>80157</v>
+        <v>75142</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>856947</v>
+        <v>856906</v>
       </c>
       <c r="R125" t="n">
-        <v>7485478</v>
+        <v>7485559</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13145,7 +13145,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13156,32 +13156,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126899894</v>
+        <v>126899816</v>
       </c>
       <c r="B126" t="n">
-        <v>75142</v>
+        <v>80157</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13191,10 +13191,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>856906</v>
+        <v>856947</v>
       </c>
       <c r="R126" t="n">
-        <v>7485559</v>
+        <v>7485478</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13361,7 +13361,7 @@
         <v>126899815</v>
       </c>
       <c r="B128" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>126899818</v>
       </c>
       <c r="B131" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>126899899</v>
       </c>
       <c r="B132" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>126899817</v>
       </c>
       <c r="B133" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>126899820</v>
       </c>
       <c r="B134" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14218,45 +14218,57 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126899901</v>
+        <v>126899819</v>
       </c>
       <c r="B136" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>856929</v>
+        <v>856846</v>
       </c>
       <c r="R136" t="n">
-        <v>7485563</v>
+        <v>7485645</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14297,6 +14309,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14308,7 +14321,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14319,57 +14332,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126899819</v>
+        <v>126899901</v>
       </c>
       <c r="B137" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>856846</v>
+        <v>856929</v>
       </c>
       <c r="R137" t="n">
-        <v>7485645</v>
+        <v>7485563</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14410,7 +14411,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14653,7 +14653,7 @@
         <v>126883898</v>
       </c>
       <c r="B140" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15556,7 +15556,7 @@
         <v>126883438</v>
       </c>
       <c r="B148" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15660,57 +15660,52 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126882171</v>
+        <v>126895796</v>
       </c>
       <c r="B149" t="n">
-        <v>98447</v>
+        <v>97325</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>856765</v>
+        <v>856693</v>
       </c>
       <c r="R149" t="n">
-        <v>7485445</v>
+        <v>7485505</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15737,27 +15732,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15780,52 +15766,57 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126895796</v>
+        <v>126882171</v>
       </c>
       <c r="B150" t="n">
-        <v>97325</v>
+        <v>98448</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>856693</v>
+        <v>856765</v>
       </c>
       <c r="R150" t="n">
-        <v>7485505</v>
+        <v>7485445</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15852,18 +15843,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16119,51 +16119,48 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126895800</v>
+        <v>127272276</v>
       </c>
       <c r="B153" t="n">
-        <v>79018</v>
+        <v>80087</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>856984</v>
+        <v>856765</v>
       </c>
       <c r="R153" t="n">
-        <v>7485301</v>
+        <v>7485445</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16190,18 +16187,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16224,48 +16230,51 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127272276</v>
+        <v>126895800</v>
       </c>
       <c r="B154" t="n">
-        <v>80087</v>
+        <v>79018</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>856765</v>
+        <v>856984</v>
       </c>
       <c r="R154" t="n">
-        <v>7485445</v>
+        <v>7485301</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16292,27 +16301,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126893335</v>
+        <v>126889016</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>857254</v>
+        <v>857042</v>
       </c>
       <c r="R31" t="n">
-        <v>7485706</v>
+        <v>7485656</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3638,12 +3638,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3654,45 +3654,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889016</v>
+        <v>126894596</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>98448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>857042</v>
+        <v>857232</v>
       </c>
       <c r="R32" t="n">
-        <v>7485656</v>
+        <v>7485521</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3739,12 +3739,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3957,48 +3957,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126894596</v>
+        <v>126893335</v>
       </c>
       <c r="B35" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>857232</v>
+        <v>857254</v>
       </c>
       <c r="R35" t="n">
-        <v>7485521</v>
+        <v>7485706</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -5880,32 +5880,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126888926</v>
+        <v>126893326</v>
       </c>
       <c r="B54" t="n">
-        <v>80157</v>
+        <v>57658</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>856904</v>
+        <v>857089</v>
       </c>
       <c r="R54" t="n">
-        <v>7485446</v>
+        <v>7485450</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5951,6 +5951,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5965,12 +5970,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -5981,32 +5986,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893336</v>
+        <v>126888926</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,13 +6021,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>857022</v>
+        <v>856904</v>
       </c>
       <c r="R55" t="n">
-        <v>7485521</v>
+        <v>7485446</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6066,12 +6071,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6082,48 +6087,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126895972</v>
+        <v>126893336</v>
       </c>
       <c r="B56" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>856725</v>
+        <v>857022</v>
       </c>
       <c r="R56" t="n">
-        <v>7485571</v>
+        <v>7485521</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6167,60 +6172,64 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126893326</v>
+        <v>126895972</v>
       </c>
       <c r="B57" t="n">
-        <v>57658</v>
+        <v>98448</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>857089</v>
+        <v>856725</v>
       </c>
       <c r="R57" t="n">
-        <v>7485450</v>
+        <v>7485571</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6250,11 +6259,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6269,19 +6273,15 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6588,45 +6588,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126888928</v>
+        <v>126894581</v>
       </c>
       <c r="B61" t="n">
-        <v>98448</v>
+        <v>80150</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>856845</v>
+        <v>857009</v>
       </c>
       <c r="R61" t="n">
-        <v>7485513</v>
+        <v>7485612</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6673,12 +6673,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6689,45 +6689,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126894581</v>
+        <v>126888928</v>
       </c>
       <c r="B62" t="n">
-        <v>80150</v>
+        <v>98448</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>857009</v>
+        <v>856845</v>
       </c>
       <c r="R62" t="n">
-        <v>7485612</v>
+        <v>7485513</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6774,12 +6774,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7392,7 +7392,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126889024</v>
+        <v>126895910</v>
       </c>
       <c r="B69" t="n">
         <v>80150</v>
@@ -7427,13 +7427,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>856962</v>
+        <v>856984</v>
       </c>
       <c r="R69" t="n">
-        <v>7485641</v>
+        <v>7485600</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7477,12 +7477,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7493,10 +7493,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126889029</v>
+        <v>126889021</v>
       </c>
       <c r="B70" t="n">
-        <v>98469</v>
+        <v>80150</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7504,21 +7504,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>857083</v>
+        <v>857000</v>
       </c>
       <c r="R70" t="n">
-        <v>7485527</v>
+        <v>7485629</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7594,7 +7594,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126895910</v>
+        <v>126889024</v>
       </c>
       <c r="B71" t="n">
         <v>80150</v>
@@ -7629,13 +7629,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>856984</v>
+        <v>856962</v>
       </c>
       <c r="R71" t="n">
-        <v>7485600</v>
+        <v>7485641</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7679,12 +7679,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7695,32 +7695,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126895920</v>
+        <v>126889045</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7730,13 +7730,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>857173</v>
+        <v>857084</v>
       </c>
       <c r="R72" t="n">
-        <v>7485506</v>
+        <v>7485530</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7780,12 +7780,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7796,32 +7796,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126895922</v>
+        <v>126889047</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7831,13 +7831,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>856981</v>
+        <v>857010</v>
       </c>
       <c r="R73" t="n">
-        <v>7485578</v>
+        <v>7485585</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7881,12 +7881,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7897,10 +7897,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126889021</v>
+        <v>126889029</v>
       </c>
       <c r="B74" t="n">
-        <v>80150</v>
+        <v>98469</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7908,21 +7908,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>857000</v>
+        <v>857083</v>
       </c>
       <c r="R74" t="n">
-        <v>7485629</v>
+        <v>7485527</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7998,32 +7998,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126889045</v>
+        <v>126895920</v>
       </c>
       <c r="B75" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8033,13 +8033,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>857084</v>
+        <v>857173</v>
       </c>
       <c r="R75" t="n">
-        <v>7485530</v>
+        <v>7485506</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8083,12 +8083,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8099,32 +8099,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126889047</v>
+        <v>126895922</v>
       </c>
       <c r="B76" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8134,13 +8134,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>857010</v>
+        <v>856981</v>
       </c>
       <c r="R76" t="n">
-        <v>7485585</v>
+        <v>7485578</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8184,12 +8184,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -9311,32 +9311,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126895917</v>
+        <v>126889017</v>
       </c>
       <c r="B88" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>857220</v>
+        <v>857021</v>
       </c>
       <c r="R88" t="n">
-        <v>7485407</v>
+        <v>7485648</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9396,12 +9396,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9412,48 +9412,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126889034</v>
+        <v>126895973</v>
       </c>
       <c r="B89" t="n">
-        <v>98469</v>
+        <v>98448</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>856998</v>
+        <v>856707</v>
       </c>
       <c r="R89" t="n">
-        <v>7485630</v>
+        <v>7485577</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9497,48 +9497,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126889017</v>
+        <v>126895917</v>
       </c>
       <c r="B90" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9548,13 +9544,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>857021</v>
+        <v>857220</v>
       </c>
       <c r="R90" t="n">
-        <v>7485648</v>
+        <v>7485407</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9598,12 +9594,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9614,48 +9610,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126895973</v>
+        <v>126889034</v>
       </c>
       <c r="B91" t="n">
-        <v>98448</v>
+        <v>98469</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>856707</v>
+        <v>856998</v>
       </c>
       <c r="R91" t="n">
-        <v>7485577</v>
+        <v>7485630</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9699,15 +9695,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10920,10 +10920,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126895966</v>
+        <v>126889036</v>
       </c>
       <c r="B104" t="n">
-        <v>80157</v>
+        <v>80025</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10931,40 +10931,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>856849</v>
+        <v>857182</v>
       </c>
       <c r="R104" t="n">
-        <v>7485405</v>
+        <v>7485442</v>
       </c>
       <c r="S104" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11002,22 +10999,25 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11122,10 +11122,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126889037</v>
+        <v>126895966</v>
       </c>
       <c r="B106" t="n">
-        <v>80025</v>
+        <v>80157</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11133,37 +11133,40 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>857094</v>
+        <v>856849</v>
       </c>
       <c r="R106" t="n">
-        <v>7485517</v>
+        <v>7485405</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11201,54 +11204,51 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126893338</v>
+        <v>126889037</v>
       </c>
       <c r="B107" t="n">
-        <v>79018</v>
+        <v>80025</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11258,13 +11258,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>856954</v>
+        <v>857094</v>
       </c>
       <c r="R107" t="n">
-        <v>7485603</v>
+        <v>7485517</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11308,12 +11308,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11324,32 +11324,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126889036</v>
+        <v>126893338</v>
       </c>
       <c r="B108" t="n">
-        <v>80025</v>
+        <v>79018</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11359,13 +11359,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>857182</v>
+        <v>856954</v>
       </c>
       <c r="R108" t="n">
-        <v>7485442</v>
+        <v>7485603</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11409,12 +11409,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11825,10 +11825,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126893320</v>
+        <v>126894585</v>
       </c>
       <c r="B113" t="n">
-        <v>80150</v>
+        <v>97331</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11836,37 +11836,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>857058</v>
+        <v>857167</v>
       </c>
       <c r="R113" t="n">
-        <v>7485807</v>
+        <v>7485432</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11910,12 +11910,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -11926,10 +11926,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126894585</v>
+        <v>126893320</v>
       </c>
       <c r="B114" t="n">
-        <v>97331</v>
+        <v>80150</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11937,37 +11937,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>857167</v>
+        <v>857058</v>
       </c>
       <c r="R114" t="n">
-        <v>7485432</v>
+        <v>7485807</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12011,12 +12011,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12027,45 +12027,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126894597</v>
+        <v>126889027</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>857222</v>
+        <v>856947</v>
       </c>
       <c r="R115" t="n">
-        <v>7485544</v>
+        <v>7485678</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12112,12 +12112,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12128,48 +12128,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126894600</v>
+        <v>126895965</v>
       </c>
       <c r="B116" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>857163</v>
+        <v>856897</v>
       </c>
       <c r="R116" t="n">
-        <v>7485497</v>
+        <v>7485429</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12213,61 +12213,57 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126889027</v>
+        <v>126894597</v>
       </c>
       <c r="B117" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>856947</v>
+        <v>857222</v>
       </c>
       <c r="R117" t="n">
-        <v>7485678</v>
+        <v>7485544</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12314,12 +12310,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12330,48 +12326,48 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126895965</v>
+        <v>126894600</v>
       </c>
       <c r="B118" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>856897</v>
+        <v>857163</v>
       </c>
       <c r="R118" t="n">
-        <v>7485429</v>
+        <v>7485497</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12415,15 +12411,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13560,45 +13560,57 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126899896</v>
+        <v>126899818</v>
       </c>
       <c r="B130" t="n">
-        <v>80150</v>
+        <v>98448</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>856908</v>
+        <v>856921</v>
       </c>
       <c r="R130" t="n">
-        <v>7485414</v>
+        <v>7485611</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13639,6 +13651,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13650,7 +13663,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13661,57 +13674,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126899818</v>
+        <v>126899896</v>
       </c>
       <c r="B131" t="n">
-        <v>98448</v>
+        <v>80150</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>856921</v>
+        <v>856908</v>
       </c>
       <c r="R131" t="n">
-        <v>7485611</v>
+        <v>7485414</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13752,7 +13753,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14218,57 +14218,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126899819</v>
+        <v>126899901</v>
       </c>
       <c r="B136" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>856846</v>
+        <v>856929</v>
       </c>
       <c r="R136" t="n">
-        <v>7485645</v>
+        <v>7485563</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14309,7 +14297,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14321,7 +14308,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14332,45 +14319,57 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126899901</v>
+        <v>126899819</v>
       </c>
       <c r="B137" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>856929</v>
+        <v>856846</v>
       </c>
       <c r="R137" t="n">
-        <v>7485563</v>
+        <v>7485645</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14411,6 +14410,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -15205,52 +15205,38 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127155655</v>
+        <v>127150856</v>
       </c>
       <c r="B145" t="n">
-        <v>41365</v>
+        <v>56853</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>215713</v>
+        <v>100138</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -15259,13 +15245,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R145" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S145" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15294,7 +15280,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15304,7 +15290,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15327,42 +15313,60 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY145" t="inlineStr"/>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127150856</v>
+        <v>127155655</v>
       </c>
       <c r="B146" t="n">
-        <v>56853</v>
+        <v>41365</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100138</v>
+        <v>215713</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -15371,13 +15375,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R146" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15406,7 +15410,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15416,7 +15420,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15439,11 +15443,7 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -3556,7 +3556,7 @@
         <v>126889016</v>
       </c>
       <c r="B31" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>126894596</v>
       </c>
       <c r="B32" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3755,32 +3755,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126893321</v>
+        <v>126893335</v>
       </c>
       <c r="B33" t="n">
-        <v>80150</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>857154</v>
+        <v>857254</v>
       </c>
       <c r="R33" t="n">
-        <v>7485805</v>
+        <v>7485706</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126895913</v>
+        <v>126893321</v>
       </c>
       <c r="B34" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857071</v>
+        <v>857154</v>
       </c>
       <c r="R34" t="n">
-        <v>7485419</v>
+        <v>7485805</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3941,12 +3941,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -3957,32 +3957,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126893335</v>
+        <v>126895913</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>80152</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3992,13 +3992,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>857254</v>
+        <v>857071</v>
       </c>
       <c r="R35" t="n">
-        <v>7485706</v>
+        <v>7485419</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4061,7 +4061,7 @@
         <v>126893328</v>
       </c>
       <c r="B36" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>126894580</v>
       </c>
       <c r="B37" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>126893330</v>
       </c>
       <c r="B38" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>126895971</v>
       </c>
       <c r="B39" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>126894589</v>
       </c>
       <c r="B40" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>126889022</v>
       </c>
       <c r="B41" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>126894594</v>
       </c>
       <c r="B42" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>126889042</v>
       </c>
       <c r="B43" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>126894588</v>
       </c>
       <c r="B44" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>126895969</v>
       </c>
       <c r="B45" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>126893332</v>
       </c>
       <c r="B46" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126895963</v>
+        <v>126894582</v>
       </c>
       <c r="B47" t="n">
-        <v>98469</v>
+        <v>80152</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5177,37 +5177,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>856930</v>
+        <v>856922</v>
       </c>
       <c r="R47" t="n">
-        <v>7485560</v>
+        <v>7485635</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
+          <t>på Sälg</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5256,22 +5256,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126894582</v>
+        <v>126895963</v>
       </c>
       <c r="B48" t="n">
-        <v>80150</v>
+        <v>98471</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5279,37 +5283,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>856922</v>
+        <v>856930</v>
       </c>
       <c r="R48" t="n">
-        <v>7485635</v>
+        <v>7485560</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5343,7 +5347,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>på Sälg</t>
+          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5358,26 +5362,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>126895968</v>
       </c>
       <c r="B49" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>126889044</v>
       </c>
       <c r="B50" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>126888927</v>
       </c>
       <c r="B51" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>126895916</v>
       </c>
       <c r="B52" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>126888930</v>
       </c>
       <c r="B53" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5880,10 +5880,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893326</v>
+        <v>126893336</v>
       </c>
       <c r="B54" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5891,21 +5891,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>857089</v>
+        <v>857022</v>
       </c>
       <c r="R54" t="n">
-        <v>7485450</v>
+        <v>7485521</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5951,11 +5951,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5989,7 +5984,7 @@
         <v>126888926</v>
       </c>
       <c r="B55" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6087,10 +6082,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893336</v>
+        <v>126893326</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6098,21 +6093,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6122,10 +6117,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>857022</v>
+        <v>857089</v>
       </c>
       <c r="R56" t="n">
-        <v>7485521</v>
+        <v>7485450</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6158,6 +6153,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6191,7 +6191,7 @@
         <v>126895972</v>
       </c>
       <c r="B57" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>126893319</v>
       </c>
       <c r="B58" t="n">
-        <v>91505</v>
+        <v>91507</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>126889013</v>
       </c>
       <c r="B59" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>126889052</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>126894581</v>
       </c>
       <c r="B61" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>126888928</v>
       </c>
       <c r="B62" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126895961</v>
+        <v>126895921</v>
       </c>
       <c r="B63" t="n">
-        <v>75142</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6801,37 +6801,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>856840</v>
+        <v>857123</v>
       </c>
       <c r="R63" t="n">
-        <v>7485479</v>
+        <v>7485402</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6875,60 +6875,64 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126894583</v>
+        <v>126895961</v>
       </c>
       <c r="B64" t="n">
-        <v>98469</v>
+        <v>75144</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>856988</v>
+        <v>856840</v>
       </c>
       <c r="R64" t="n">
-        <v>7485572</v>
+        <v>7485479</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6972,26 +6976,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126889032</v>
+        <v>126894583</v>
       </c>
       <c r="B65" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7019,14 +7019,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>857038</v>
+        <v>856988</v>
       </c>
       <c r="R65" t="n">
-        <v>7485636</v>
+        <v>7485572</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7073,12 +7073,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7089,32 +7089,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126895921</v>
+        <v>126889032</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>98471</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7124,13 +7124,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>857123</v>
+        <v>857038</v>
       </c>
       <c r="R66" t="n">
-        <v>7485402</v>
+        <v>7485636</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7174,12 +7174,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7193,7 +7193,7 @@
         <v>126895915</v>
       </c>
       <c r="B67" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>126889041</v>
       </c>
       <c r="B68" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7392,10 +7392,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126895910</v>
+        <v>126889021</v>
       </c>
       <c r="B69" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7427,13 +7427,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>856984</v>
+        <v>857000</v>
       </c>
       <c r="R69" t="n">
-        <v>7485600</v>
+        <v>7485629</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7477,12 +7477,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7493,10 +7493,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126889021</v>
+        <v>126889024</v>
       </c>
       <c r="B70" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>857000</v>
+        <v>856962</v>
       </c>
       <c r="R70" t="n">
-        <v>7485629</v>
+        <v>7485641</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7594,10 +7594,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126889024</v>
+        <v>126889029</v>
       </c>
       <c r="B71" t="n">
-        <v>80150</v>
+        <v>98471</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7605,21 +7605,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>856962</v>
+        <v>857083</v>
       </c>
       <c r="R71" t="n">
-        <v>7485641</v>
+        <v>7485527</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7695,32 +7695,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126889045</v>
+        <v>126895922</v>
       </c>
       <c r="B72" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7730,13 +7730,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>857084</v>
+        <v>856981</v>
       </c>
       <c r="R72" t="n">
-        <v>7485530</v>
+        <v>7485578</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7780,12 +7780,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7796,32 +7796,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126889047</v>
+        <v>126895920</v>
       </c>
       <c r="B73" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7831,13 +7831,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>857010</v>
+        <v>857173</v>
       </c>
       <c r="R73" t="n">
-        <v>7485585</v>
+        <v>7485506</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7881,12 +7881,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7897,10 +7897,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126889029</v>
+        <v>126895910</v>
       </c>
       <c r="B74" t="n">
-        <v>98469</v>
+        <v>80152</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7908,21 +7908,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7932,13 +7932,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>857083</v>
+        <v>856984</v>
       </c>
       <c r="R74" t="n">
-        <v>7485527</v>
+        <v>7485600</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7982,12 +7982,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -7998,32 +7998,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126895920</v>
+        <v>126889045</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8033,13 +8033,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>857173</v>
+        <v>857084</v>
       </c>
       <c r="R75" t="n">
-        <v>7485506</v>
+        <v>7485530</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8083,12 +8083,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8099,32 +8099,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126895922</v>
+        <v>126889047</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8134,13 +8134,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>856981</v>
+        <v>857010</v>
       </c>
       <c r="R76" t="n">
-        <v>7485578</v>
+        <v>7485585</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8184,12 +8184,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8203,7 +8203,7 @@
         <v>126894602</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>126894584</v>
       </c>
       <c r="B78" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>126889039</v>
       </c>
       <c r="B79" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8503,32 +8503,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126895912</v>
+        <v>126895918</v>
       </c>
       <c r="B80" t="n">
-        <v>80150</v>
+        <v>79020</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>857018</v>
+        <v>857150</v>
       </c>
       <c r="R80" t="n">
-        <v>7485408</v>
+        <v>7485418</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -8604,32 +8604,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126895918</v>
+        <v>126895912</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>80152</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>857150</v>
+        <v>857018</v>
       </c>
       <c r="R81" t="n">
-        <v>7485418</v>
+        <v>7485408</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -8705,32 +8705,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126889019</v>
+        <v>126893339</v>
       </c>
       <c r="B82" t="n">
-        <v>80150</v>
+        <v>79020</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8740,13 +8740,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>857016</v>
+        <v>857104</v>
       </c>
       <c r="R82" t="n">
-        <v>7485635</v>
+        <v>7485447</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8790,12 +8790,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8806,10 +8806,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126893339</v>
+        <v>126894601</v>
       </c>
       <c r="B83" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8837,17 +8837,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>857104</v>
+        <v>857215</v>
       </c>
       <c r="R83" t="n">
-        <v>7485447</v>
+        <v>7485457</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8891,12 +8891,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8907,45 +8907,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126894601</v>
+        <v>126888931</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>91906</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>857215</v>
+        <v>856896</v>
       </c>
       <c r="R84" t="n">
-        <v>7485457</v>
+        <v>7485431</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8992,12 +8992,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9008,32 +9008,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126888931</v>
+        <v>126889019</v>
       </c>
       <c r="B85" t="n">
-        <v>91904</v>
+        <v>80152</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9043,10 +9043,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>856896</v>
+        <v>857016</v>
       </c>
       <c r="R85" t="n">
-        <v>7485431</v>
+        <v>7485635</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9093,12 +9093,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9112,7 +9112,7 @@
         <v>126888929</v>
       </c>
       <c r="B86" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>126894590</v>
       </c>
       <c r="B87" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>126889017</v>
       </c>
       <c r="B88" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>126895973</v>
       </c>
       <c r="B89" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>126895917</v>
       </c>
       <c r="B90" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>126889034</v>
       </c>
       <c r="B91" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>126893327</v>
       </c>
       <c r="B92" t="n">
-        <v>91314</v>
+        <v>91316</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>126895962</v>
       </c>
       <c r="B93" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>126889025</v>
       </c>
       <c r="B94" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>126889050</v>
       </c>
       <c r="B95" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10111,10 +10111,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126893325</v>
+        <v>126893323</v>
       </c>
       <c r="B96" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>856884</v>
+        <v>856995</v>
       </c>
       <c r="R96" t="n">
-        <v>7485698</v>
+        <v>7485538</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10212,10 +10212,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126895914</v>
+        <v>126893325</v>
       </c>
       <c r="B97" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10247,13 +10247,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>856958</v>
+        <v>856884</v>
       </c>
       <c r="R97" t="n">
-        <v>7485679</v>
+        <v>7485698</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10297,12 +10297,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10313,10 +10313,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126893323</v>
+        <v>126895914</v>
       </c>
       <c r="B98" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10348,13 +10348,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>856995</v>
+        <v>856958</v>
       </c>
       <c r="R98" t="n">
-        <v>7485538</v>
+        <v>7485679</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10398,12 +10398,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10417,7 +10417,7 @@
         <v>126893333</v>
       </c>
       <c r="B99" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>126895911</v>
       </c>
       <c r="B100" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>126894595</v>
       </c>
       <c r="B101" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>126889049</v>
       </c>
       <c r="B102" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>126895967</v>
       </c>
       <c r="B103" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>126889036</v>
       </c>
       <c r="B104" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11021,10 +11021,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126893322</v>
+        <v>126889037</v>
       </c>
       <c r="B105" t="n">
-        <v>80150</v>
+        <v>80027</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11032,21 +11032,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11056,13 +11056,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>857015</v>
+        <v>857094</v>
       </c>
       <c r="R105" t="n">
-        <v>7485514</v>
+        <v>7485517</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11106,12 +11106,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11125,7 +11125,7 @@
         <v>126895966</v>
       </c>
       <c r="B106" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11223,10 +11223,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126889037</v>
+        <v>126893322</v>
       </c>
       <c r="B107" t="n">
-        <v>80025</v>
+        <v>80152</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11234,21 +11234,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11258,13 +11258,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>857094</v>
+        <v>857015</v>
       </c>
       <c r="R107" t="n">
-        <v>7485517</v>
+        <v>7485514</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11308,12 +11308,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11327,7 +11327,7 @@
         <v>126893338</v>
       </c>
       <c r="B108" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>126895975</v>
       </c>
       <c r="B109" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>126893324</v>
       </c>
       <c r="B110" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>126893334</v>
       </c>
       <c r="B111" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>126893329</v>
       </c>
       <c r="B112" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126894585</v>
+        <v>126893320</v>
       </c>
       <c r="B113" t="n">
-        <v>97331</v>
+        <v>80152</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11836,37 +11836,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>857167</v>
+        <v>857058</v>
       </c>
       <c r="R113" t="n">
-        <v>7485432</v>
+        <v>7485807</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11910,12 +11910,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -11926,10 +11926,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126893320</v>
+        <v>126894585</v>
       </c>
       <c r="B114" t="n">
-        <v>80150</v>
+        <v>97333</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11937,37 +11937,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>857058</v>
+        <v>857167</v>
       </c>
       <c r="R114" t="n">
-        <v>7485807</v>
+        <v>7485432</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12011,12 +12011,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12030,7 +12030,7 @@
         <v>126889027</v>
       </c>
       <c r="B115" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>126895965</v>
       </c>
       <c r="B116" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12225,48 +12225,48 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126894597</v>
+        <v>126895970</v>
       </c>
       <c r="B117" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>857222</v>
+        <v>856849</v>
       </c>
       <c r="R117" t="n">
-        <v>7485544</v>
+        <v>7485559</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12310,48 +12310,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126894600</v>
+        <v>126894592</v>
       </c>
       <c r="B118" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12361,10 +12357,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>857163</v>
+        <v>857255</v>
       </c>
       <c r="R118" t="n">
-        <v>7485497</v>
+        <v>7485644</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12427,48 +12423,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126895970</v>
+        <v>126894600</v>
       </c>
       <c r="B119" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>856849</v>
+        <v>857163</v>
       </c>
       <c r="R119" t="n">
-        <v>7485559</v>
+        <v>7485497</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12512,44 +12508,48 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126894592</v>
+        <v>126894597</v>
       </c>
       <c r="B120" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12559,10 +12559,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>857255</v>
+        <v>857222</v>
       </c>
       <c r="R120" t="n">
-        <v>7485644</v>
+        <v>7485544</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12625,10 +12625,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126889014</v>
+        <v>126889030</v>
       </c>
       <c r="B121" t="n">
-        <v>80150</v>
+        <v>98471</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12636,21 +12636,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12660,10 +12660,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>857043</v>
+        <v>857008</v>
       </c>
       <c r="R121" t="n">
-        <v>7485634</v>
+        <v>7485578</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12726,10 +12726,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126889030</v>
+        <v>126889014</v>
       </c>
       <c r="B122" t="n">
-        <v>98469</v>
+        <v>80152</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12737,21 +12737,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12761,10 +12761,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>857008</v>
+        <v>857043</v>
       </c>
       <c r="R122" t="n">
-        <v>7485578</v>
+        <v>7485634</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12830,7 +12830,7 @@
         <v>126899900</v>
       </c>
       <c r="B123" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>126899898</v>
       </c>
       <c r="B124" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>126899894</v>
       </c>
       <c r="B125" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>126899816</v>
       </c>
       <c r="B126" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>126899814</v>
       </c>
       <c r="B127" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>126899815</v>
       </c>
       <c r="B128" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>126899897</v>
       </c>
       <c r="B129" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13560,57 +13560,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126899818</v>
+        <v>126899896</v>
       </c>
       <c r="B130" t="n">
-        <v>98448</v>
+        <v>80152</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>856921</v>
+        <v>856908</v>
       </c>
       <c r="R130" t="n">
-        <v>7485611</v>
+        <v>7485414</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13651,7 +13639,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13663,7 +13650,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13674,45 +13661,57 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126899896</v>
+        <v>126899818</v>
       </c>
       <c r="B131" t="n">
-        <v>80150</v>
+        <v>98450</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>856908</v>
+        <v>856921</v>
       </c>
       <c r="R131" t="n">
-        <v>7485414</v>
+        <v>7485611</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13753,6 +13752,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -13778,7 +13778,7 @@
         <v>126899899</v>
       </c>
       <c r="B132" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>126899817</v>
       </c>
       <c r="B133" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>126899820</v>
       </c>
       <c r="B134" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>126899902</v>
       </c>
       <c r="B135" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>126899901</v>
       </c>
       <c r="B136" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>126899819</v>
       </c>
       <c r="B137" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>126899895</v>
       </c>
       <c r="B138" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>126882460</v>
       </c>
       <c r="B139" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14650,49 +14650,37 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126883898</v>
+        <v>126895795</v>
       </c>
       <c r="B140" t="n">
-        <v>98448</v>
+        <v>97327</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -14701,13 +14689,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>856979</v>
+        <v>856787</v>
       </c>
       <c r="R140" t="n">
-        <v>7485287</v>
+        <v>7485429</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14734,19 +14722,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>13:19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14767,7 +14745,7 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -14778,37 +14756,49 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126895795</v>
+        <v>126883898</v>
       </c>
       <c r="B141" t="n">
-        <v>97325</v>
+        <v>98450</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -14817,13 +14807,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>856787</v>
+        <v>856979</v>
       </c>
       <c r="R141" t="n">
-        <v>7485429</v>
+        <v>7485287</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14850,9 +14840,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14887,7 +14887,7 @@
         <v>126895801</v>
       </c>
       <c r="B142" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>127272114</v>
       </c>
       <c r="B143" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>126895799</v>
       </c>
       <c r="B144" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>127150856</v>
       </c>
       <c r="B145" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>127155655</v>
       </c>
       <c r="B146" t="n">
-        <v>41365</v>
+        <v>41367</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>126895794</v>
       </c>
       <c r="B147" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>126883438</v>
       </c>
       <c r="B148" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>126895796</v>
       </c>
       <c r="B149" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>126882171</v>
       </c>
       <c r="B150" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>126883505</v>
       </c>
       <c r="B151" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>126895798</v>
       </c>
       <c r="B152" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>127272276</v>
       </c>
       <c r="B153" t="n">
-        <v>80087</v>
+        <v>80089</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>126895800</v>
       </c>
       <c r="B154" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>126882331</v>
       </c>
       <c r="B155" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -12827,7 +12827,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126899900</v>
+        <v>126899898</v>
       </c>
       <c r="B123" t="n">
         <v>98450</v>
@@ -12857,12 +12857,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -12874,10 +12874,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>856926</v>
+        <v>856878</v>
       </c>
       <c r="R123" t="n">
-        <v>7485578</v>
+        <v>7485406</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12941,7 +12941,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126899898</v>
+        <v>126899900</v>
       </c>
       <c r="B124" t="n">
         <v>98450</v>
@@ -12971,12 +12971,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>856878</v>
+        <v>856926</v>
       </c>
       <c r="R124" t="n">
-        <v>7485406</v>
+        <v>7485578</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14207,7 +14207,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Lisa Olson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -15660,52 +15660,57 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126895796</v>
+        <v>126882171</v>
       </c>
       <c r="B149" t="n">
-        <v>97327</v>
+        <v>98450</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>856693</v>
+        <v>856765</v>
       </c>
       <c r="R149" t="n">
-        <v>7485505</v>
+        <v>7485445</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15732,18 +15737,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15766,57 +15780,52 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126882171</v>
+        <v>126895796</v>
       </c>
       <c r="B150" t="n">
-        <v>98450</v>
+        <v>97327</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>856765</v>
+        <v>856693</v>
       </c>
       <c r="R150" t="n">
-        <v>7485445</v>
+        <v>7485505</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15843,27 +15852,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -14650,37 +14650,49 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126895795</v>
+        <v>126883898</v>
       </c>
       <c r="B140" t="n">
-        <v>97327</v>
+        <v>98450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -14689,13 +14701,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>856787</v>
+        <v>856979</v>
       </c>
       <c r="R140" t="n">
-        <v>7485429</v>
+        <v>7485287</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14722,9 +14734,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14756,49 +14778,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126883898</v>
+        <v>126895795</v>
       </c>
       <c r="B141" t="n">
-        <v>98450</v>
+        <v>97327</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -14807,13 +14817,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>856979</v>
+        <v>856787</v>
       </c>
       <c r="R141" t="n">
-        <v>7485287</v>
+        <v>7485429</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14840,19 +14850,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>13:19</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15886,10 +15886,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126883505</v>
+        <v>126895798</v>
       </c>
       <c r="B151" t="n">
-        <v>91297</v>
+        <v>97333</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15897,37 +15897,41 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R151" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15954,49 +15958,20 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -16009,14 +15984,18 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY151" t="inlineStr"/>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126895798</v>
+        <v>126883505</v>
       </c>
       <c r="B152" t="n">
-        <v>97333</v>
+        <v>91297</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16024,41 +16003,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R152" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16085,20 +16060,49 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16111,11 +16115,7 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -14639,7 +14639,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -15660,57 +15660,52 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126882171</v>
+        <v>126895796</v>
       </c>
       <c r="B149" t="n">
-        <v>98450</v>
+        <v>97327</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>856765</v>
+        <v>856693</v>
       </c>
       <c r="R149" t="n">
-        <v>7485445</v>
+        <v>7485505</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15737,27 +15732,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15780,52 +15766,57 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126895796</v>
+        <v>126882171</v>
       </c>
       <c r="B150" t="n">
-        <v>97327</v>
+        <v>98450</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>856693</v>
+        <v>856765</v>
       </c>
       <c r="R150" t="n">
-        <v>7485505</v>
+        <v>7485445</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15852,18 +15843,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15886,10 +15886,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126895798</v>
+        <v>126883505</v>
       </c>
       <c r="B151" t="n">
-        <v>97333</v>
+        <v>91297</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15897,41 +15897,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R151" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15958,20 +15954,49 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -15984,18 +16009,14 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126883505</v>
+        <v>126895798</v>
       </c>
       <c r="B152" t="n">
-        <v>91297</v>
+        <v>97333</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16003,37 +16024,41 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R152" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16060,49 +16085,20 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16115,7 +16111,11 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY152" t="inlineStr"/>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -14639,7 +14639,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -14653,7 +14653,7 @@
         <v>126883898</v>
       </c>
       <c r="B140" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>126895795</v>
       </c>
       <c r="B141" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15205,38 +15205,52 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127150856</v>
+        <v>127155655</v>
       </c>
       <c r="B145" t="n">
-        <v>56855</v>
+        <v>41367</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100138</v>
+        <v>215713</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -15245,13 +15259,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R145" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15280,7 +15294,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15290,7 +15304,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15313,60 +15327,42 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127155655</v>
+        <v>127150856</v>
       </c>
       <c r="B146" t="n">
-        <v>41367</v>
+        <v>56855</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>215713</v>
+        <v>100138</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -15375,13 +15371,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R146" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S146" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15410,7 +15406,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15420,7 +15416,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15443,14 +15439,18 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY146" t="inlineStr"/>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
         <v>126895794</v>
       </c>
       <c r="B147" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>126883438</v>
       </c>
       <c r="B148" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15660,52 +15660,57 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126895796</v>
+        <v>126882171</v>
       </c>
       <c r="B149" t="n">
-        <v>97327</v>
+        <v>98456</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>856693</v>
+        <v>856765</v>
       </c>
       <c r="R149" t="n">
-        <v>7485505</v>
+        <v>7485445</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15732,18 +15737,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15766,57 +15780,52 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126882171</v>
+        <v>126895796</v>
       </c>
       <c r="B150" t="n">
-        <v>98450</v>
+        <v>97333</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>856765</v>
+        <v>856693</v>
       </c>
       <c r="R150" t="n">
-        <v>7485445</v>
+        <v>7485505</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15843,27 +15852,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15889,7 +15889,7 @@
         <v>126883505</v>
       </c>
       <c r="B151" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>126895798</v>
       </c>
       <c r="B152" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -14537,7 +14537,7 @@
         <v>126882460</v>
       </c>
       <c r="B139" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14650,49 +14650,37 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126883898</v>
+        <v>126895795</v>
       </c>
       <c r="B140" t="n">
-        <v>98456</v>
+        <v>97336</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -14701,13 +14689,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>856979</v>
+        <v>856787</v>
       </c>
       <c r="R140" t="n">
-        <v>7485287</v>
+        <v>7485429</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14734,19 +14722,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>13:19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14778,37 +14756,49 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126895795</v>
+        <v>126883898</v>
       </c>
       <c r="B141" t="n">
-        <v>97333</v>
+        <v>98459</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -14817,13 +14807,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>856787</v>
+        <v>856979</v>
       </c>
       <c r="R141" t="n">
-        <v>7485429</v>
+        <v>7485287</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14850,9 +14840,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14887,7 +14887,7 @@
         <v>126895801</v>
       </c>
       <c r="B142" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>127272114</v>
       </c>
       <c r="B143" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>126895799</v>
       </c>
       <c r="B144" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15205,52 +15205,38 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127155655</v>
+        <v>127150856</v>
       </c>
       <c r="B145" t="n">
-        <v>41367</v>
+        <v>56858</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>215713</v>
+        <v>100138</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -15259,13 +15245,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R145" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S145" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15294,7 +15280,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15304,7 +15290,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15327,42 +15313,60 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY145" t="inlineStr"/>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127150856</v>
+        <v>127155655</v>
       </c>
       <c r="B146" t="n">
-        <v>56855</v>
+        <v>41368</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100138</v>
+        <v>215713</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -15371,13 +15375,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R146" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15406,7 +15410,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15416,7 +15420,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15439,18 +15443,14 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
         <v>126895794</v>
       </c>
       <c r="B147" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>126883438</v>
       </c>
       <c r="B148" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15660,57 +15660,52 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126882171</v>
+        <v>126895796</v>
       </c>
       <c r="B149" t="n">
-        <v>98456</v>
+        <v>97336</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>856765</v>
+        <v>856693</v>
       </c>
       <c r="R149" t="n">
-        <v>7485445</v>
+        <v>7485505</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15737,27 +15732,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15780,52 +15766,57 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126895796</v>
+        <v>126882171</v>
       </c>
       <c r="B150" t="n">
-        <v>97333</v>
+        <v>98459</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>856693</v>
+        <v>856765</v>
       </c>
       <c r="R150" t="n">
-        <v>7485505</v>
+        <v>7485445</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15852,18 +15843,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15889,7 +15889,7 @@
         <v>126883505</v>
       </c>
       <c r="B151" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>126895798</v>
       </c>
       <c r="B152" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16119,48 +16119,51 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127272276</v>
+        <v>126895800</v>
       </c>
       <c r="B153" t="n">
-        <v>80089</v>
+        <v>79023</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>856765</v>
+        <v>856984</v>
       </c>
       <c r="R153" t="n">
-        <v>7485445</v>
+        <v>7485301</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16187,27 +16190,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16230,51 +16224,48 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126895800</v>
+        <v>127272276</v>
       </c>
       <c r="B154" t="n">
-        <v>79020</v>
+        <v>80092</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>856984</v>
+        <v>856765</v>
       </c>
       <c r="R154" t="n">
-        <v>7485301</v>
+        <v>7485445</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16301,18 +16292,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -16338,7 +16338,7 @@
         <v>126882331</v>
       </c>
       <c r="B155" t="n">
-        <v>80151</v>
+        <v>80154</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -14537,7 +14537,7 @@
         <v>126882460</v>
       </c>
       <c r="B139" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14650,37 +14650,49 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126895795</v>
+        <v>126883898</v>
       </c>
       <c r="B140" t="n">
-        <v>97336</v>
+        <v>98467</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -14689,13 +14701,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>856787</v>
+        <v>856979</v>
       </c>
       <c r="R140" t="n">
-        <v>7485429</v>
+        <v>7485287</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14722,9 +14734,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14756,49 +14778,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126883898</v>
+        <v>126895795</v>
       </c>
       <c r="B141" t="n">
-        <v>98459</v>
+        <v>97344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -14807,13 +14817,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>856979</v>
+        <v>856787</v>
       </c>
       <c r="R141" t="n">
-        <v>7485287</v>
+        <v>7485429</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14840,19 +14850,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>13:19</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14887,7 +14887,7 @@
         <v>126895801</v>
       </c>
       <c r="B142" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>127272114</v>
       </c>
       <c r="B143" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>126895799</v>
       </c>
       <c r="B144" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>127150856</v>
       </c>
       <c r="B145" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>126895794</v>
       </c>
       <c r="B147" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>126883438</v>
       </c>
       <c r="B148" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15653,59 +15653,64 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126895796</v>
+        <v>126882171</v>
       </c>
       <c r="B149" t="n">
-        <v>97336</v>
+        <v>98467</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>856693</v>
+        <v>856765</v>
       </c>
       <c r="R149" t="n">
-        <v>7485505</v>
+        <v>7485445</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15732,18 +15737,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15766,57 +15780,52 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126882171</v>
+        <v>126895796</v>
       </c>
       <c r="B150" t="n">
-        <v>98459</v>
+        <v>97344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>856765</v>
+        <v>856693</v>
       </c>
       <c r="R150" t="n">
-        <v>7485445</v>
+        <v>7485505</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15843,27 +15852,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15889,7 +15889,7 @@
         <v>126883505</v>
       </c>
       <c r="B151" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -16016,7 +16016,7 @@
         <v>126895798</v>
       </c>
       <c r="B152" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>126895800</v>
       </c>
       <c r="B153" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>127272276</v>
       </c>
       <c r="B154" t="n">
-        <v>80092</v>
+        <v>80098</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>126882331</v>
       </c>
       <c r="B155" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -14653,7 +14653,7 @@
         <v>126883898</v>
       </c>
       <c r="B140" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>126895795</v>
       </c>
       <c r="B141" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15205,38 +15205,52 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127150856</v>
+        <v>127155655</v>
       </c>
       <c r="B145" t="n">
-        <v>56864</v>
+        <v>41368</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100138</v>
+        <v>215713</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -15245,13 +15259,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R145" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15280,7 +15294,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15290,7 +15304,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15313,60 +15327,42 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127155655</v>
+        <v>127150856</v>
       </c>
       <c r="B146" t="n">
-        <v>41368</v>
+        <v>56864</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>215713</v>
+        <v>100138</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -15375,13 +15371,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R146" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S146" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15410,7 +15406,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15420,7 +15416,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15443,14 +15439,18 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY146" t="inlineStr"/>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
         <v>126895794</v>
       </c>
       <c r="B147" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>126883438</v>
       </c>
       <c r="B148" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -15663,7 +15663,7 @@
         <v>126882171</v>
       </c>
       <c r="B149" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>126895796</v>
       </c>
       <c r="B150" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15886,10 +15886,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126883505</v>
+        <v>126895798</v>
       </c>
       <c r="B151" t="n">
-        <v>91314</v>
+        <v>97351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15897,37 +15897,41 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R151" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15954,49 +15958,20 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -16006,17 +15981,21 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr"/>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126895798</v>
+        <v>126883505</v>
       </c>
       <c r="B152" t="n">
-        <v>97350</v>
+        <v>91315</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16024,41 +16003,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R152" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16085,20 +16060,49 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16111,11 +16115,7 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -15205,52 +15205,38 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127155655</v>
+        <v>127150856</v>
       </c>
       <c r="B145" t="n">
-        <v>41368</v>
+        <v>56864</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>215713</v>
+        <v>100138</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -15259,13 +15245,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R145" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S145" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15294,7 +15280,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15304,7 +15290,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15327,42 +15313,60 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY145" t="inlineStr"/>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127150856</v>
+        <v>127155655</v>
       </c>
       <c r="B146" t="n">
-        <v>56864</v>
+        <v>41368</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100138</v>
+        <v>215713</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -15371,13 +15375,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R146" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15406,7 +15410,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15416,7 +15420,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15439,11 +15443,7 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16119,51 +16119,48 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126895800</v>
+        <v>127272276</v>
       </c>
       <c r="B153" t="n">
-        <v>79029</v>
+        <v>80098</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>856984</v>
+        <v>856765</v>
       </c>
       <c r="R153" t="n">
-        <v>7485301</v>
+        <v>7485445</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16190,18 +16187,27 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -16224,48 +16230,51 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127272276</v>
+        <v>126895800</v>
       </c>
       <c r="B154" t="n">
-        <v>80098</v>
+        <v>79029</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>856765</v>
+        <v>856984</v>
       </c>
       <c r="R154" t="n">
-        <v>7485445</v>
+        <v>7485301</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16292,27 +16301,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY155"/>
+  <dimension ref="A1:AY173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16444,6 +16444,1784 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>126888993</v>
+      </c>
+      <c r="B156" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>857162</v>
+      </c>
+      <c r="R156" t="n">
+        <v>7485705</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>126888875</v>
+      </c>
+      <c r="B157" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>857144</v>
+      </c>
+      <c r="R157" t="n">
+        <v>7485771</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>126888991</v>
+      </c>
+      <c r="B158" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>857155</v>
+      </c>
+      <c r="R158" t="n">
+        <v>7485715</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>126888890</v>
+      </c>
+      <c r="B159" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>857028</v>
+      </c>
+      <c r="R159" t="n">
+        <v>7485594</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>126888883</v>
+      </c>
+      <c r="B160" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>857179</v>
+      </c>
+      <c r="R160" t="n">
+        <v>7485692</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>126888888</v>
+      </c>
+      <c r="B161" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>856992</v>
+      </c>
+      <c r="R161" t="n">
+        <v>7485577</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>126889008</v>
+      </c>
+      <c r="B162" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>857020</v>
+      </c>
+      <c r="R162" t="n">
+        <v>7485595</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>126888879</v>
+      </c>
+      <c r="B163" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>857164</v>
+      </c>
+      <c r="R163" t="n">
+        <v>7485718</v>
+      </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>126888877</v>
+      </c>
+      <c r="B164" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>857201</v>
+      </c>
+      <c r="R164" t="n">
+        <v>7485722</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>126889001</v>
+      </c>
+      <c r="B165" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>857190</v>
+      </c>
+      <c r="R165" t="n">
+        <v>7485693</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>126888999</v>
+      </c>
+      <c r="B166" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>857178</v>
+      </c>
+      <c r="R166" t="n">
+        <v>7485688</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>126888891</v>
+      </c>
+      <c r="B167" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>857035</v>
+      </c>
+      <c r="R167" t="n">
+        <v>7485607</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>126888985</v>
+      </c>
+      <c r="B168" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>857187</v>
+      </c>
+      <c r="R168" t="n">
+        <v>7485734</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>126888886</v>
+      </c>
+      <c r="B169" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>857027</v>
+      </c>
+      <c r="R169" t="n">
+        <v>7485577</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>126888887</v>
+      </c>
+      <c r="B170" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>856998</v>
+      </c>
+      <c r="R170" t="n">
+        <v>7485568</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>126888874</v>
+      </c>
+      <c r="B171" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>857128</v>
+      </c>
+      <c r="R171" t="n">
+        <v>7485813</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>126888995</v>
+      </c>
+      <c r="B172" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>857166</v>
+      </c>
+      <c r="R172" t="n">
+        <v>7485696</v>
+      </c>
+      <c r="S172" t="n">
+        <v>10</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>126888988</v>
+      </c>
+      <c r="B173" t="n">
+        <v>80217</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Aihkivinsa, Nb</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>857191</v>
+      </c>
+      <c r="R173" t="n">
+        <v>7485719</v>
+      </c>
+      <c r="S173" t="n">
+        <v>10</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -16446,7 +16446,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126888993</v>
+        <v>126888991</v>
       </c>
       <c r="B156" t="n">
         <v>80217</v>
@@ -16481,10 +16481,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>857162</v>
+        <v>857155</v>
       </c>
       <c r="R156" t="n">
-        <v>7485705</v>
+        <v>7485715</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16644,7 +16644,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126888991</v>
+        <v>126888993</v>
       </c>
       <c r="B158" t="n">
         <v>80217</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>857155</v>
+        <v>857162</v>
       </c>
       <c r="R158" t="n">
-        <v>7485715</v>
+        <v>7485705</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16842,7 +16842,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126888883</v>
+        <v>126889008</v>
       </c>
       <c r="B160" t="n">
         <v>80217</v>
@@ -16877,10 +16877,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>857179</v>
+        <v>857020</v>
       </c>
       <c r="R160" t="n">
-        <v>7485692</v>
+        <v>7485595</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16935,7 +16935,11 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY160" t="inlineStr"/>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17036,7 +17040,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126889008</v>
+        <v>126888883</v>
       </c>
       <c r="B162" t="n">
         <v>80217</v>
@@ -17071,10 +17075,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>857020</v>
+        <v>857179</v>
       </c>
       <c r="R162" t="n">
-        <v>7485595</v>
+        <v>7485692</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17129,11 +17133,7 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17234,7 +17234,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126888877</v>
+        <v>126889001</v>
       </c>
       <c r="B164" t="n">
         <v>80217</v>
@@ -17269,10 +17269,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>857201</v>
+        <v>857190</v>
       </c>
       <c r="R164" t="n">
-        <v>7485722</v>
+        <v>7485693</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17327,11 +17327,15 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY164" t="inlineStr"/>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126889001</v>
+        <v>126888877</v>
       </c>
       <c r="B165" t="n">
         <v>80217</v>
@@ -17366,10 +17370,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>857190</v>
+        <v>857201</v>
       </c>
       <c r="R165" t="n">
-        <v>7485693</v>
+        <v>7485722</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17424,11 +17428,7 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17828,7 +17828,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126888887</v>
+        <v>126888874</v>
       </c>
       <c r="B170" t="n">
         <v>80217</v>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>856998</v>
+        <v>857128</v>
       </c>
       <c r="R170" t="n">
-        <v>7485568</v>
+        <v>7485813</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17925,7 +17925,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126888874</v>
+        <v>126888887</v>
       </c>
       <c r="B171" t="n">
         <v>80217</v>
@@ -17960,10 +17960,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>857128</v>
+        <v>856998</v>
       </c>
       <c r="R171" t="n">
-        <v>7485813</v>
+        <v>7485568</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -18022,7 +18022,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126888995</v>
+        <v>126888988</v>
       </c>
       <c r="B172" t="n">
         <v>80217</v>
@@ -18057,10 +18057,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>857166</v>
+        <v>857191</v>
       </c>
       <c r="R172" t="n">
-        <v>7485696</v>
+        <v>7485719</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18123,7 +18123,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126888988</v>
+        <v>126888882</v>
       </c>
       <c r="B173" t="n">
         <v>80217</v>
@@ -18158,10 +18158,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>857191</v>
+        <v>857166</v>
       </c>
       <c r="R173" t="n">
-        <v>7485719</v>
+        <v>7485696</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18216,11 +18216,7 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY173" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -16449,7 +16449,7 @@
         <v>126888991</v>
       </c>
       <c r="B156" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>126888875</v>
       </c>
       <c r="B157" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>126888993</v>
       </c>
       <c r="B158" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>126888890</v>
       </c>
       <c r="B159" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126889008</v>
+        <v>126888883</v>
       </c>
       <c r="B160" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16877,10 +16877,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>857020</v>
+        <v>857179</v>
       </c>
       <c r="R160" t="n">
-        <v>7485595</v>
+        <v>7485692</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16935,18 +16935,14 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126888888</v>
+        <v>126889008</v>
       </c>
       <c r="B161" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16978,10 +16974,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>856992</v>
+        <v>857020</v>
       </c>
       <c r="R161" t="n">
-        <v>7485577</v>
+        <v>7485595</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17036,14 +17032,18 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY161" t="inlineStr"/>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126888883</v>
+        <v>126888879</v>
       </c>
       <c r="B162" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17075,10 +17075,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>857179</v>
+        <v>857164</v>
       </c>
       <c r="R162" t="n">
-        <v>7485692</v>
+        <v>7485718</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17137,10 +17137,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126888879</v>
+        <v>126888888</v>
       </c>
       <c r="B163" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17172,10 +17172,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>857164</v>
+        <v>856992</v>
       </c>
       <c r="R163" t="n">
-        <v>7485718</v>
+        <v>7485577</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17237,7 +17237,7 @@
         <v>126889001</v>
       </c>
       <c r="B164" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>126888877</v>
       </c>
       <c r="B165" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126888999</v>
       </c>
       <c r="B166" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>126888891</v>
       </c>
       <c r="B167" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>126888985</v>
       </c>
       <c r="B168" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>126888886</v>
       </c>
       <c r="B169" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>126888874</v>
       </c>
       <c r="B170" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17925,10 +17925,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126888887</v>
+        <v>126889004</v>
       </c>
       <c r="B171" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18018,14 +18018,18 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY171" t="inlineStr"/>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
         <v>126888988</v>
       </c>
       <c r="B172" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18123,10 +18127,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126888882</v>
+        <v>126888995</v>
       </c>
       <c r="B173" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18216,7 +18220,11 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY173" t="inlineStr"/>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -18127,7 +18127,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126888995</v>
+        <v>126888882</v>
       </c>
       <c r="B173" t="n">
         <v>80221</v>
@@ -18220,11 +18220,7 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY173" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -16449,7 +16449,7 @@
         <v>126888991</v>
       </c>
       <c r="B156" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>126888875</v>
       </c>
       <c r="B157" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>126888993</v>
       </c>
       <c r="B158" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>126888890</v>
       </c>
       <c r="B159" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>126888883</v>
       </c>
       <c r="B160" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>126889008</v>
       </c>
       <c r="B161" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>126888879</v>
       </c>
       <c r="B162" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>126888888</v>
       </c>
       <c r="B163" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>126889001</v>
       </c>
       <c r="B164" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>126888877</v>
       </c>
       <c r="B165" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126888999</v>
       </c>
       <c r="B166" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>126888891</v>
       </c>
       <c r="B167" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>126888985</v>
       </c>
       <c r="B168" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>126888886</v>
       </c>
       <c r="B169" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>126888874</v>
       </c>
       <c r="B170" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>126889004</v>
       </c>
       <c r="B171" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>126888988</v>
       </c>
       <c r="B172" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>126888882</v>
       </c>
       <c r="B173" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -17828,7 +17828,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126888874</v>
+        <v>126888887</v>
       </c>
       <c r="B170" t="n">
         <v>80223</v>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>857128</v>
+        <v>856998</v>
       </c>
       <c r="R170" t="n">
-        <v>7485813</v>
+        <v>7485568</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17925,7 +17925,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126889004</v>
+        <v>126888874</v>
       </c>
       <c r="B171" t="n">
         <v>80223</v>
@@ -17960,10 +17960,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>856998</v>
+        <v>857128</v>
       </c>
       <c r="R171" t="n">
-        <v>7485568</v>
+        <v>7485813</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18018,11 +18018,7 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -17828,7 +17828,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126888887</v>
+        <v>126888874</v>
       </c>
       <c r="B170" t="n">
         <v>80223</v>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>856998</v>
+        <v>857128</v>
       </c>
       <c r="R170" t="n">
-        <v>7485568</v>
+        <v>7485813</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17925,7 +17925,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126888874</v>
+        <v>126889004</v>
       </c>
       <c r="B171" t="n">
         <v>80223</v>
@@ -17960,10 +17960,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>857128</v>
+        <v>856998</v>
       </c>
       <c r="R171" t="n">
-        <v>7485813</v>
+        <v>7485568</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18018,7 +18018,11 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY171" t="inlineStr"/>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -16449,7 +16449,7 @@
         <v>126888991</v>
       </c>
       <c r="B156" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>126888875</v>
       </c>
       <c r="B157" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>126888993</v>
       </c>
       <c r="B158" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>126888890</v>
       </c>
       <c r="B159" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>126888883</v>
       </c>
       <c r="B160" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>126889008</v>
       </c>
       <c r="B161" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>126888879</v>
       </c>
       <c r="B162" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>126888888</v>
       </c>
       <c r="B163" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>126889001</v>
       </c>
       <c r="B164" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>126888877</v>
       </c>
       <c r="B165" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126888999</v>
       </c>
       <c r="B166" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>126888891</v>
       </c>
       <c r="B167" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>126888985</v>
       </c>
       <c r="B168" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>126888886</v>
       </c>
       <c r="B169" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>126888874</v>
       </c>
       <c r="B170" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>126889004</v>
       </c>
       <c r="B171" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>126888988</v>
       </c>
       <c r="B172" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>126888882</v>
       </c>
       <c r="B173" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -16449,7 +16449,7 @@
         <v>126888991</v>
       </c>
       <c r="B156" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>126888875</v>
       </c>
       <c r="B157" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>126888993</v>
       </c>
       <c r="B158" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>126888890</v>
       </c>
       <c r="B159" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>126888883</v>
       </c>
       <c r="B160" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>126889008</v>
       </c>
       <c r="B161" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>126888879</v>
       </c>
       <c r="B162" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>126888888</v>
       </c>
       <c r="B163" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>126889001</v>
       </c>
       <c r="B164" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>126888877</v>
       </c>
       <c r="B165" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126888999</v>
       </c>
       <c r="B166" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>126888891</v>
       </c>
       <c r="B167" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>126888985</v>
       </c>
       <c r="B168" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>126888886</v>
       </c>
       <c r="B169" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>126888874</v>
       </c>
       <c r="B170" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>126889004</v>
       </c>
       <c r="B171" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>126888988</v>
       </c>
       <c r="B172" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>126888882</v>
       </c>
       <c r="B173" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -17925,7 +17925,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126889004</v>
+        <v>126888887</v>
       </c>
       <c r="B171" t="n">
         <v>80254</v>
@@ -18018,15 +18018,11 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126888988</v>
+        <v>126888995</v>
       </c>
       <c r="B172" t="n">
         <v>80254</v>
@@ -18061,10 +18057,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>857191</v>
+        <v>857166</v>
       </c>
       <c r="R172" t="n">
-        <v>7485719</v>
+        <v>7485696</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18127,7 +18123,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126888882</v>
+        <v>126888988</v>
       </c>
       <c r="B173" t="n">
         <v>80254</v>
@@ -18162,10 +18158,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>857166</v>
+        <v>857191</v>
       </c>
       <c r="R173" t="n">
-        <v>7485696</v>
+        <v>7485719</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18220,7 +18216,11 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY173" t="inlineStr"/>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -16449,7 +16449,7 @@
         <v>126888991</v>
       </c>
       <c r="B156" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>126888875</v>
       </c>
       <c r="B157" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>126888993</v>
       </c>
       <c r="B158" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>126888890</v>
       </c>
       <c r="B159" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>126888883</v>
       </c>
       <c r="B160" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>126889008</v>
       </c>
       <c r="B161" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>126888879</v>
       </c>
       <c r="B162" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>126888888</v>
       </c>
       <c r="B163" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>126889001</v>
       </c>
       <c r="B164" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>126888877</v>
       </c>
       <c r="B165" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126888999</v>
       </c>
       <c r="B166" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>126888891</v>
       </c>
       <c r="B167" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>126888985</v>
       </c>
       <c r="B168" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>126888886</v>
       </c>
       <c r="B169" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>126888874</v>
       </c>
       <c r="B170" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17925,10 +17925,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126888887</v>
+        <v>126889004</v>
       </c>
       <c r="B171" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18018,14 +18018,18 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY171" t="inlineStr"/>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126888995</v>
+        <v>126888988</v>
       </c>
       <c r="B172" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18057,10 +18061,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>857166</v>
+        <v>857191</v>
       </c>
       <c r="R172" t="n">
-        <v>7485696</v>
+        <v>7485719</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18123,10 +18127,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126888988</v>
+        <v>126888882</v>
       </c>
       <c r="B173" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18158,10 +18162,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>857191</v>
+        <v>857166</v>
       </c>
       <c r="R173" t="n">
-        <v>7485719</v>
+        <v>7485696</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18216,11 +18220,7 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY173" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -17828,7 +17828,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126888874</v>
+        <v>126888887</v>
       </c>
       <c r="B170" t="n">
         <v>80258</v>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>857128</v>
+        <v>856998</v>
       </c>
       <c r="R170" t="n">
-        <v>7485813</v>
+        <v>7485568</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17925,7 +17925,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126889004</v>
+        <v>126888874</v>
       </c>
       <c r="B171" t="n">
         <v>80258</v>
@@ -17960,10 +17960,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>856998</v>
+        <v>857128</v>
       </c>
       <c r="R171" t="n">
-        <v>7485568</v>
+        <v>7485813</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18018,11 +18018,7 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -17828,7 +17828,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126888887</v>
+        <v>126888874</v>
       </c>
       <c r="B170" t="n">
         <v>80258</v>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>856998</v>
+        <v>857128</v>
       </c>
       <c r="R170" t="n">
-        <v>7485568</v>
+        <v>7485813</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17925,7 +17925,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126888874</v>
+        <v>126889004</v>
       </c>
       <c r="B171" t="n">
         <v>80258</v>
@@ -17960,10 +17960,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>857128</v>
+        <v>856998</v>
       </c>
       <c r="R171" t="n">
-        <v>7485813</v>
+        <v>7485568</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18018,7 +18018,11 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY171" t="inlineStr"/>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -16449,7 +16449,7 @@
         <v>126888991</v>
       </c>
       <c r="B156" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>126888875</v>
       </c>
       <c r="B157" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>126888993</v>
       </c>
       <c r="B158" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>126888890</v>
       </c>
       <c r="B159" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>126888883</v>
       </c>
       <c r="B160" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>126889008</v>
       </c>
       <c r="B161" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>126888879</v>
       </c>
       <c r="B162" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>126888888</v>
       </c>
       <c r="B163" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>126889001</v>
       </c>
       <c r="B164" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>126888877</v>
       </c>
       <c r="B165" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126888999</v>
       </c>
       <c r="B166" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>126888891</v>
       </c>
       <c r="B167" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>126888985</v>
       </c>
       <c r="B168" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>126888886</v>
       </c>
       <c r="B169" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>126888874</v>
       </c>
       <c r="B170" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>126889004</v>
       </c>
       <c r="B171" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>126888988</v>
       </c>
       <c r="B172" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>126888882</v>
       </c>
       <c r="B173" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -16449,7 +16449,7 @@
         <v>126888991</v>
       </c>
       <c r="B156" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>126888875</v>
       </c>
       <c r="B157" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>126888993</v>
       </c>
       <c r="B158" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>126888890</v>
       </c>
       <c r="B159" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>126888883</v>
       </c>
       <c r="B160" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>126889008</v>
       </c>
       <c r="B161" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>126888879</v>
       </c>
       <c r="B162" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>126888888</v>
       </c>
       <c r="B163" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>126889001</v>
       </c>
       <c r="B164" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>126888877</v>
       </c>
       <c r="B165" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126888999</v>
       </c>
       <c r="B166" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>126888891</v>
       </c>
       <c r="B167" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>126888985</v>
       </c>
       <c r="B168" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>126888886</v>
       </c>
       <c r="B169" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>126888874</v>
       </c>
       <c r="B170" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>126889004</v>
       </c>
       <c r="B171" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>126888988</v>
       </c>
       <c r="B172" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>126888882</v>
       </c>
       <c r="B173" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -16842,7 +16842,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126888883</v>
+        <v>126888888</v>
       </c>
       <c r="B160" t="n">
         <v>80168</v>
@@ -16877,10 +16877,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>857179</v>
+        <v>856992</v>
       </c>
       <c r="R160" t="n">
-        <v>7485692</v>
+        <v>7485577</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16939,7 +16939,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126889008</v>
+        <v>126888883</v>
       </c>
       <c r="B161" t="n">
         <v>80168</v>
@@ -16974,10 +16974,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>857020</v>
+        <v>857179</v>
       </c>
       <c r="R161" t="n">
-        <v>7485595</v>
+        <v>7485692</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17032,15 +17032,11 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126888879</v>
+        <v>126889008</v>
       </c>
       <c r="B162" t="n">
         <v>80168</v>
@@ -17075,10 +17071,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>857164</v>
+        <v>857020</v>
       </c>
       <c r="R162" t="n">
-        <v>7485718</v>
+        <v>7485595</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17133,11 +17129,15 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY162" t="inlineStr"/>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126888888</v>
+        <v>126888879</v>
       </c>
       <c r="B163" t="n">
         <v>80168</v>
@@ -17172,10 +17172,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>856992</v>
+        <v>857164</v>
       </c>
       <c r="R163" t="n">
-        <v>7485577</v>
+        <v>7485718</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -16449,7 +16449,7 @@
         <v>126888991</v>
       </c>
       <c r="B156" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>126888875</v>
       </c>
       <c r="B157" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>126888993</v>
       </c>
       <c r="B158" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>126888890</v>
       </c>
       <c r="B159" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126888888</v>
+        <v>126888883</v>
       </c>
       <c r="B160" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16877,10 +16877,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>856992</v>
+        <v>857179</v>
       </c>
       <c r="R160" t="n">
-        <v>7485577</v>
+        <v>7485692</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16939,10 +16939,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126888883</v>
+        <v>126889008</v>
       </c>
       <c r="B161" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16974,10 +16974,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>857179</v>
+        <v>857020</v>
       </c>
       <c r="R161" t="n">
-        <v>7485692</v>
+        <v>7485595</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17032,14 +17032,18 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY161" t="inlineStr"/>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126889008</v>
+        <v>126888879</v>
       </c>
       <c r="B162" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17071,10 +17075,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>857020</v>
+        <v>857164</v>
       </c>
       <c r="R162" t="n">
-        <v>7485595</v>
+        <v>7485718</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17129,18 +17133,14 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126888879</v>
+        <v>126888888</v>
       </c>
       <c r="B163" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17172,10 +17172,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>857164</v>
+        <v>856992</v>
       </c>
       <c r="R163" t="n">
-        <v>7485718</v>
+        <v>7485577</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17237,7 +17237,7 @@
         <v>126889001</v>
       </c>
       <c r="B164" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>126888877</v>
       </c>
       <c r="B165" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>126888999</v>
       </c>
       <c r="B166" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>126888891</v>
       </c>
       <c r="B167" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>126888985</v>
       </c>
       <c r="B168" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>126888886</v>
       </c>
       <c r="B169" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>126888874</v>
       </c>
       <c r="B170" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>126889004</v>
       </c>
       <c r="B171" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>126888988</v>
       </c>
       <c r="B172" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>126888882</v>
       </c>
       <c r="B173" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -16547,7 +16547,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126888875</v>
+        <v>126888993</v>
       </c>
       <c r="B157" t="n">
         <v>80169</v>
@@ -16582,10 +16582,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>857144</v>
+        <v>857162</v>
       </c>
       <c r="R157" t="n">
-        <v>7485771</v>
+        <v>7485705</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16640,11 +16640,15 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY157" t="inlineStr"/>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126888993</v>
+        <v>126888875</v>
       </c>
       <c r="B158" t="n">
         <v>80169</v>
@@ -16679,10 +16683,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>857162</v>
+        <v>857144</v>
       </c>
       <c r="R158" t="n">
-        <v>7485705</v>
+        <v>7485771</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16737,11 +16741,7 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17234,7 +17234,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126889001</v>
+        <v>126888877</v>
       </c>
       <c r="B164" t="n">
         <v>80169</v>
@@ -17269,10 +17269,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>857190</v>
+        <v>857201</v>
       </c>
       <c r="R164" t="n">
-        <v>7485693</v>
+        <v>7485722</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17327,15 +17327,11 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126888877</v>
+        <v>126889001</v>
       </c>
       <c r="B165" t="n">
         <v>80169</v>
@@ -17370,10 +17366,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>857201</v>
+        <v>857190</v>
       </c>
       <c r="R165" t="n">
-        <v>7485722</v>
+        <v>7485693</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17428,7 +17424,11 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY165" t="inlineStr"/>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17925,7 +17925,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126889004</v>
+        <v>126888887</v>
       </c>
       <c r="B171" t="n">
         <v>80169</v>
@@ -18018,15 +18018,11 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126888988</v>
+        <v>126888995</v>
       </c>
       <c r="B172" t="n">
         <v>80169</v>
@@ -18061,10 +18057,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>857191</v>
+        <v>857166</v>
       </c>
       <c r="R172" t="n">
-        <v>7485719</v>
+        <v>7485696</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18127,7 +18123,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126888882</v>
+        <v>126888988</v>
       </c>
       <c r="B173" t="n">
         <v>80169</v>
@@ -18162,10 +18158,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>857166</v>
+        <v>857191</v>
       </c>
       <c r="R173" t="n">
-        <v>7485696</v>
+        <v>7485719</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18220,7 +18216,11 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY173" t="inlineStr"/>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9757-2024 artfynd.xlsx
+++ b/artfynd/A 9757-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>126722664</v>
       </c>
       <c r="B3" t="n">
-        <v>105463</v>
+        <v>105456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126722149</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>126722342</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>126722592</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>126722905</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>126728180</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>126722949</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>126722514</v>
       </c>
       <c r="B10" t="n">
-        <v>98464</v>
+        <v>98457</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>126722689</v>
       </c>
       <c r="B11" t="n">
-        <v>80153</v>
+        <v>80150</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>126728177</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>126722224</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>126728181</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>126722469</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>80143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>126728179</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>126722237</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>126722544</v>
       </c>
       <c r="B18" t="n">
-        <v>80153</v>
+        <v>80150</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>126722838</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>126722552</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>126722312</v>
       </c>
       <c r="B21" t="n">
-        <v>91276</v>
+        <v>91269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>126722784</v>
       </c>
       <c r="B22" t="n">
-        <v>98464</v>
+        <v>98457</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>126728174</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>126728176</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>126722975</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>126722205</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>126728182</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>126728178</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>126722914</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>126722768</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3553,32 +3553,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889016</v>
+        <v>126893335</v>
       </c>
       <c r="B31" t="n">
-        <v>80152</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,13 +3588,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>857042</v>
+        <v>857254</v>
       </c>
       <c r="R31" t="n">
-        <v>7485656</v>
+        <v>7485706</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3638,12 +3638,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3654,45 +3654,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126894596</v>
+        <v>126889016</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>80143</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>857232</v>
+        <v>857042</v>
       </c>
       <c r="R32" t="n">
-        <v>7485521</v>
+        <v>7485656</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3739,12 +3739,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3755,32 +3755,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126893335</v>
+        <v>126893321</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>80143</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>857254</v>
+        <v>857154</v>
       </c>
       <c r="R33" t="n">
-        <v>7485706</v>
+        <v>7485805</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126893321</v>
+        <v>126895913</v>
       </c>
       <c r="B34" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>857154</v>
+        <v>857071</v>
       </c>
       <c r="R34" t="n">
-        <v>7485805</v>
+        <v>7485419</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3941,12 +3941,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -3957,48 +3957,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126895913</v>
+        <v>126894596</v>
       </c>
       <c r="B35" t="n">
-        <v>80152</v>
+        <v>98436</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>857071</v>
+        <v>857232</v>
       </c>
       <c r="R35" t="n">
-        <v>7485419</v>
+        <v>7485521</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4058,10 +4058,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126893328</v>
+        <v>126894580</v>
       </c>
       <c r="B36" t="n">
-        <v>80159</v>
+        <v>80143</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4069,37 +4069,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>856959</v>
+        <v>857065</v>
       </c>
       <c r="R36" t="n">
-        <v>7485620</v>
+        <v>7485568</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4143,12 +4143,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4159,10 +4159,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126894580</v>
+        <v>126893328</v>
       </c>
       <c r="B37" t="n">
-        <v>80152</v>
+        <v>80150</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4170,37 +4170,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>857065</v>
+        <v>856959</v>
       </c>
       <c r="R37" t="n">
-        <v>7485568</v>
+        <v>7485620</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4244,12 +4244,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4263,7 +4263,7 @@
         <v>126893330</v>
       </c>
       <c r="B38" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>126895971</v>
       </c>
       <c r="B39" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>126894589</v>
       </c>
       <c r="B40" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>126889022</v>
       </c>
       <c r="B41" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>126894594</v>
       </c>
       <c r="B42" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>126889042</v>
       </c>
       <c r="B43" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>126894588</v>
       </c>
       <c r="B44" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>126895969</v>
       </c>
       <c r="B45" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>126893332</v>
       </c>
       <c r="B46" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>126894582</v>
       </c>
       <c r="B47" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5272,32 +5272,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126895963</v>
+        <v>126895968</v>
       </c>
       <c r="B48" t="n">
-        <v>98471</v>
+        <v>98436</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>856930</v>
+        <v>856872</v>
       </c>
       <c r="R48" t="n">
-        <v>7485560</v>
+        <v>7485620</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
+          <t>Flera blommande ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5374,10 +5374,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126895968</v>
+        <v>126889044</v>
       </c>
       <c r="B49" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5405,17 +5405,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>856872</v>
+        <v>857220</v>
       </c>
       <c r="R49" t="n">
-        <v>7485620</v>
+        <v>7485601</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5445,11 +5445,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Flera blommande ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5464,22 +5459,26 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126889044</v>
+        <v>126895916</v>
       </c>
       <c r="B50" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5511,13 +5510,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>857220</v>
+        <v>857225</v>
       </c>
       <c r="R50" t="n">
-        <v>7485601</v>
+        <v>7485668</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5561,12 +5560,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5577,10 +5576,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126888927</v>
+        <v>126888930</v>
       </c>
       <c r="B51" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5612,10 +5611,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>856896</v>
+        <v>856694</v>
       </c>
       <c r="R51" t="n">
-        <v>7485538</v>
+        <v>7485592</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5678,10 +5677,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126895916</v>
+        <v>126888927</v>
       </c>
       <c r="B52" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5713,13 +5712,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>857225</v>
+        <v>856896</v>
       </c>
       <c r="R52" t="n">
-        <v>7485668</v>
+        <v>7485538</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5763,12 +5762,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5779,48 +5778,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126888930</v>
+        <v>126895963</v>
       </c>
       <c r="B53" t="n">
-        <v>98450</v>
+        <v>98457</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>856694</v>
+        <v>856930</v>
       </c>
       <c r="R53" t="n">
-        <v>7485592</v>
+        <v>7485560</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5850,6 +5849,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tiotal bladrosetter, varav en överblommade. Intill knärotslokaler med rikligt med bladrosetter på någon m2.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5864,26 +5868,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>126893336</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>126888926</v>
       </c>
       <c r="B55" t="n">
-        <v>80159</v>
+        <v>80150</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>126893326</v>
       </c>
       <c r="B56" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>126895972</v>
       </c>
       <c r="B57" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>126893319</v>
       </c>
       <c r="B58" t="n">
-        <v>91507</v>
+        <v>91494</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6386,32 +6386,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126889013</v>
+        <v>126889052</v>
       </c>
       <c r="B59" t="n">
-        <v>80152</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>857038</v>
+        <v>857206</v>
       </c>
       <c r="R59" t="n">
-        <v>7485632</v>
+        <v>7485553</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6487,32 +6487,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126889052</v>
+        <v>126889013</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>80143</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>857206</v>
+        <v>857038</v>
       </c>
       <c r="R60" t="n">
-        <v>7485553</v>
+        <v>7485632</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6591,7 +6591,7 @@
         <v>126894581</v>
       </c>
       <c r="B61" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>126888928</v>
       </c>
       <c r="B62" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6790,32 +6790,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126895921</v>
+        <v>126895915</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>98436</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6825,10 +6825,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>857123</v>
+        <v>857242</v>
       </c>
       <c r="R63" t="n">
-        <v>7485402</v>
+        <v>7485724</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -6891,48 +6891,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126895961</v>
+        <v>126889041</v>
       </c>
       <c r="B64" t="n">
-        <v>75144</v>
+        <v>98436</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>856840</v>
+        <v>856978</v>
       </c>
       <c r="R64" t="n">
-        <v>7485479</v>
+        <v>7485792</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6976,60 +6976,64 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126894583</v>
+        <v>126895921</v>
       </c>
       <c r="B65" t="n">
-        <v>98471</v>
+        <v>79011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>856988</v>
+        <v>857123</v>
       </c>
       <c r="R65" t="n">
-        <v>7485572</v>
+        <v>7485402</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7073,12 +7077,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7089,48 +7093,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126889032</v>
+        <v>126895961</v>
       </c>
       <c r="B66" t="n">
-        <v>98471</v>
+        <v>75135</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>857038</v>
+        <v>856840</v>
       </c>
       <c r="R66" t="n">
-        <v>7485636</v>
+        <v>7485479</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7174,64 +7178,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126895915</v>
+        <v>126894583</v>
       </c>
       <c r="B67" t="n">
-        <v>98450</v>
+        <v>98457</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>857242</v>
+        <v>856988</v>
       </c>
       <c r="R67" t="n">
-        <v>7485724</v>
+        <v>7485572</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7275,12 +7275,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7291,32 +7291,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126889041</v>
+        <v>126889032</v>
       </c>
       <c r="B68" t="n">
-        <v>98450</v>
+        <v>98457</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>856978</v>
+        <v>857038</v>
       </c>
       <c r="R68" t="n">
-        <v>7485792</v>
+        <v>7485636</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7392,32 +7392,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126889021</v>
+        <v>126889045</v>
       </c>
       <c r="B69" t="n">
-        <v>80152</v>
+        <v>98436</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>857000</v>
+        <v>857084</v>
       </c>
       <c r="R69" t="n">
-        <v>7485629</v>
+        <v>7485530</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7493,32 +7493,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126889024</v>
+        <v>126889047</v>
       </c>
       <c r="B70" t="n">
-        <v>80152</v>
+        <v>98436</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>856962</v>
+        <v>857010</v>
       </c>
       <c r="R70" t="n">
-        <v>7485641</v>
+        <v>7485585</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7597,7 +7597,7 @@
         <v>126889029</v>
       </c>
       <c r="B71" t="n">
-        <v>98471</v>
+        <v>98457</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7695,32 +7695,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126895922</v>
+        <v>126895910</v>
       </c>
       <c r="B72" t="n">
-        <v>79020</v>
+        <v>80143</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7730,10 +7730,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>856981</v>
+        <v>856984</v>
       </c>
       <c r="R72" t="n">
-        <v>7485578</v>
+        <v>7485600</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -7796,32 +7796,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126895920</v>
+        <v>126889021</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>80143</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7831,13 +7831,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>857173</v>
+        <v>857000</v>
       </c>
       <c r="R73" t="n">
-        <v>7485506</v>
+        <v>7485629</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7881,12 +7881,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7897,10 +7897,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126895910</v>
+        <v>126889024</v>
       </c>
       <c r="B74" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7932,13 +7932,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>856984</v>
+        <v>856962</v>
       </c>
       <c r="R74" t="n">
-        <v>7485600</v>
+        <v>7485641</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7982,12 +7982,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -7998,32 +7998,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126889045</v>
+        <v>126895920</v>
       </c>
       <c r="B75" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8033,13 +8033,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>857084</v>
+        <v>857173</v>
       </c>
       <c r="R75" t="n">
-        <v>7485530</v>
+        <v>7485506</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8083,12 +8083,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8099,32 +8099,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126889047</v>
+        <v>126895922</v>
       </c>
       <c r="B76" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8134,13 +8134,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>857010</v>
+        <v>856981</v>
       </c>
       <c r="R76" t="n">
-        <v>7485585</v>
+        <v>7485578</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8184,12 +8184,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8200,32 +8200,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126894602</v>
+        <v>126894584</v>
       </c>
       <c r="B77" t="n">
-        <v>79020</v>
+        <v>97320</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>857075</v>
+        <v>857231</v>
       </c>
       <c r="R77" t="n">
-        <v>7485539</v>
+        <v>7485574</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8301,10 +8301,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126894584</v>
+        <v>126889039</v>
       </c>
       <c r="B78" t="n">
-        <v>97333</v>
+        <v>97320</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8332,14 +8332,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>857231</v>
+        <v>857184</v>
       </c>
       <c r="R78" t="n">
-        <v>7485574</v>
+        <v>7485414</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8386,12 +8386,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8402,45 +8402,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126889039</v>
+        <v>126894602</v>
       </c>
       <c r="B79" t="n">
-        <v>97333</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>857184</v>
+        <v>857075</v>
       </c>
       <c r="R79" t="n">
-        <v>7485414</v>
+        <v>7485539</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8487,12 +8487,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8503,32 +8503,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126895918</v>
+        <v>126895912</v>
       </c>
       <c r="B80" t="n">
-        <v>79020</v>
+        <v>80143</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>857150</v>
+        <v>857018</v>
       </c>
       <c r="R80" t="n">
-        <v>7485418</v>
+        <v>7485408</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -8604,32 +8604,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126895912</v>
+        <v>126895918</v>
       </c>
       <c r="B81" t="n">
-        <v>80152</v>
+        <v>79011</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>857018</v>
+        <v>857150</v>
       </c>
       <c r="R81" t="n">
-        <v>7485408</v>
+        <v>7485418</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -8705,32 +8705,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126893339</v>
+        <v>126888931</v>
       </c>
       <c r="B82" t="n">
-        <v>79020</v>
+        <v>91893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8740,13 +8740,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>857104</v>
+        <v>856896</v>
       </c>
       <c r="R82" t="n">
-        <v>7485447</v>
+        <v>7485431</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8790,12 +8790,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8806,32 +8806,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126894601</v>
+        <v>126894590</v>
       </c>
       <c r="B83" t="n">
-        <v>79020</v>
+        <v>98436</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>857215</v>
+        <v>857265</v>
       </c>
       <c r="R83" t="n">
-        <v>7485457</v>
+        <v>7485680</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8907,32 +8907,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126888931</v>
+        <v>126893339</v>
       </c>
       <c r="B84" t="n">
-        <v>91906</v>
+        <v>79011</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8942,13 +8942,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>856896</v>
+        <v>857104</v>
       </c>
       <c r="R84" t="n">
-        <v>7485431</v>
+        <v>7485447</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8992,12 +8992,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9008,45 +9008,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126889019</v>
+        <v>126894601</v>
       </c>
       <c r="B85" t="n">
-        <v>80152</v>
+        <v>79011</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>857016</v>
+        <v>857215</v>
       </c>
       <c r="R85" t="n">
-        <v>7485635</v>
+        <v>7485457</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9093,12 +9093,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9109,32 +9109,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126888929</v>
+        <v>126889019</v>
       </c>
       <c r="B86" t="n">
-        <v>98450</v>
+        <v>80143</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>856800</v>
+        <v>857016</v>
       </c>
       <c r="R86" t="n">
-        <v>7485540</v>
+        <v>7485635</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9194,12 +9194,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9210,10 +9210,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126894590</v>
+        <v>126888929</v>
       </c>
       <c r="B87" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9241,14 +9241,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>857265</v>
+        <v>856800</v>
       </c>
       <c r="R87" t="n">
-        <v>7485680</v>
+        <v>7485540</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9295,12 +9295,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Ulrika Hållstedt, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9311,32 +9311,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126889017</v>
+        <v>126895917</v>
       </c>
       <c r="B88" t="n">
-        <v>80152</v>
+        <v>79011</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>857021</v>
+        <v>857220</v>
       </c>
       <c r="R88" t="n">
-        <v>7485648</v>
+        <v>7485407</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9396,12 +9396,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9412,48 +9412,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126895973</v>
+        <v>126889017</v>
       </c>
       <c r="B89" t="n">
-        <v>98450</v>
+        <v>80143</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>856707</v>
+        <v>857021</v>
       </c>
       <c r="R89" t="n">
-        <v>7485577</v>
+        <v>7485648</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9497,44 +9497,48 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126895917</v>
+        <v>126889034</v>
       </c>
       <c r="B90" t="n">
-        <v>79020</v>
+        <v>98457</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9544,13 +9548,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>857220</v>
+        <v>856998</v>
       </c>
       <c r="R90" t="n">
-        <v>7485407</v>
+        <v>7485630</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9594,12 +9598,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9610,48 +9614,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126889034</v>
+        <v>126895973</v>
       </c>
       <c r="B91" t="n">
-        <v>98471</v>
+        <v>98436</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>856998</v>
+        <v>856707</v>
       </c>
       <c r="R91" t="n">
-        <v>7485630</v>
+        <v>7485577</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9695,64 +9699,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126893327</v>
+        <v>126895962</v>
       </c>
       <c r="B92" t="n">
-        <v>91316</v>
+        <v>91319</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4660</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>857141</v>
+        <v>856927</v>
       </c>
       <c r="R92" t="n">
-        <v>7485413</v>
+        <v>7485482</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9796,64 +9796,60 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126895962</v>
+        <v>126893327</v>
       </c>
       <c r="B93" t="n">
-        <v>91332</v>
+        <v>91303</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>856927</v>
+        <v>857141</v>
       </c>
       <c r="R93" t="n">
-        <v>7485482</v>
+        <v>7485413</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9897,22 +9893,26 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
         <v>126889025</v>
       </c>
       <c r="B94" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>126889050</v>
       </c>
       <c r="B95" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>126893323</v>
       </c>
       <c r="B96" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>126893325</v>
       </c>
       <c r="B97" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>126895914</v>
       </c>
       <c r="B98" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>126893333</v>
       </c>
       <c r="B99" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10515,48 +10515,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126895911</v>
+        <v>126894595</v>
       </c>
       <c r="B100" t="n">
-        <v>80152</v>
+        <v>98436</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>856885</v>
+        <v>857231</v>
       </c>
       <c r="R100" t="n">
-        <v>7485704</v>
+        <v>7485574</v>
       </c>
       <c r="S100" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10586,11 +10586,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10605,12 +10600,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Marlene Kangas</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10621,10 +10616,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126894595</v>
+        <v>126889049</v>
       </c>
       <c r="B101" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10652,14 +10647,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>857231</v>
+        <v>857013</v>
       </c>
       <c r="R101" t="n">
-        <v>7485574</v>
+        <v>7485581</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10706,12 +10701,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10722,10 +10717,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126889049</v>
+        <v>126895967</v>
       </c>
       <c r="B102" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10753,17 +10748,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>857013</v>
+        <v>856932</v>
       </c>
       <c r="R102" t="n">
-        <v>7485581</v>
+        <v>7485559</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10807,64 +10802,60 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126895967</v>
+        <v>126895911</v>
       </c>
       <c r="B103" t="n">
-        <v>98450</v>
+        <v>80143</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>856932</v>
+        <v>856885</v>
       </c>
       <c r="R103" t="n">
-        <v>7485559</v>
+        <v>7485704</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10894,6 +10885,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10908,22 +10904,26 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marlene Kangas</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr"/>
+          <t>Marlene Kangas, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
         <v>126889036</v>
       </c>
       <c r="B104" t="n">
-        <v>80027</v>
+        <v>80018</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>126889037</v>
       </c>
       <c r="B105" t="n">
-        <v>80027</v>
+        <v>80018</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11122,10 +11122,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126895966</v>
+        <v>126893322</v>
       </c>
       <c r="B106" t="n">
-        <v>80159</v>
+        <v>80143</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11133,40 +11133,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>856849</v>
+        <v>857015</v>
       </c>
       <c r="R106" t="n">
-        <v>7485405</v>
+        <v>7485514</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11204,29 +11201,32 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126893322</v>
+        <v>126895966</v>
       </c>
       <c r="B107" t="n">
-        <v>80152</v>
+        <v>80150</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11234,37 +11234,40 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>857015</v>
+        <v>856849</v>
       </c>
       <c r="R107" t="n">
-        <v>7485514</v>
+        <v>7485405</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11302,32 +11305,29 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
         <v>126893338</v>
       </c>
       <c r="B108" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11425,48 +11425,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126895975</v>
+        <v>126893324</v>
       </c>
       <c r="B109" t="n">
-        <v>79020</v>
+        <v>80143</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>856864</v>
+        <v>856949</v>
       </c>
       <c r="R109" t="n">
-        <v>7485417</v>
+        <v>7485588</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11510,60 +11510,64 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126893324</v>
+        <v>126895975</v>
       </c>
       <c r="B110" t="n">
-        <v>80152</v>
+        <v>79011</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>856949</v>
+        <v>856864</v>
       </c>
       <c r="R110" t="n">
-        <v>7485588</v>
+        <v>7485417</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11607,26 +11611,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
         <v>126893334</v>
       </c>
       <c r="B111" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>126893329</v>
       </c>
       <c r="B112" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126893320</v>
+        <v>126894585</v>
       </c>
       <c r="B113" t="n">
-        <v>80152</v>
+        <v>97320</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11836,37 +11836,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>857058</v>
+        <v>857167</v>
       </c>
       <c r="R113" t="n">
-        <v>7485807</v>
+        <v>7485432</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11910,12 +11910,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Marie Persson, Stefan Phalagorn Bergström</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -11926,10 +11926,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126894585</v>
+        <v>126893320</v>
       </c>
       <c r="B114" t="n">
-        <v>97333</v>
+        <v>80143</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11937,37 +11937,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>857167</v>
+        <v>857058</v>
       </c>
       <c r="R114" t="n">
-        <v>7485432</v>
+        <v>7485807</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12011,12 +12011,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Marie Persson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12027,48 +12027,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126889027</v>
+        <v>126895970</v>
       </c>
       <c r="B115" t="n">
-        <v>80152</v>
+        <v>98436</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Aihkivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>856947</v>
+        <v>856849</v>
       </c>
       <c r="R115" t="n">
-        <v>7485678</v>
+        <v>7485559</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12112,64 +12112,60 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126895965</v>
+        <v>126894592</v>
       </c>
       <c r="B116" t="n">
-        <v>80159</v>
+        <v>98436</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>856897</v>
+        <v>857255</v>
       </c>
       <c r="R116" t="n">
-        <v>7485429</v>
+        <v>7485644</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12213,60 +12209,64 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126895970</v>
+        <v>126894600</v>
       </c>
       <c r="B117" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Aihkivinsa Ö, Nb</t>
+          <t>Aihikivinsa, Nb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>856849</v>
+        <v>857163</v>
       </c>
       <c r="R117" t="n">
-        <v>7485559</v>
+        <v>7485497</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12310,44 +12310,48 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Sarah Jost</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr"/>
+          <t>Sarah Jost</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126894592</v>
+        <v>126894597</v>
       </c>
       <c r="B118" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12357,10 +12361,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>857255</v>
+        <v>857222</v>
       </c>
       <c r="R118" t="n">
-        <v>7485644</v>
+        <v>7485544</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12423,45 +12427,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126894600</v>
+        <v>126889027</v>
       </c>
       <c r="B119" t="n">
-        <v>79020</v>
+        <v>80143</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>857163</v>
+        <v>856947</v>
       </c>
       <c r="R119" t="n">
-        <v>7485497</v>
+        <v>7485678</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12508,12 +12512,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Viktoria Sturk, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12524,48 +12528,48 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126894597</v>
+        <v>126895965</v>
       </c>
       <c r="B120" t="n">
-        <v>79020</v>
+        <v>80150</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Aihikivinsa, Nb</t>
+          <t>Aihkivinsa Ö, Nb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>857222</v>
+        <v>856897</v>
       </c>
       <c r="R120" t="n">
-        <v>7485544</v>
+        <v>7485429</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12609,26 +12613,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Sarah Jost</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126889030</v>
+        <v>126889014</v>
       </c>
       <c r="B121" t="n">
-        <v>98471</v>
+        <v>80143</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12636,21 +12636,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12660,10 +12660,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>857008</v>
+        <v>857043</v>
       </c>
       <c r="R121" t="n">
-        <v>7485578</v>
+        <v>7485634</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12726,10 +12726,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126889014</v>
+        <v>126889030</v>
       </c>
       <c r="B122" t="n">
-        <v>80152</v>
+        <v>98457</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12737,21 +12737,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12761,10 +12761,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>857043</v>
+        <v>857008</v>
       </c>
       <c r="R122" t="n">
-        <v>7485634</v>
+        <v>7485578</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12827,10 +12827,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126899898</v>
+        <v>126899900</v>
       </c>
       <c r="B123" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12857,12 +12857,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -12874,10 +12874,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>856878</v>
+        <v>856926</v>
       </c>
       <c r="R123" t="n">
-        <v>7485406</v>
+        <v>7485578</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12941,10 +12941,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126899900</v>
+        <v>126899898</v>
       </c>
       <c r="B124" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12971,12 +12971,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>856926</v>
+        <v>856878</v>
       </c>
       <c r="R124" t="n">
-        <v>7485578</v>
+        <v>7485406</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13058,7 +13058,7 @@
         <v>126899894</v>
       </c>
       <c r="B125" t="n">
-        <v>75144</v>
+        <v>75135</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>126899816</v>
       </c>
       <c r="B126" t="n">
-        <v>80159</v>
+        <v>80150</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>126899814</v>
       </c>
       <c r="B127" t="n">
-        <v>75144</v>
+        <v>75135</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>126899815</v>
       </c>
       <c r="B128" t="n">
-        <v>98471</v>
+        <v>98457</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>126899897</v>
       </c>
       <c r="B129" t="n">
-        <v>80159</v>
+        <v>80150</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13560,45 +13560,57 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126899896</v>
+        <v>126899818</v>
       </c>
       <c r="B130" t="n">
-        <v>80152</v>
+        <v>98436</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>856908</v>
+        <v>856921</v>
       </c>
       <c r="R130" t="n">
-        <v>7485414</v>
+        <v>7485611</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13639,6 +13651,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13650,7 +13663,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13661,57 +13674,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126899818</v>
+        <v>126899896</v>
       </c>
       <c r="B131" t="n">
-        <v>98450</v>
+        <v>80143</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>856921</v>
+        <v>856908</v>
       </c>
       <c r="R131" t="n">
-        <v>7485611</v>
+        <v>7485414</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13752,7 +13753,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -13778,7 +13778,7 @@
         <v>126899899</v>
       </c>
       <c r="B132" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>126899817</v>
       </c>
       <c r="B133" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>126899820</v>
       </c>
       <c r="B134" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>126899902</v>
       </c>
       <c r="B135" t="n">
-        <v>91906</v>
+        <v>91893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Lisa Olson</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14218,45 +14218,57 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126899901</v>
+        <v>126899819</v>
       </c>
       <c r="B136" t="n">
-        <v>79020</v>
+        <v>98436</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>856929</v>
+        <v>856846</v>
       </c>
       <c r="R136" t="n">
-        <v>7485563</v>
+        <v>7485645</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14297,6 +14309,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14308,7 +14321,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
+          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14319,57 +14332,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126899819</v>
+        <v>126899901</v>
       </c>
       <c r="B137" t="n">
-        <v>98450</v>
+        <v>79011</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>856846</v>
+        <v>856929</v>
       </c>
       <c r="R137" t="n">
-        <v>7485645</v>
+        <v>7485563</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14410,7 +14411,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Göran Ehn, Stefan Phalagorn Bergström</t>
+          <t>Lisa Olson, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14436,7 +14436,7 @@
         <v>126899895</v>
       </c>
       <c r="B138" t="n">
-        <v>75144</v>
+        <v>75135</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>126882460</v>
       </c>
       <c r="B139" t="n">
-        <v>56864</v>
+        <v>56849</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>126883898</v>
       </c>
       <c r="B140" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>126895795</v>
       </c>
       <c r="B141" t="n">
-        <v>97345</v>
+        <v>97314</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>126895801</v>
       </c>
       <c r="B142" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>127272114</v>
       </c>
       <c r="B143" t="n">
-        <v>80161</v>
+        <v>80143</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>126895799</v>
       </c>
       <c r="B144" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>127150856</v>
       </c>
       <c r="B145" t="n">
-        <v>56864</v>
+        <v>56849</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15324,7 +15324,7 @@
         <v>127155655</v>
       </c>
       <c r="B146" t="n">
-        <v>41368</v>
+        <v>41361</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>126895794</v>
       </c>
       <c r="B147" t="n">
-        <v>97345</v>
+        <v>97314</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>126883438</v>
       </c>
       <c r="B148" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>126882171</v>
       </c>
       <c r="B149" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>126895796</v>
       </c>
       <c r="B150" t="n">
-        <v>97345</v>
+        <v>97314</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15886,10 +15886,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126895798</v>
+        <v>126883505</v>
       </c>
       <c r="B151" t="n">
-        <v>97351</v>
+        <v>91284</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15897,41 +15897,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>857037</v>
+        <v>856901</v>
       </c>
       <c r="R151" t="n">
-        <v>7485288</v>
+        <v>7485387</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -15958,20 +15954,49 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -15984,18 +16009,14 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126883505</v>
+        <v>126895798</v>
       </c>
       <c r="B152" t="n">
-        <v>91315</v>
+        <v>97320</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16003,37 +16024,41 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Aihkivinsa, Nb</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>856901</v>
+        <v>857037</v>
       </c>
       <c r="R152" t="n">
-        <v>7485387</v>
+        <v>7485288</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16060,49 +16085,20 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
@@ -16115,14 +16111,18 @@
           <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
-      <c r="AY152" t="inlineStr"/>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
         <v>127272276</v>
       </c>
       <c r="B153" t="n">
-        <v>80098</v>
+        <v>80080</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>126895800</v>
       </c>
       <c r="B154" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>126882331</v>
       </c>
       <c r="B155" t="n">
-        <v>80160</v>
+        <v>80142</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
